--- a/data/chapter2/Brundrett and Tedersoo 2018 - mycorrhizal associations.xlsx
+++ b/data/chapter2/Brundrett and Tedersoo 2018 - mycorrhizal associations.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="27309"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Brundrettm/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90963425_westernsydney_edu_au/Documents/PhD/code/data/chapter2/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_9EE980E2FD5D26AFDFEDEA635E1132CB8726D636" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1000" yWindow="460" windowWidth="27340" windowHeight="16400" tabRatio="500"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Article Information" sheetId="7" r:id="rId1"/>
@@ -20,10 +21,21 @@
     <sheet name="Terminology" sheetId="6" r:id="rId6"/>
     <sheet name="References" sheetId="4" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="150000" concurrentCalc="0"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr defaultImageDpi="32767"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
@@ -4378,8 +4390,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="25" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="25">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -4774,16 +4786,16 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4822,26 +4834,29 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:I439" totalsRowShown="0" headerRowDxfId="1" tableBorderDxfId="0">
-  <autoFilter ref="A1:I439"/>
-  <sortState ref="A2:I439">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:I439" totalsRowShown="0" headerRowDxfId="1" tableBorderDxfId="0">
+  <autoFilter ref="A1:I439" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I439">
     <sortCondition ref="C1:C439"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="2" name="Order"/>
-    <tableColumn id="3" name="Family"/>
-    <tableColumn id="4" name="Numeric Order"/>
-    <tableColumn id="5" name="~Genera"/>
-    <tableColumn id="6" name="~Species"/>
-    <tableColumn id="8" name="Mycorrhiza"/>
-    <tableColumn id="9" name="Second Type"/>
-    <tableColumn id="10" name="Category"/>
-    <tableColumn id="11" name="Notes"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Order"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Family"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Numeric Order"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="~Genera"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="~Species"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Mycorrhiza"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Second Type"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Category"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5109,29 +5124,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="97.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>1239</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1">
       <c r="A2" s="12" t="s">
         <v>1240</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1">
       <c r="A3" s="12" t="s">
         <v>1241</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1">
       <c r="A4" s="12" t="s">
         <v>1242</v>
       </c>
@@ -5142,128 +5157,128 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="140" style="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" ht="36" customHeight="1">
       <c r="A1" s="60" t="s">
         <v>1289</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" ht="22" customHeight="1">
       <c r="A2" s="59" t="s">
         <v>1238</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1">
       <c r="A3" s="19" t="s">
         <v>1228</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1">
       <c r="A4" s="19" t="s">
         <v>1232</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1">
       <c r="A5" s="19" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1">
       <c r="A6" s="19" t="s">
         <v>1217</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" ht="31">
       <c r="A7" s="19" t="s">
         <v>1215</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1">
       <c r="A8" s="19" t="s">
         <v>1229</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1">
       <c r="A9" s="24" t="s">
         <v>1216</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1">
       <c r="A10" s="19"/>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1">
       <c r="A11" s="20" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="48" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" ht="46.5">
       <c r="A12" s="19" t="s">
         <v>1230</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1">
       <c r="A13" s="19"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1">
       <c r="A14" s="20" t="s">
         <v>1231</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" ht="31">
       <c r="A15" s="22" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1">
       <c r="A16" s="22" t="s">
         <v>1243</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" ht="31">
       <c r="A17" s="22" t="s">
         <v>1244</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" ht="31">
       <c r="A18" s="22" t="s">
         <v>1233</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" ht="31">
       <c r="A19" s="22" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" ht="31">
       <c r="A20" s="22" t="s">
         <v>1245</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1">
       <c r="A21" s="23" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1">
       <c r="A22" s="19"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1">
       <c r="A23" s="20" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1">
       <c r="A24" s="19" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1">
       <c r="A26" s="25" t="s">
         <v>1237</v>
       </c>
@@ -5274,9 +5289,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K446"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
     <col min="2" max="2" width="24.5" customWidth="1"/>
@@ -5289,7 +5304,7 @@
     <col min="9" max="9" width="28.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5317,11 +5332,11 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="64" t="s">
+      <c r="K1" s="62" t="s">
         <v>1246</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>45</v>
       </c>
@@ -5348,7 +5363,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>126</v>
       </c>
@@ -5372,7 +5387,7 @@
       </c>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>126</v>
       </c>
@@ -5398,7 +5413,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>126</v>
       </c>
@@ -5422,7 +5437,7 @@
       </c>
       <c r="I5" s="4"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>84</v>
       </c>
@@ -5446,7 +5461,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
         <v>84</v>
       </c>
@@ -5470,7 +5485,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
         <v>84</v>
       </c>
@@ -5494,7 +5509,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>136</v>
       </c>
@@ -5518,7 +5533,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>136</v>
       </c>
@@ -5542,7 +5557,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>72</v>
       </c>
@@ -5563,7 +5578,7 @@
       </c>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
         <v>72</v>
       </c>
@@ -5586,7 +5601,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="13" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" s="8" customFormat="1">
       <c r="A13" s="8" t="s">
         <v>72</v>
       </c>
@@ -5612,7 +5627,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11">
       <c r="A14" s="8" t="s">
         <v>72</v>
       </c>
@@ -5637,7 +5652,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
         <v>53</v>
       </c>
@@ -5658,7 +5673,7 @@
       </c>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
         <v>53</v>
       </c>
@@ -5679,7 +5694,7 @@
       </c>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
         <v>53</v>
       </c>
@@ -5703,7 +5718,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -5727,7 +5742,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" s="8" customFormat="1">
       <c r="A19" t="s">
         <v>53</v>
       </c>
@@ -5752,7 +5767,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -5773,7 +5788,7 @@
       </c>
       <c r="H20" s="4"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
         <v>82</v>
       </c>
@@ -5794,7 +5809,7 @@
       </c>
       <c r="H21" s="4"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
         <v>82</v>
       </c>
@@ -5818,7 +5833,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" s="8" customFormat="1">
       <c r="A23" t="s">
         <v>82</v>
       </c>
@@ -5843,7 +5858,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
         <v>82</v>
       </c>
@@ -5867,7 +5882,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9">
       <c r="A25" t="s">
         <v>82</v>
       </c>
@@ -5888,7 +5903,7 @@
       </c>
       <c r="H25" s="4"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
         <v>82</v>
       </c>
@@ -5909,7 +5924,7 @@
       </c>
       <c r="H26" s="4"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9">
       <c r="A27" s="8" t="s">
         <v>82</v>
       </c>
@@ -5934,7 +5949,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9">
       <c r="A28" t="s">
         <v>158</v>
       </c>
@@ -5958,7 +5973,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9">
       <c r="A29" s="8" t="s">
         <v>82</v>
       </c>
@@ -5983,7 +5998,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9">
       <c r="A30" t="s">
         <v>19</v>
       </c>
@@ -6006,7 +6021,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9">
       <c r="A31" s="8" t="s">
         <v>32</v>
       </c>
@@ -6035,7 +6050,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9">
       <c r="A32" s="12" t="s">
         <v>32</v>
       </c>
@@ -6060,7 +6075,7 @@
       </c>
       <c r="I32" s="12"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -6083,7 +6098,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -6106,7 +6121,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9">
       <c r="A35" t="s">
         <v>32</v>
       </c>
@@ -6129,7 +6144,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" s="8" customFormat="1">
       <c r="A36" t="s">
         <v>32</v>
       </c>
@@ -6154,7 +6169,7 @@
       </c>
       <c r="I36"/>
     </row>
-    <row r="37" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" s="8" customFormat="1">
       <c r="A37" t="s">
         <v>32</v>
       </c>
@@ -6181,7 +6196,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" s="8" customFormat="1">
       <c r="A38" t="s">
         <v>32</v>
       </c>
@@ -6206,7 +6221,7 @@
       </c>
       <c r="I38"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9">
       <c r="A39" t="s">
         <v>32</v>
       </c>
@@ -6229,7 +6244,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9">
       <c r="A40" t="s">
         <v>32</v>
       </c>
@@ -6255,7 +6270,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9">
       <c r="A41" t="s">
         <v>32</v>
       </c>
@@ -6278,7 +6293,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" s="5" customFormat="1">
       <c r="A42" t="s">
         <v>32</v>
       </c>
@@ -6303,7 +6318,7 @@
       </c>
       <c r="I42"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9">
       <c r="A43" t="s">
         <v>32</v>
       </c>
@@ -6326,7 +6341,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9">
       <c r="A44" t="s">
         <v>32</v>
       </c>
@@ -6352,7 +6367,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9">
       <c r="A45" t="s">
         <v>32</v>
       </c>
@@ -6375,7 +6390,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9">
       <c r="A46" t="s">
         <v>398</v>
       </c>
@@ -6402,7 +6417,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9">
       <c r="A47" t="s">
         <v>117</v>
       </c>
@@ -6423,7 +6438,7 @@
       </c>
       <c r="H47" s="4"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9">
       <c r="A48" t="s">
         <v>117</v>
       </c>
@@ -6450,7 +6465,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9">
       <c r="A49" t="s">
         <v>117</v>
       </c>
@@ -6471,7 +6486,7 @@
       </c>
       <c r="H49" s="4"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9">
       <c r="A50" t="s">
         <v>188</v>
       </c>
@@ -6498,7 +6513,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9">
       <c r="A51" t="s">
         <v>188</v>
       </c>
@@ -6519,7 +6534,7 @@
       </c>
       <c r="H51" s="4"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9">
       <c r="A52" t="s">
         <v>188</v>
       </c>
@@ -6540,7 +6555,7 @@
       </c>
       <c r="H52" s="4"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9">
       <c r="A53" t="s">
         <v>188</v>
       </c>
@@ -6563,7 +6578,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9">
       <c r="A54" t="s">
         <v>188</v>
       </c>
@@ -6584,7 +6599,7 @@
       </c>
       <c r="H54" s="4"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9">
       <c r="A55" t="s">
         <v>36</v>
       </c>
@@ -6608,7 +6623,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9">
       <c r="A56" t="s">
         <v>36</v>
       </c>
@@ -6634,7 +6649,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9">
       <c r="A57" t="s">
         <v>36</v>
       </c>
@@ -6655,7 +6670,7 @@
       </c>
       <c r="H57" s="4"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9">
       <c r="A58" t="s">
         <v>36</v>
       </c>
@@ -6679,7 +6694,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9">
       <c r="A59" t="s">
         <v>36</v>
       </c>
@@ -6700,7 +6715,7 @@
       </c>
       <c r="H59" s="4"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9">
       <c r="A60" t="s">
         <v>36</v>
       </c>
@@ -6721,7 +6736,7 @@
       </c>
       <c r="H60" s="4"/>
     </row>
-    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" s="7" customFormat="1">
       <c r="A61" t="s">
         <v>36</v>
       </c>
@@ -6746,7 +6761,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9">
       <c r="A62" t="s">
         <v>36</v>
       </c>
@@ -6770,7 +6785,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9">
       <c r="A63" t="s">
         <v>36</v>
       </c>
@@ -6791,7 +6806,7 @@
       </c>
       <c r="H63" s="4"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9">
       <c r="A64" t="s">
         <v>36</v>
       </c>
@@ -6812,7 +6827,7 @@
       </c>
       <c r="H64" s="4"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9">
       <c r="A65" t="s">
         <v>43</v>
       </c>
@@ -6838,7 +6853,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9">
       <c r="A66" t="s">
         <v>43</v>
       </c>
@@ -6859,7 +6874,7 @@
       </c>
       <c r="H66" s="4"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9">
       <c r="A67" t="s">
         <v>43</v>
       </c>
@@ -6883,7 +6898,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9">
       <c r="A68" t="s">
         <v>43</v>
       </c>
@@ -6904,7 +6919,7 @@
       </c>
       <c r="H68" s="4"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9">
       <c r="A69" t="s">
         <v>43</v>
       </c>
@@ -6928,7 +6943,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:9">
       <c r="A70" t="s">
         <v>43</v>
       </c>
@@ -6951,7 +6966,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9">
       <c r="A71" t="s">
         <v>43</v>
       </c>
@@ -6975,7 +6990,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:9">
       <c r="A72" t="s">
         <v>43</v>
       </c>
@@ -6996,7 +7011,7 @@
       </c>
       <c r="H72" s="4"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9">
       <c r="A73" t="s">
         <v>43</v>
       </c>
@@ -7017,7 +7032,7 @@
       </c>
       <c r="H73" s="4"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:9">
       <c r="A74" t="s">
         <v>43</v>
       </c>
@@ -7038,7 +7053,7 @@
       </c>
       <c r="H74" s="4"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:9">
       <c r="A75" t="s">
         <v>43</v>
       </c>
@@ -7062,7 +7077,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:9">
       <c r="A76" t="s">
         <v>43</v>
       </c>
@@ -7083,7 +7098,7 @@
       </c>
       <c r="H76" s="4"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:9">
       <c r="A77" t="s">
         <v>43</v>
       </c>
@@ -7104,7 +7119,7 @@
       </c>
       <c r="H77" s="4"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:9">
       <c r="A78" s="8" t="s">
         <v>43</v>
       </c>
@@ -7131,7 +7146,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:9">
       <c r="A79" s="8" t="s">
         <v>43</v>
       </c>
@@ -7156,7 +7171,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:9">
       <c r="A80" t="s">
         <v>69</v>
       </c>
@@ -7179,7 +7194,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9">
       <c r="A81" t="s">
         <v>69</v>
       </c>
@@ -7208,7 +7223,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9">
       <c r="A82" t="s">
         <v>170</v>
       </c>
@@ -7232,7 +7247,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9">
       <c r="A83" t="s">
         <v>170</v>
       </c>
@@ -7258,7 +7273,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9">
       <c r="A84" t="s">
         <v>170</v>
       </c>
@@ -7281,7 +7296,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9">
       <c r="A85" t="s">
         <v>170</v>
       </c>
@@ -7304,7 +7319,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9">
       <c r="A86" t="s">
         <v>170</v>
       </c>
@@ -7327,7 +7342,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9">
       <c r="A87" t="s">
         <v>139</v>
       </c>
@@ -7348,7 +7363,7 @@
       </c>
       <c r="H87" s="4"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9">
       <c r="A88" t="s">
         <v>139</v>
       </c>
@@ -7372,7 +7387,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9">
       <c r="A89" t="s">
         <v>139</v>
       </c>
@@ -7393,7 +7408,7 @@
       </c>
       <c r="H89" s="4"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9">
       <c r="A90" t="s">
         <v>139</v>
       </c>
@@ -7414,7 +7429,7 @@
       </c>
       <c r="H90" s="4"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:9">
       <c r="A91" t="s">
         <v>139</v>
       </c>
@@ -7435,7 +7450,7 @@
       </c>
       <c r="H91" s="4"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:9">
       <c r="A92" t="s">
         <v>139</v>
       </c>
@@ -7456,7 +7471,7 @@
       </c>
       <c r="H92" s="4"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:9">
       <c r="A93" t="s">
         <v>139</v>
       </c>
@@ -7477,7 +7492,7 @@
       </c>
       <c r="H93" s="4"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:9">
       <c r="A94" t="s">
         <v>139</v>
       </c>
@@ -7498,7 +7513,7 @@
       </c>
       <c r="H94" s="4"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:9">
       <c r="A95" t="s">
         <v>111</v>
       </c>
@@ -7521,7 +7536,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:9">
       <c r="A96" t="s">
         <v>111</v>
       </c>
@@ -7544,7 +7559,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="97" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9" s="8" customFormat="1">
       <c r="A97" t="s">
         <v>111</v>
       </c>
@@ -7569,7 +7584,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9">
       <c r="A98" t="s">
         <v>111</v>
       </c>
@@ -7592,7 +7607,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9">
       <c r="A99" t="s">
         <v>111</v>
       </c>
@@ -7615,7 +7630,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9">
       <c r="A100" t="s">
         <v>111</v>
       </c>
@@ -7639,7 +7654,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9">
       <c r="A101" t="s">
         <v>111</v>
       </c>
@@ -7663,7 +7678,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9" s="8" customFormat="1">
       <c r="A102" t="s">
         <v>111</v>
       </c>
@@ -7688,7 +7703,7 @@
       </c>
       <c r="I102"/>
     </row>
-    <row r="103" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9" ht="46.5">
       <c r="A103" s="8" t="s">
         <v>111</v>
       </c>
@@ -7710,14 +7725,14 @@
       <c r="G103" s="8" t="s">
         <v>1225</v>
       </c>
-      <c r="H103" s="65" t="s">
+      <c r="H103" s="63" t="s">
         <v>1276</v>
       </c>
       <c r="I103" s="8" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:9">
       <c r="A104" s="8" t="s">
         <v>111</v>
       </c>
@@ -7742,7 +7757,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9">
       <c r="A105" t="s">
         <v>111</v>
       </c>
@@ -7767,7 +7782,7 @@
       </c>
       <c r="I105" s="7"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9">
       <c r="A106" t="s">
         <v>111</v>
       </c>
@@ -7790,7 +7805,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:9">
       <c r="A107" t="s">
         <v>111</v>
       </c>
@@ -7813,7 +7828,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:9">
       <c r="A108" t="s">
         <v>111</v>
       </c>
@@ -7837,7 +7852,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:9">
       <c r="A109" t="s">
         <v>111</v>
       </c>
@@ -7863,7 +7878,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:9">
       <c r="A110" t="s">
         <v>111</v>
       </c>
@@ -7889,7 +7904,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:9">
       <c r="A111" t="s">
         <v>155</v>
       </c>
@@ -7912,7 +7927,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:9">
       <c r="A112" t="s">
         <v>96</v>
       </c>
@@ -7933,7 +7948,7 @@
       </c>
       <c r="H112" s="4"/>
     </row>
-    <row r="113" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:9" s="8" customFormat="1">
       <c r="A113" s="8" t="s">
         <v>96</v>
       </c>
@@ -7962,7 +7977,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:9">
       <c r="A114" t="s">
         <v>96</v>
       </c>
@@ -7986,7 +8001,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:9">
       <c r="A115" t="s">
         <v>96</v>
       </c>
@@ -8007,7 +8022,7 @@
       </c>
       <c r="H115" s="4"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:9">
       <c r="A116" t="s">
         <v>96</v>
       </c>
@@ -8028,7 +8043,7 @@
       </c>
       <c r="H116" s="4"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:9">
       <c r="A117" t="s">
         <v>96</v>
       </c>
@@ -8049,7 +8064,7 @@
       </c>
       <c r="H117" s="4"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:9">
       <c r="A118" t="s">
         <v>96</v>
       </c>
@@ -8070,7 +8085,7 @@
       </c>
       <c r="H118" s="4"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:9">
       <c r="A119" t="s">
         <v>357</v>
       </c>
@@ -8091,7 +8106,7 @@
       </c>
       <c r="H119" s="4"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:9">
       <c r="A120" t="s">
         <v>357</v>
       </c>
@@ -8114,7 +8129,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:9">
       <c r="A121" t="s">
         <v>357</v>
       </c>
@@ -8135,7 +8150,7 @@
       </c>
       <c r="H121" s="4"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:9">
       <c r="A122" t="s">
         <v>357</v>
       </c>
@@ -8158,7 +8173,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:9">
       <c r="A123" t="s">
         <v>509</v>
       </c>
@@ -8182,7 +8197,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:9">
       <c r="A124" t="s">
         <v>123</v>
       </c>
@@ -8203,7 +8218,7 @@
       </c>
       <c r="H124" s="4"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:9">
       <c r="A125" t="s">
         <v>262</v>
       </c>
@@ -8227,7 +8242,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:9">
       <c r="A126" t="s">
         <v>262</v>
       </c>
@@ -8248,7 +8263,7 @@
       </c>
       <c r="H126" s="4"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:9">
       <c r="A127" t="s">
         <v>204</v>
       </c>
@@ -8269,7 +8284,7 @@
       </c>
       <c r="H127" s="4"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:9">
       <c r="A128" t="s">
         <v>38</v>
       </c>
@@ -8293,7 +8308,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:9">
       <c r="A129" t="s">
         <v>38</v>
       </c>
@@ -8314,7 +8329,7 @@
       </c>
       <c r="H129" s="4"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:9">
       <c r="A130" t="s">
         <v>38</v>
       </c>
@@ -8338,7 +8353,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:9">
       <c r="A131" t="s">
         <v>38</v>
       </c>
@@ -8359,7 +8374,7 @@
       </c>
       <c r="H131" s="4"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:9">
       <c r="A132" t="s">
         <v>38</v>
       </c>
@@ -8380,7 +8395,7 @@
       </c>
       <c r="H132" s="4"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:9">
       <c r="A133" t="s">
         <v>38</v>
       </c>
@@ -8404,7 +8419,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:9">
       <c r="A134" t="s">
         <v>38</v>
       </c>
@@ -8428,7 +8443,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:9">
       <c r="A135" t="s">
         <v>38</v>
       </c>
@@ -8449,7 +8464,7 @@
       </c>
       <c r="H135" s="4"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:9">
       <c r="A136" t="s">
         <v>38</v>
       </c>
@@ -8478,7 +8493,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:9">
       <c r="A137" t="s">
         <v>38</v>
       </c>
@@ -8504,7 +8519,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:9">
       <c r="A138" t="s">
         <v>38</v>
       </c>
@@ -8528,7 +8543,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:9">
       <c r="A139" t="s">
         <v>38</v>
       </c>
@@ -8552,7 +8567,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:9">
       <c r="A140" t="s">
         <v>38</v>
       </c>
@@ -8576,7 +8591,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:9">
       <c r="A141" t="s">
         <v>38</v>
       </c>
@@ -8602,7 +8617,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:9">
       <c r="A142" t="s">
         <v>192</v>
       </c>
@@ -8625,7 +8640,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:9">
       <c r="A143" t="s">
         <v>521</v>
       </c>
@@ -8648,7 +8663,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:9">
       <c r="A144" t="s">
         <v>298</v>
       </c>
@@ -8671,7 +8686,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:9">
       <c r="A145" t="s">
         <v>298</v>
       </c>
@@ -8694,7 +8709,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:9">
       <c r="A146" t="s">
         <v>236</v>
       </c>
@@ -8718,7 +8733,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:9">
       <c r="A147" s="8" t="s">
         <v>236</v>
       </c>
@@ -8745,7 +8760,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:9">
       <c r="A148" s="8" t="s">
         <v>236</v>
       </c>
@@ -8770,7 +8785,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:9">
       <c r="A149" s="8" t="s">
         <v>236</v>
       </c>
@@ -8795,7 +8810,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:9">
       <c r="A150" t="s">
         <v>236</v>
       </c>
@@ -8819,7 +8834,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:9">
       <c r="A151" t="s">
         <v>236</v>
       </c>
@@ -8843,7 +8858,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:9">
       <c r="A152" s="8" t="s">
         <v>91</v>
       </c>
@@ -8868,7 +8883,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:9">
       <c r="A153" s="8" t="s">
         <v>91</v>
       </c>
@@ -8893,7 +8908,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:9">
       <c r="A154" t="s">
         <v>91</v>
       </c>
@@ -8917,7 +8932,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:9">
       <c r="A155" t="s">
         <v>91</v>
       </c>
@@ -8941,7 +8956,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:9">
       <c r="A156" t="s">
         <v>91</v>
       </c>
@@ -8965,7 +8980,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:9">
       <c r="A157" s="8" t="s">
         <v>91</v>
       </c>
@@ -8990,7 +9005,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:9">
       <c r="A158" s="8" t="s">
         <v>91</v>
       </c>
@@ -9015,7 +9030,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:9">
       <c r="A159" t="s">
         <v>91</v>
       </c>
@@ -9038,7 +9053,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:9">
       <c r="A160" t="s">
         <v>91</v>
       </c>
@@ -9059,7 +9074,7 @@
       </c>
       <c r="H160" s="4"/>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:9">
       <c r="A161" t="s">
         <v>91</v>
       </c>
@@ -9080,7 +9095,7 @@
       </c>
       <c r="H161" s="4"/>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:9">
       <c r="A162" s="8" t="s">
         <v>91</v>
       </c>
@@ -9107,7 +9122,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:9">
       <c r="A163" s="8" t="s">
         <v>91</v>
       </c>
@@ -9134,7 +9149,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:9">
       <c r="A164" t="s">
         <v>99</v>
       </c>
@@ -9155,7 +9170,7 @@
       </c>
       <c r="H164" s="4"/>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:9">
       <c r="A165" s="8" t="s">
         <v>99</v>
       </c>
@@ -9180,7 +9195,7 @@
       </c>
       <c r="I165" s="8"/>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:9">
       <c r="A166" t="s">
         <v>99</v>
       </c>
@@ -9206,7 +9221,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:9">
       <c r="A167" s="8" t="s">
         <v>99</v>
       </c>
@@ -9231,7 +9246,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:9">
       <c r="A168" s="8" t="s">
         <v>99</v>
       </c>
@@ -9258,7 +9273,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:9">
       <c r="A169" s="58" t="s">
         <v>99</v>
       </c>
@@ -9285,7 +9300,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:9">
       <c r="A170" s="58" t="s">
         <v>99</v>
       </c>
@@ -9312,7 +9327,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:9">
       <c r="A171" t="s">
         <v>99</v>
       </c>
@@ -9333,7 +9348,7 @@
       </c>
       <c r="H171" s="4"/>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:9">
       <c r="A172" t="s">
         <v>99</v>
       </c>
@@ -9356,7 +9371,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:9">
       <c r="A173" t="s">
         <v>51</v>
       </c>
@@ -9379,7 +9394,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:9">
       <c r="A174" t="s">
         <v>51</v>
       </c>
@@ -9403,7 +9418,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:9">
       <c r="A175" t="s">
         <v>51</v>
       </c>
@@ -9427,7 +9442,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:9">
       <c r="A176" t="s">
         <v>51</v>
       </c>
@@ -9451,7 +9466,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:9">
       <c r="A177" t="s">
         <v>51</v>
       </c>
@@ -9472,7 +9487,7 @@
       </c>
       <c r="H177" s="4"/>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:9">
       <c r="A178" t="s">
         <v>51</v>
       </c>
@@ -9496,7 +9511,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:9">
       <c r="A179" t="s">
         <v>51</v>
       </c>
@@ -9520,7 +9535,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:9">
       <c r="A180" t="s">
         <v>51</v>
       </c>
@@ -9541,7 +9556,7 @@
       </c>
       <c r="H180" s="4"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:9">
       <c r="A181" t="s">
         <v>150</v>
       </c>
@@ -9562,7 +9577,7 @@
       </c>
       <c r="H181" s="4"/>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:9">
       <c r="A182" t="s">
         <v>150</v>
       </c>
@@ -9583,7 +9598,7 @@
       </c>
       <c r="H182" s="4"/>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:9">
       <c r="A183" t="s">
         <v>113</v>
       </c>
@@ -9607,7 +9622,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:9">
       <c r="A184" t="s">
         <v>113</v>
       </c>
@@ -9628,7 +9643,7 @@
       </c>
       <c r="H184" s="4"/>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:9">
       <c r="A185" t="s">
         <v>113</v>
       </c>
@@ -9651,7 +9666,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:9">
       <c r="A186" t="s">
         <v>113</v>
       </c>
@@ -9672,7 +9687,7 @@
       </c>
       <c r="H186" s="4"/>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:9">
       <c r="A187" t="s">
         <v>113</v>
       </c>
@@ -9693,7 +9708,7 @@
       </c>
       <c r="H187" s="4"/>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:9">
       <c r="A188" t="s">
         <v>113</v>
       </c>
@@ -9716,7 +9731,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:9">
       <c r="A189" t="s">
         <v>113</v>
       </c>
@@ -9737,7 +9752,7 @@
       </c>
       <c r="H189" s="4"/>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:9">
       <c r="A190" t="s">
         <v>13</v>
       </c>
@@ -9758,7 +9773,7 @@
       </c>
       <c r="H190" s="4"/>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:9">
       <c r="A191" t="s">
         <v>13</v>
       </c>
@@ -9779,7 +9794,7 @@
       </c>
       <c r="H191" s="4"/>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:9">
       <c r="A192" t="s">
         <v>13</v>
       </c>
@@ -9803,7 +9818,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:9">
       <c r="A193" t="s">
         <v>13</v>
       </c>
@@ -9829,7 +9844,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:9">
       <c r="A194" t="s">
         <v>13</v>
       </c>
@@ -9852,7 +9867,7 @@
       <c r="H194" s="10"/>
       <c r="I194" s="8"/>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:9">
       <c r="A195" t="s">
         <v>13</v>
       </c>
@@ -9879,7 +9894,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:9">
       <c r="A196" t="s">
         <v>13</v>
       </c>
@@ -9903,7 +9918,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:9">
       <c r="A197" t="s">
         <v>13</v>
       </c>
@@ -9924,7 +9939,7 @@
       </c>
       <c r="H197" s="4"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:9">
       <c r="A198" t="s">
         <v>13</v>
       </c>
@@ -9945,7 +9960,7 @@
       </c>
       <c r="H198" s="4"/>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:9">
       <c r="A199" t="s">
         <v>13</v>
       </c>
@@ -9968,7 +9983,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:9">
       <c r="A200" t="s">
         <v>13</v>
       </c>
@@ -9992,7 +10007,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:9">
       <c r="A201" t="s">
         <v>13</v>
       </c>
@@ -10013,7 +10028,7 @@
       </c>
       <c r="H201" s="4"/>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:9">
       <c r="A202" t="s">
         <v>13</v>
       </c>
@@ -10037,7 +10052,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:9">
       <c r="A203" t="s">
         <v>13</v>
       </c>
@@ -10058,7 +10073,7 @@
       </c>
       <c r="H203" s="4"/>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:9">
       <c r="A204" t="s">
         <v>13</v>
       </c>
@@ -10082,7 +10097,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:9">
       <c r="A205" t="s">
         <v>13</v>
       </c>
@@ -10105,7 +10120,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:9">
       <c r="A206" t="s">
         <v>13</v>
       </c>
@@ -10126,7 +10141,7 @@
       </c>
       <c r="H206" s="4"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:9">
       <c r="A207" t="s">
         <v>13</v>
       </c>
@@ -10150,7 +10165,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="208" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:9" s="8" customFormat="1">
       <c r="A208" t="s">
         <v>13</v>
       </c>
@@ -10175,7 +10190,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:9">
       <c r="A209" t="s">
         <v>13</v>
       </c>
@@ -10196,7 +10211,7 @@
       </c>
       <c r="H209" s="4"/>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:9">
       <c r="A210" t="s">
         <v>13</v>
       </c>
@@ -10220,7 +10235,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:9">
       <c r="A211" t="s">
         <v>13</v>
       </c>
@@ -10241,7 +10256,7 @@
       </c>
       <c r="H211" s="4"/>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:9">
       <c r="A212" t="s">
         <v>13</v>
       </c>
@@ -10262,7 +10277,7 @@
       </c>
       <c r="H212" s="4"/>
     </row>
-    <row r="213" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:9" s="12" customFormat="1">
       <c r="A213" t="s">
         <v>13</v>
       </c>
@@ -10287,7 +10302,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:9">
       <c r="A214" t="s">
         <v>13</v>
       </c>
@@ -10308,7 +10323,7 @@
       </c>
       <c r="H214" s="4"/>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:9">
       <c r="A215" t="s">
         <v>13</v>
       </c>
@@ -10332,7 +10347,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:9">
       <c r="A216" t="s">
         <v>13</v>
       </c>
@@ -10353,7 +10368,7 @@
       </c>
       <c r="H216" s="4"/>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:9">
       <c r="A217" t="s">
         <v>13</v>
       </c>
@@ -10377,7 +10392,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:9">
       <c r="A218" s="8" t="s">
         <v>13</v>
       </c>
@@ -10402,7 +10417,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:9">
       <c r="A219" s="8" t="s">
         <v>13</v>
       </c>
@@ -10429,7 +10444,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:9">
       <c r="A220" t="s">
         <v>13</v>
       </c>
@@ -10453,7 +10468,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="221" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:9" s="5" customFormat="1">
       <c r="A221" t="s">
         <v>13</v>
       </c>
@@ -10478,7 +10493,7 @@
       </c>
       <c r="I221"/>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:9">
       <c r="A222" t="s">
         <v>13</v>
       </c>
@@ -10499,7 +10514,7 @@
       </c>
       <c r="H222" s="4"/>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:9">
       <c r="A223" t="s">
         <v>13</v>
       </c>
@@ -10520,7 +10535,7 @@
       </c>
       <c r="H223" s="4"/>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:9">
       <c r="A224" t="s">
         <v>13</v>
       </c>
@@ -10544,7 +10559,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="225" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:9" s="8" customFormat="1">
       <c r="A225" t="s">
         <v>13</v>
       </c>
@@ -10567,7 +10582,7 @@
       <c r="H225" s="4"/>
       <c r="I225"/>
     </row>
-    <row r="226" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:9" s="8" customFormat="1">
       <c r="A226" s="8" t="s">
         <v>13</v>
       </c>
@@ -10597,7 +10612,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:9">
       <c r="A227" s="8" t="s">
         <v>13</v>
       </c>
@@ -10622,7 +10637,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:9">
       <c r="A228" t="s">
         <v>242</v>
       </c>
@@ -10643,7 +10658,7 @@
       </c>
       <c r="H228" s="4"/>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:9">
       <c r="A229" t="s">
         <v>242</v>
       </c>
@@ -10667,7 +10682,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:9">
       <c r="A230" t="s">
         <v>40</v>
       </c>
@@ -10688,7 +10703,7 @@
       </c>
       <c r="H230" s="4"/>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:9">
       <c r="A231" t="s">
         <v>40</v>
       </c>
@@ -10709,7 +10724,7 @@
       </c>
       <c r="H231" s="4"/>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:9">
       <c r="A232" t="s">
         <v>40</v>
       </c>
@@ -10732,7 +10747,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:9">
       <c r="A233" t="s">
         <v>40</v>
       </c>
@@ -10753,7 +10768,7 @@
       </c>
       <c r="H233" s="4"/>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:9">
       <c r="A234" s="8" t="s">
         <v>40</v>
       </c>
@@ -10780,7 +10795,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:9">
       <c r="A235" s="8" t="s">
         <v>40</v>
       </c>
@@ -10809,7 +10824,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:9">
       <c r="A236" t="s">
         <v>40</v>
       </c>
@@ -10831,7 +10846,7 @@
       <c r="G236" s="8"/>
       <c r="H236" s="4"/>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:9">
       <c r="A237" t="s">
         <v>40</v>
       </c>
@@ -10855,7 +10870,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:9">
       <c r="A238" t="s">
         <v>40</v>
       </c>
@@ -10879,7 +10894,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:9">
       <c r="A239" t="s">
         <v>40</v>
       </c>
@@ -10900,7 +10915,7 @@
       </c>
       <c r="H239" s="4"/>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:9">
       <c r="A240" t="s">
         <v>56</v>
       </c>
@@ -10924,7 +10939,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:9">
       <c r="A241" t="s">
         <v>56</v>
       </c>
@@ -10948,7 +10963,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:9">
       <c r="A242" t="s">
         <v>56</v>
       </c>
@@ -10972,7 +10987,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:9">
       <c r="A243" t="s">
         <v>56</v>
       </c>
@@ -10993,7 +11008,7 @@
       </c>
       <c r="H243" s="4"/>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:9">
       <c r="A244" t="s">
         <v>56</v>
       </c>
@@ -11017,7 +11032,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:9">
       <c r="A245" t="s">
         <v>56</v>
       </c>
@@ -11038,7 +11053,7 @@
       </c>
       <c r="H245" s="4"/>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:9">
       <c r="A246" t="s">
         <v>56</v>
       </c>
@@ -11062,7 +11077,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:9">
       <c r="A247" t="s">
         <v>411</v>
       </c>
@@ -11086,7 +11101,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:9">
       <c r="A248" t="s">
         <v>48</v>
       </c>
@@ -11110,7 +11125,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:9">
       <c r="A249" t="s">
         <v>48</v>
       </c>
@@ -11139,7 +11154,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:9">
       <c r="A250" t="s">
         <v>48</v>
       </c>
@@ -11163,7 +11178,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:9">
       <c r="A251" t="s">
         <v>48</v>
       </c>
@@ -11184,7 +11199,7 @@
       </c>
       <c r="H251" s="4"/>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:9">
       <c r="A252" t="s">
         <v>48</v>
       </c>
@@ -11208,7 +11223,7 @@
       </c>
       <c r="H252" s="4"/>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:9">
       <c r="A253" t="s">
         <v>48</v>
       </c>
@@ -11229,7 +11244,7 @@
       </c>
       <c r="H253" s="4"/>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:9">
       <c r="A254" t="s">
         <v>48</v>
       </c>
@@ -11250,7 +11265,7 @@
       </c>
       <c r="H254" s="4"/>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:9">
       <c r="A255" t="s">
         <v>48</v>
       </c>
@@ -11271,7 +11286,7 @@
       </c>
       <c r="H255" s="4"/>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:9">
       <c r="A256" t="s">
         <v>48</v>
       </c>
@@ -11292,7 +11307,7 @@
       </c>
       <c r="H256" s="4"/>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:9">
       <c r="A257" t="s">
         <v>209</v>
       </c>
@@ -11316,7 +11331,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:9">
       <c r="A258" t="s">
         <v>209</v>
       </c>
@@ -11340,7 +11355,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:9">
       <c r="A259" t="s">
         <v>209</v>
       </c>
@@ -11364,7 +11379,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:9">
       <c r="A260" t="s">
         <v>209</v>
       </c>
@@ -11388,7 +11403,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:9">
       <c r="A261" t="s">
         <v>104</v>
       </c>
@@ -11411,7 +11426,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:9">
       <c r="A262" t="s">
         <v>104</v>
       </c>
@@ -11435,7 +11450,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:9">
       <c r="A263" t="s">
         <v>104</v>
       </c>
@@ -11456,7 +11471,7 @@
       </c>
       <c r="H263" s="4"/>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:9">
       <c r="A264" t="s">
         <v>104</v>
       </c>
@@ -11477,7 +11492,7 @@
       </c>
       <c r="H264" s="4"/>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:9">
       <c r="A265" t="s">
         <v>104</v>
       </c>
@@ -11501,7 +11516,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:9">
       <c r="A266" t="s">
         <v>104</v>
       </c>
@@ -11522,7 +11537,7 @@
       </c>
       <c r="H266" s="4"/>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:9">
       <c r="A267" t="s">
         <v>104</v>
       </c>
@@ -11543,7 +11558,7 @@
       </c>
       <c r="H267" s="4"/>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:9">
       <c r="A268" t="s">
         <v>104</v>
       </c>
@@ -11566,7 +11581,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:9">
       <c r="A269" t="s">
         <v>104</v>
       </c>
@@ -11589,7 +11604,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:9">
       <c r="A270" t="s">
         <v>104</v>
       </c>
@@ -11612,7 +11627,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:9">
       <c r="A271" s="7" t="s">
         <v>30</v>
       </c>
@@ -11636,7 +11651,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:9">
       <c r="A272" t="s">
         <v>30</v>
       </c>
@@ -11657,7 +11672,7 @@
       </c>
       <c r="H272" s="4"/>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:9">
       <c r="A273" t="s">
         <v>30</v>
       </c>
@@ -11678,7 +11693,7 @@
       </c>
       <c r="H273" s="4"/>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:9">
       <c r="A274" t="s">
         <v>30</v>
       </c>
@@ -11699,7 +11714,7 @@
       </c>
       <c r="H274" s="4"/>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:9">
       <c r="A275" t="s">
         <v>30</v>
       </c>
@@ -11722,7 +11737,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="276" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:9" s="8" customFormat="1">
       <c r="A276" t="s">
         <v>30</v>
       </c>
@@ -11747,7 +11762,7 @@
       </c>
       <c r="I276"/>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:9">
       <c r="A277" t="s">
         <v>30</v>
       </c>
@@ -11773,7 +11788,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:9">
       <c r="A278" t="s">
         <v>30</v>
       </c>
@@ -11799,7 +11814,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:9">
       <c r="A279" t="s">
         <v>30</v>
       </c>
@@ -11820,7 +11835,7 @@
       </c>
       <c r="H279" s="4"/>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:9">
       <c r="A280" t="s">
         <v>30</v>
       </c>
@@ -11844,7 +11859,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:9">
       <c r="A281" t="s">
         <v>30</v>
       </c>
@@ -11868,7 +11883,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:9">
       <c r="A282" t="s">
         <v>30</v>
       </c>
@@ -11894,7 +11909,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:9">
       <c r="A283" t="s">
         <v>30</v>
       </c>
@@ -11918,7 +11933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:9">
       <c r="A284" t="s">
         <v>30</v>
       </c>
@@ -11944,7 +11959,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:9">
       <c r="A285" t="s">
         <v>30</v>
       </c>
@@ -11967,7 +11982,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:9">
       <c r="A286" t="s">
         <v>30</v>
       </c>
@@ -11990,7 +12005,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:9">
       <c r="A287" t="s">
         <v>30</v>
       </c>
@@ -12013,7 +12028,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:9">
       <c r="A288" t="s">
         <v>27</v>
       </c>
@@ -12037,7 +12052,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:9">
       <c r="A289" t="s">
         <v>27</v>
       </c>
@@ -12061,7 +12076,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:9">
       <c r="A290" t="s">
         <v>87</v>
       </c>
@@ -12087,7 +12102,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:9">
       <c r="A291" t="s">
         <v>87</v>
       </c>
@@ -12113,7 +12128,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:9">
       <c r="A292" t="s">
         <v>87</v>
       </c>
@@ -12136,7 +12151,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:9">
       <c r="A293" s="5" t="s">
         <v>9</v>
       </c>
@@ -12161,7 +12176,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:9">
       <c r="A294" t="s">
         <v>87</v>
       </c>
@@ -12184,7 +12199,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:9">
       <c r="A295" t="s">
         <v>87</v>
       </c>
@@ -12207,7 +12222,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:9">
       <c r="A296" t="s">
         <v>87</v>
       </c>
@@ -12230,7 +12245,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:9">
       <c r="A297" t="s">
         <v>87</v>
       </c>
@@ -12253,7 +12268,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:9">
       <c r="A298" t="s">
         <v>16</v>
       </c>
@@ -12276,7 +12291,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:9">
       <c r="A299" t="s">
         <v>16</v>
       </c>
@@ -12299,7 +12314,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:9">
       <c r="A300" t="s">
         <v>16</v>
       </c>
@@ -12322,7 +12337,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:9">
       <c r="A301" s="8" t="s">
         <v>16</v>
       </c>
@@ -12349,7 +12364,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:9">
       <c r="A302" s="8" t="s">
         <v>16</v>
       </c>
@@ -12376,7 +12391,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:9">
       <c r="A303" t="s">
         <v>16</v>
       </c>
@@ -12399,7 +12414,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:9">
       <c r="A304" t="s">
         <v>16</v>
       </c>
@@ -12422,7 +12437,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:9">
       <c r="A305" t="s">
         <v>16</v>
       </c>
@@ -12445,7 +12460,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:9">
       <c r="A306" s="8" t="s">
         <v>16</v>
       </c>
@@ -12474,7 +12489,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:9">
       <c r="A307" t="s">
         <v>16</v>
       </c>
@@ -12498,7 +12513,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:9">
       <c r="A308" t="s">
         <v>16</v>
       </c>
@@ -12522,7 +12537,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:9">
       <c r="A309" t="s">
         <v>16</v>
       </c>
@@ -12546,7 +12561,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:9">
       <c r="A310" t="s">
         <v>16</v>
       </c>
@@ -12570,7 +12585,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:9">
       <c r="A311" s="5" t="s">
         <v>16</v>
       </c>
@@ -12593,7 +12608,7 @@
       <c r="H311" s="55"/>
       <c r="I311" s="5"/>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:9">
       <c r="A312" t="s">
         <v>16</v>
       </c>
@@ -12617,7 +12632,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:9">
       <c r="A313" t="s">
         <v>16</v>
       </c>
@@ -12640,7 +12655,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:9">
       <c r="A314" t="s">
         <v>16</v>
       </c>
@@ -12663,7 +12678,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:9">
       <c r="A315" t="s">
         <v>16</v>
       </c>
@@ -12686,7 +12701,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:9">
       <c r="A316" t="s">
         <v>16</v>
       </c>
@@ -12712,7 +12727,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:9">
       <c r="A317" t="s">
         <v>16</v>
       </c>
@@ -12738,7 +12753,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:9">
       <c r="A318" t="s">
         <v>16</v>
       </c>
@@ -12762,7 +12777,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="319" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:9" s="8" customFormat="1">
       <c r="A319" t="s">
         <v>16</v>
       </c>
@@ -12787,7 +12802,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:9">
       <c r="A320" t="s">
         <v>16</v>
       </c>
@@ -12813,7 +12828,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:9">
       <c r="A321" t="s">
         <v>16</v>
       </c>
@@ -12837,7 +12852,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:9">
       <c r="A322" t="s">
         <v>16</v>
       </c>
@@ -12861,7 +12876,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:9">
       <c r="A323" t="s">
         <v>16</v>
       </c>
@@ -12884,7 +12899,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:9">
       <c r="A324" t="s">
         <v>16</v>
       </c>
@@ -12907,7 +12922,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:9">
       <c r="A325" t="s">
         <v>16</v>
       </c>
@@ -12931,7 +12946,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:9">
       <c r="A326" t="s">
         <v>16</v>
       </c>
@@ -12955,7 +12970,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:9">
       <c r="A327" s="8" t="s">
         <v>16</v>
       </c>
@@ -12982,7 +12997,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:9">
       <c r="A328" s="8" t="s">
         <v>16</v>
       </c>
@@ -13009,7 +13024,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:9">
       <c r="A329" t="s">
         <v>16</v>
       </c>
@@ -13032,7 +13047,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:9">
       <c r="A330" t="s">
         <v>16</v>
       </c>
@@ -13053,7 +13068,7 @@
       </c>
       <c r="H330" s="4"/>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:9">
       <c r="A331" t="s">
         <v>16</v>
       </c>
@@ -13074,7 +13089,7 @@
       </c>
       <c r="H331" s="4"/>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:9">
       <c r="A332" t="s">
         <v>16</v>
       </c>
@@ -13098,7 +13113,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:9">
       <c r="A333" s="8" t="s">
         <v>16</v>
       </c>
@@ -13125,7 +13140,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:9">
       <c r="A334" t="s">
         <v>16</v>
       </c>
@@ -13149,7 +13164,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:9">
       <c r="A335" t="s">
         <v>16</v>
       </c>
@@ -13175,7 +13190,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:9">
       <c r="A336" t="s">
         <v>16</v>
       </c>
@@ -13199,7 +13214,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:9">
       <c r="A337" t="s">
         <v>16</v>
       </c>
@@ -13222,7 +13237,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:9">
       <c r="A338" t="s">
         <v>176</v>
       </c>
@@ -13246,7 +13261,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:9">
       <c r="A339" t="s">
         <v>176</v>
       </c>
@@ -13272,7 +13287,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:9">
       <c r="A340" t="s">
         <v>176</v>
       </c>
@@ -13293,7 +13308,7 @@
       </c>
       <c r="H340" s="4"/>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:9">
       <c r="A341" t="s">
         <v>176</v>
       </c>
@@ -13316,7 +13331,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:9">
       <c r="A342" t="s">
         <v>176</v>
       </c>
@@ -13340,7 +13355,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:9">
       <c r="A343" t="s">
         <v>176</v>
       </c>
@@ -13364,7 +13379,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:9">
       <c r="A344" t="s">
         <v>176</v>
       </c>
@@ -13385,7 +13400,7 @@
       </c>
       <c r="H344" s="4"/>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:9">
       <c r="A345" t="s">
         <v>22</v>
       </c>
@@ -13406,7 +13421,7 @@
       </c>
       <c r="H345" s="4"/>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:9">
       <c r="A346" t="s">
         <v>22</v>
       </c>
@@ -13430,7 +13445,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:9">
       <c r="A347" t="s">
         <v>22</v>
       </c>
@@ -13451,7 +13466,7 @@
       </c>
       <c r="H347" s="4"/>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:9">
       <c r="A348" t="s">
         <v>22</v>
       </c>
@@ -13472,7 +13487,7 @@
       </c>
       <c r="H348" s="4"/>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:9">
       <c r="A349" t="s">
         <v>22</v>
       </c>
@@ -13493,7 +13508,7 @@
       </c>
       <c r="H349" s="4"/>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:9">
       <c r="A350" t="s">
         <v>22</v>
       </c>
@@ -13514,7 +13529,7 @@
       </c>
       <c r="H350" s="4"/>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:9">
       <c r="A351" t="s">
         <v>22</v>
       </c>
@@ -13538,7 +13553,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:9">
       <c r="A352" t="s">
         <v>22</v>
       </c>
@@ -13562,7 +13577,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:9">
       <c r="A353" t="s">
         <v>22</v>
       </c>
@@ -13583,7 +13598,7 @@
       </c>
       <c r="H353" s="4"/>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:9">
       <c r="A354" t="s">
         <v>22</v>
       </c>
@@ -13604,7 +13619,7 @@
       </c>
       <c r="H354" s="4"/>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:9">
       <c r="A355" t="s">
         <v>22</v>
       </c>
@@ -13628,7 +13643,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:9">
       <c r="A356" t="s">
         <v>22</v>
       </c>
@@ -13649,7 +13664,7 @@
       </c>
       <c r="H356" s="4"/>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:9">
       <c r="A357" t="s">
         <v>22</v>
       </c>
@@ -13670,7 +13685,7 @@
       </c>
       <c r="H357" s="4"/>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:9">
       <c r="A358" t="s">
         <v>22</v>
       </c>
@@ -13691,7 +13706,7 @@
       </c>
       <c r="H358" s="4"/>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:9">
       <c r="A359" t="s">
         <v>22</v>
       </c>
@@ -13712,7 +13727,7 @@
       </c>
       <c r="H359" s="4"/>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:9">
       <c r="A360" t="s">
         <v>22</v>
       </c>
@@ -13735,7 +13750,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:9">
       <c r="A361" t="s">
         <v>22</v>
       </c>
@@ -13761,7 +13776,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:9">
       <c r="A362" s="5" t="s">
         <v>22</v>
       </c>
@@ -13782,7 +13797,7 @@
       </c>
       <c r="H362" s="4"/>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:9">
       <c r="A363" t="s">
         <v>22</v>
       </c>
@@ -13803,7 +13818,7 @@
       </c>
       <c r="H363" s="4"/>
     </row>
-    <row r="364" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:9" s="8" customFormat="1">
       <c r="A364" t="s">
         <v>22</v>
       </c>
@@ -13828,7 +13843,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="365" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:9" s="8" customFormat="1">
       <c r="A365" t="s">
         <v>22</v>
       </c>
@@ -13855,7 +13870,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:9">
       <c r="A366" t="s">
         <v>22</v>
       </c>
@@ -13881,7 +13896,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:9">
       <c r="A367" t="s">
         <v>22</v>
       </c>
@@ -13904,7 +13919,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:9">
       <c r="A368" t="s">
         <v>283</v>
       </c>
@@ -13928,7 +13943,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:9">
       <c r="A369" t="s">
         <v>283</v>
       </c>
@@ -13949,7 +13964,7 @@
       </c>
       <c r="H369" s="4"/>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:9">
       <c r="A370" t="s">
         <v>338</v>
       </c>
@@ -13973,7 +13988,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:9">
       <c r="A371" t="s">
         <v>230</v>
       </c>
@@ -13997,7 +14012,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:9">
       <c r="A372" t="s">
         <v>230</v>
       </c>
@@ -14021,7 +14036,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:9">
       <c r="A373" t="s">
         <v>60</v>
       </c>
@@ -14042,7 +14057,7 @@
       </c>
       <c r="H373" s="4"/>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:9">
       <c r="A374" t="s">
         <v>60</v>
       </c>
@@ -14069,7 +14084,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:9">
       <c r="A375" t="s">
         <v>60</v>
       </c>
@@ -14090,7 +14105,7 @@
       </c>
       <c r="H375" s="4"/>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:9">
       <c r="A376" t="s">
         <v>60</v>
       </c>
@@ -14111,7 +14126,7 @@
       </c>
       <c r="H376" s="4"/>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:9">
       <c r="A377" t="s">
         <v>60</v>
       </c>
@@ -14132,7 +14147,7 @@
       </c>
       <c r="H377" s="4"/>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:9">
       <c r="A378" t="s">
         <v>60</v>
       </c>
@@ -14153,7 +14168,7 @@
       </c>
       <c r="H378" s="4"/>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:9">
       <c r="A379" t="s">
         <v>516</v>
       </c>
@@ -14177,7 +14192,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:9">
       <c r="A380" s="8" t="s">
         <v>173</v>
       </c>
@@ -14204,7 +14219,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:9">
       <c r="A381" s="8" t="s">
         <v>173</v>
       </c>
@@ -14231,7 +14246,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:9">
       <c r="A382" t="s">
         <v>173</v>
       </c>
@@ -14252,7 +14267,7 @@
       </c>
       <c r="H382" s="4"/>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:9">
       <c r="A383" t="s">
         <v>173</v>
       </c>
@@ -14276,7 +14291,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:9">
       <c r="A384" t="s">
         <v>173</v>
       </c>
@@ -14300,7 +14315,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:9">
       <c r="A385" t="s">
         <v>173</v>
       </c>
@@ -14323,7 +14338,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:9">
       <c r="A386" t="s">
         <v>9</v>
       </c>
@@ -14347,7 +14362,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:9">
       <c r="A387" t="s">
         <v>9</v>
       </c>
@@ -14371,7 +14386,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:9">
       <c r="A388" t="s">
         <v>9</v>
       </c>
@@ -14392,7 +14407,7 @@
       </c>
       <c r="H388" s="4"/>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:9">
       <c r="A389" t="s">
         <v>9</v>
       </c>
@@ -14416,7 +14431,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:9">
       <c r="A390" t="s">
         <v>9</v>
       </c>
@@ -14437,7 +14452,7 @@
       </c>
       <c r="H390" s="4"/>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:9">
       <c r="A391" t="s">
         <v>9</v>
       </c>
@@ -14460,7 +14475,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:9">
       <c r="A392" t="s">
         <v>9</v>
       </c>
@@ -14486,7 +14501,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:9">
       <c r="A393" t="s">
         <v>9</v>
       </c>
@@ -14507,7 +14522,7 @@
       </c>
       <c r="H393" s="4"/>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:9">
       <c r="A394" t="s">
         <v>9</v>
       </c>
@@ -14531,7 +14546,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:9">
       <c r="A395" t="s">
         <v>9</v>
       </c>
@@ -14555,7 +14570,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:9">
       <c r="A396" t="s">
         <v>9</v>
       </c>
@@ -14578,7 +14593,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:9">
       <c r="A397" t="s">
         <v>9</v>
       </c>
@@ -14599,7 +14614,7 @@
       </c>
       <c r="H397" s="4"/>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:9">
       <c r="A398" t="s">
         <v>9</v>
       </c>
@@ -14620,7 +14635,7 @@
       </c>
       <c r="H398" s="4"/>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:9">
       <c r="A399" t="s">
         <v>9</v>
       </c>
@@ -14644,7 +14659,7 @@
       </c>
       <c r="H399" s="4"/>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:9">
       <c r="A400" t="s">
         <v>9</v>
       </c>
@@ -14665,7 +14680,7 @@
       </c>
       <c r="H400" s="4"/>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:9">
       <c r="A401" t="s">
         <v>9</v>
       </c>
@@ -14688,7 +14703,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:9">
       <c r="A402" t="s">
         <v>9</v>
       </c>
@@ -14712,7 +14727,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:9">
       <c r="A403" t="s">
         <v>9</v>
       </c>
@@ -14733,7 +14748,7 @@
       </c>
       <c r="H403" s="4"/>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:9">
       <c r="A404" t="s">
         <v>9</v>
       </c>
@@ -14754,7 +14769,7 @@
       </c>
       <c r="H404" s="4"/>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:9">
       <c r="A405" t="s">
         <v>9</v>
       </c>
@@ -14775,7 +14790,7 @@
       </c>
       <c r="H405" s="4"/>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:9">
       <c r="A406" t="s">
         <v>9</v>
       </c>
@@ -14799,7 +14814,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:9">
       <c r="A407" t="s">
         <v>9</v>
       </c>
@@ -14820,7 +14835,7 @@
       </c>
       <c r="H407" s="4"/>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:9">
       <c r="A408" t="s">
         <v>9</v>
       </c>
@@ -14841,7 +14856,7 @@
       </c>
       <c r="H408" s="4"/>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:9">
       <c r="A409" t="s">
         <v>9</v>
       </c>
@@ -14865,7 +14880,7 @@
       </c>
       <c r="I409" s="8"/>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:9">
       <c r="A410" t="s">
         <v>65</v>
       </c>
@@ -14889,7 +14904,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:9">
       <c r="A411" t="s">
         <v>65</v>
       </c>
@@ -14913,7 +14928,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:9">
       <c r="A412" t="s">
         <v>65</v>
       </c>
@@ -14937,7 +14952,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:9">
       <c r="A413" t="s">
         <v>65</v>
       </c>
@@ -14961,7 +14976,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:9">
       <c r="A414" t="s">
         <v>65</v>
       </c>
@@ -14982,7 +14997,7 @@
       </c>
       <c r="H414" s="4"/>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:9">
       <c r="A415" t="s">
         <v>34</v>
       </c>
@@ -15006,7 +15021,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:9">
       <c r="A416" t="s">
         <v>34</v>
       </c>
@@ -15027,7 +15042,7 @@
       </c>
       <c r="H416" s="4"/>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:9">
       <c r="A417" t="s">
         <v>34</v>
       </c>
@@ -15051,7 +15066,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:9">
       <c r="A418" t="s">
         <v>34</v>
       </c>
@@ -15072,7 +15087,7 @@
       </c>
       <c r="H418" s="4"/>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:9">
       <c r="A419" t="s">
         <v>34</v>
       </c>
@@ -15096,7 +15111,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:9">
       <c r="A420" t="s">
         <v>34</v>
       </c>
@@ -15120,7 +15135,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:9">
       <c r="A421" t="s">
         <v>34</v>
       </c>
@@ -15144,7 +15159,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:9">
       <c r="A422" t="s">
         <v>34</v>
       </c>
@@ -15167,7 +15182,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:9">
       <c r="A423" t="s">
         <v>34</v>
       </c>
@@ -15188,7 +15203,7 @@
       </c>
       <c r="H423" s="4"/>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:9">
       <c r="A424" t="s">
         <v>34</v>
       </c>
@@ -15209,7 +15224,7 @@
       </c>
       <c r="H424" s="4"/>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:9">
       <c r="A425" t="s">
         <v>34</v>
       </c>
@@ -15230,7 +15245,7 @@
       </c>
       <c r="H425" s="4"/>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:9">
       <c r="A426" t="s">
         <v>228</v>
       </c>
@@ -15251,7 +15266,7 @@
       </c>
       <c r="H426" s="4"/>
     </row>
-    <row r="427" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:9" s="8" customFormat="1">
       <c r="A427" t="s">
         <v>115</v>
       </c>
@@ -15276,7 +15291,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:9">
       <c r="A428" t="s">
         <v>115</v>
       </c>
@@ -15297,7 +15312,7 @@
       </c>
       <c r="H428" s="4"/>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:9">
       <c r="A429" t="s">
         <v>381</v>
       </c>
@@ -15321,7 +15336,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:9">
       <c r="A430" t="s">
         <v>24</v>
       </c>
@@ -15347,7 +15362,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:9">
       <c r="A431" t="s">
         <v>24</v>
       </c>
@@ -15368,7 +15383,7 @@
       </c>
       <c r="H431" s="4"/>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:9">
       <c r="A432" t="s">
         <v>58</v>
       </c>
@@ -15392,7 +15407,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:9">
       <c r="A433" t="s">
         <v>58</v>
       </c>
@@ -15416,7 +15431,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:9">
       <c r="A434" t="s">
         <v>58</v>
       </c>
@@ -15440,7 +15455,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:9">
       <c r="A435" t="s">
         <v>58</v>
       </c>
@@ -15461,7 +15476,7 @@
       </c>
       <c r="H435" s="4"/>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:9">
       <c r="A436" t="s">
         <v>58</v>
       </c>
@@ -15482,7 +15497,7 @@
       </c>
       <c r="H436" s="4"/>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:9">
       <c r="A437" t="s">
         <v>58</v>
       </c>
@@ -15506,7 +15521,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:9">
       <c r="A438" t="s">
         <v>58</v>
       </c>
@@ -15527,7 +15542,7 @@
       </c>
       <c r="H438" s="4"/>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:9">
       <c r="A439" t="s">
         <v>87</v>
       </c>
@@ -15537,28 +15552,28 @@
       <c r="E439" s="3"/>
       <c r="H439" s="4"/>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:9">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
       <c r="D442" s="13"/>
       <c r="E442" s="13"/>
     </row>
-    <row r="443" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:9" s="14" customFormat="1">
       <c r="A443" s="15"/>
       <c r="E443" s="16"/>
       <c r="H443" s="17"/>
     </row>
-    <row r="444" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:9" s="14" customFormat="1">
       <c r="A444" s="15"/>
       <c r="E444" s="16"/>
       <c r="H444" s="17"/>
     </row>
-    <row r="445" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:9" s="14" customFormat="1">
       <c r="E445" s="16"/>
       <c r="H445" s="17"/>
     </row>
-    <row r="446" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:9" s="14" customFormat="1">
       <c r="A446" s="15"/>
       <c r="B446" s="15"/>
       <c r="C446" s="15"/>
@@ -15575,29 +15590,29 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G90"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="82" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="61" t="s">
+    <row r="1" spans="1:7" ht="82" customHeight="1" thickBot="1">
+      <c r="A1" s="64" t="s">
         <v>560</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
       <c r="G1" s="8" t="s">
         <v>1261</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="16" thickBot="1">
       <c r="A2" s="35" t="s">
         <v>0</v>
       </c>
@@ -15617,7 +15632,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16" thickBot="1">
       <c r="A3" s="38" t="s">
         <v>126</v>
       </c>
@@ -15635,7 +15650,7 @@
       </c>
       <c r="F3" s="41"/>
     </row>
-    <row r="4" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16" thickBot="1">
       <c r="A4" s="42" t="s">
         <v>155</v>
       </c>
@@ -15653,7 +15668,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16" thickBot="1">
       <c r="A5" s="38" t="s">
         <v>82</v>
       </c>
@@ -15671,7 +15686,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="25.5" thickBot="1">
       <c r="A6" s="42" t="s">
         <v>72</v>
       </c>
@@ -15689,7 +15704,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16" thickBot="1">
       <c r="A7" s="38" t="s">
         <v>72</v>
       </c>
@@ -15707,7 +15722,7 @@
       </c>
       <c r="F7" s="41"/>
     </row>
-    <row r="8" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16" thickBot="1">
       <c r="A8" s="42" t="s">
         <v>19</v>
       </c>
@@ -15725,7 +15740,7 @@
       </c>
       <c r="F8" s="45"/>
     </row>
-    <row r="9" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16" thickBot="1">
       <c r="A9" s="38" t="s">
         <v>32</v>
       </c>
@@ -15743,7 +15758,7 @@
       </c>
       <c r="F9" s="41"/>
     </row>
-    <row r="10" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16" thickBot="1">
       <c r="A10" s="42" t="s">
         <v>32</v>
       </c>
@@ -15761,7 +15776,7 @@
       </c>
       <c r="F10" s="45"/>
     </row>
-    <row r="11" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16" thickBot="1">
       <c r="A11" s="38" t="s">
         <v>32</v>
       </c>
@@ -15779,7 +15794,7 @@
       </c>
       <c r="F11" s="41"/>
     </row>
-    <row r="12" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16" thickBot="1">
       <c r="A12" s="42" t="s">
         <v>32</v>
       </c>
@@ -15797,7 +15812,7 @@
       </c>
       <c r="F12" s="45"/>
     </row>
-    <row r="13" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16" thickBot="1">
       <c r="A13" s="38" t="s">
         <v>32</v>
       </c>
@@ -15815,7 +15830,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16" thickBot="1">
       <c r="A14" s="42" t="s">
         <v>32</v>
       </c>
@@ -15833,7 +15848,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16" thickBot="1">
       <c r="A15" s="38" t="s">
         <v>32</v>
       </c>
@@ -15851,7 +15866,7 @@
       </c>
       <c r="F15" s="41"/>
     </row>
-    <row r="16" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16" thickBot="1">
       <c r="A16" s="42" t="s">
         <v>32</v>
       </c>
@@ -15869,7 +15884,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="16" thickBot="1">
       <c r="A17" s="38" t="s">
         <v>32</v>
       </c>
@@ -15887,7 +15902,7 @@
       </c>
       <c r="F17" s="41"/>
     </row>
-    <row r="18" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="16" thickBot="1">
       <c r="A18" s="42" t="s">
         <v>32</v>
       </c>
@@ -15905,7 +15920,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="16" thickBot="1">
       <c r="A19" s="38" t="s">
         <v>32</v>
       </c>
@@ -15923,7 +15938,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="16" thickBot="1">
       <c r="A20" s="42" t="s">
         <v>188</v>
       </c>
@@ -15941,7 +15956,7 @@
       </c>
       <c r="F20" s="45"/>
     </row>
-    <row r="21" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="16" thickBot="1">
       <c r="A21" s="38" t="s">
         <v>575</v>
       </c>
@@ -15959,7 +15974,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="16" thickBot="1">
       <c r="A22" s="42" t="s">
         <v>170</v>
       </c>
@@ -15977,7 +15992,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="16" thickBot="1">
       <c r="A23" s="38" t="s">
         <v>170</v>
       </c>
@@ -15995,7 +16010,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="16" thickBot="1">
       <c r="A24" s="42" t="s">
         <v>170</v>
       </c>
@@ -16013,7 +16028,7 @@
       </c>
       <c r="F24" s="45"/>
     </row>
-    <row r="25" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="16" thickBot="1">
       <c r="A25" s="38" t="s">
         <v>111</v>
       </c>
@@ -16031,7 +16046,7 @@
       </c>
       <c r="F25" s="41"/>
     </row>
-    <row r="26" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="16" thickBot="1">
       <c r="A26" s="42" t="s">
         <v>111</v>
       </c>
@@ -16049,7 +16064,7 @@
       </c>
       <c r="F26" s="45"/>
     </row>
-    <row r="27" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="16" thickBot="1">
       <c r="A27" s="38" t="s">
         <v>111</v>
       </c>
@@ -16067,7 +16082,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="16" thickBot="1">
       <c r="A28" s="42" t="s">
         <v>111</v>
       </c>
@@ -16085,7 +16100,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="25.5" thickBot="1">
       <c r="A29" s="38" t="s">
         <v>111</v>
       </c>
@@ -16103,7 +16118,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="16" thickBot="1">
       <c r="A30" s="42" t="s">
         <v>111</v>
       </c>
@@ -16121,7 +16136,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="16" thickBot="1">
       <c r="A31" s="38" t="s">
         <v>111</v>
       </c>
@@ -16139,7 +16154,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="16" thickBot="1">
       <c r="A32" s="42" t="s">
         <v>357</v>
       </c>
@@ -16157,7 +16172,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="16" thickBot="1">
       <c r="A33" s="38" t="s">
         <v>357</v>
       </c>
@@ -16175,7 +16190,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="25.5" thickBot="1">
       <c r="A34" s="42" t="s">
         <v>236</v>
       </c>
@@ -16193,7 +16208,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="16" thickBot="1">
       <c r="A35" s="38" t="s">
         <v>96</v>
       </c>
@@ -16211,7 +16226,7 @@
       </c>
       <c r="F35" s="41"/>
     </row>
-    <row r="36" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="25.5" thickBot="1">
       <c r="A36" s="42" t="s">
         <v>16</v>
       </c>
@@ -16229,7 +16244,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="16" thickBot="1">
       <c r="A37" s="38" t="s">
         <v>51</v>
       </c>
@@ -16247,7 +16262,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="25.5" thickBot="1">
       <c r="A38" s="42" t="s">
         <v>16</v>
       </c>
@@ -16265,7 +16280,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="16" thickBot="1">
       <c r="A39" s="38" t="s">
         <v>16</v>
       </c>
@@ -16283,7 +16298,7 @@
         <v>2625</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="16" thickBot="1">
       <c r="A40" s="42" t="s">
         <v>104</v>
       </c>
@@ -16301,7 +16316,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="16" thickBot="1">
       <c r="A41" s="38" t="s">
         <v>16</v>
       </c>
@@ -16319,7 +16334,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="16" thickBot="1">
       <c r="A42" s="42" t="s">
         <v>16</v>
       </c>
@@ -16337,7 +16352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="16" thickBot="1">
       <c r="A43" s="38" t="s">
         <v>16</v>
       </c>
@@ -16355,7 +16370,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="16" thickBot="1">
       <c r="A44" s="42" t="s">
         <v>16</v>
       </c>
@@ -16373,7 +16388,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="16" thickBot="1">
       <c r="A45" s="38" t="s">
         <v>16</v>
       </c>
@@ -16391,7 +16406,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="16" thickBot="1">
       <c r="A46" s="42" t="s">
         <v>16</v>
       </c>
@@ -16409,7 +16424,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="16" thickBot="1">
       <c r="A47" s="38" t="s">
         <v>16</v>
       </c>
@@ -16427,7 +16442,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="16" thickBot="1">
       <c r="A48" s="42" t="s">
         <v>16</v>
       </c>
@@ -16445,7 +16460,7 @@
       </c>
       <c r="F48" s="45"/>
     </row>
-    <row r="49" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="16" thickBot="1">
       <c r="A49" s="38" t="s">
         <v>16</v>
       </c>
@@ -16463,7 +16478,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="16" thickBot="1">
       <c r="A50" s="42" t="s">
         <v>16</v>
       </c>
@@ -16481,7 +16496,7 @@
       </c>
       <c r="F50" s="45"/>
     </row>
-    <row r="51" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="16" thickBot="1">
       <c r="A51" s="38" t="s">
         <v>16</v>
       </c>
@@ -16499,7 +16514,7 @@
       </c>
       <c r="F51" s="41"/>
     </row>
-    <row r="52" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" ht="16" thickBot="1">
       <c r="A52" s="42" t="s">
         <v>87</v>
       </c>
@@ -16517,7 +16532,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" ht="16" thickBot="1">
       <c r="A53" s="38" t="s">
         <v>87</v>
       </c>
@@ -16535,7 +16550,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" ht="16" thickBot="1">
       <c r="A54" s="42" t="s">
         <v>87</v>
       </c>
@@ -16553,7 +16568,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" ht="16" thickBot="1">
       <c r="A55" s="38" t="s">
         <v>87</v>
       </c>
@@ -16571,7 +16586,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" ht="16" thickBot="1">
       <c r="A56" s="42" t="s">
         <v>87</v>
       </c>
@@ -16589,7 +16604,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" ht="16" thickBot="1">
       <c r="A57" s="38" t="s">
         <v>87</v>
       </c>
@@ -16607,7 +16622,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="16" thickBot="1">
       <c r="A58" s="42" t="s">
         <v>38</v>
       </c>
@@ -16625,7 +16640,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" ht="16" thickBot="1">
       <c r="A59" s="38" t="s">
         <v>38</v>
       </c>
@@ -16645,7 +16660,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" ht="16" thickBot="1">
       <c r="A60" s="42" t="s">
         <v>38</v>
       </c>
@@ -16663,7 +16678,7 @@
       </c>
       <c r="F60" s="45"/>
     </row>
-    <row r="61" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" ht="16" thickBot="1">
       <c r="A61" s="38" t="s">
         <v>38</v>
       </c>
@@ -16681,7 +16696,7 @@
       </c>
       <c r="F61" s="41"/>
     </row>
-    <row r="62" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" ht="16" thickBot="1">
       <c r="A62" s="42" t="s">
         <v>298</v>
       </c>
@@ -16699,7 +16714,7 @@
       </c>
       <c r="F62" s="45"/>
     </row>
-    <row r="63" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" ht="16" thickBot="1">
       <c r="A63" s="38" t="s">
         <v>99</v>
       </c>
@@ -16717,7 +16732,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" ht="16" thickBot="1">
       <c r="A64" s="42" t="s">
         <v>13</v>
       </c>
@@ -16735,7 +16750,7 @@
       </c>
       <c r="F64" s="45"/>
     </row>
-    <row r="65" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="16" thickBot="1">
       <c r="A65" s="38" t="s">
         <v>13</v>
       </c>
@@ -16753,7 +16768,7 @@
       </c>
       <c r="F65" s="41"/>
     </row>
-    <row r="66" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" ht="16" thickBot="1">
       <c r="A66" s="42" t="s">
         <v>13</v>
       </c>
@@ -16771,7 +16786,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" ht="16" thickBot="1">
       <c r="A67" s="38" t="s">
         <v>616</v>
       </c>
@@ -16789,7 +16804,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" ht="16" thickBot="1">
       <c r="A68" s="42" t="s">
         <v>13</v>
       </c>
@@ -16807,7 +16822,7 @@
       </c>
       <c r="F68" s="45"/>
     </row>
-    <row r="69" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" ht="16" thickBot="1">
       <c r="A69" s="38" t="s">
         <v>113</v>
       </c>
@@ -16825,7 +16840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" ht="16" thickBot="1">
       <c r="A70" s="42" t="s">
         <v>91</v>
       </c>
@@ -16843,7 +16858,7 @@
       </c>
       <c r="F70" s="45"/>
     </row>
-    <row r="71" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="16" thickBot="1">
       <c r="A71" s="38" t="s">
         <v>30</v>
       </c>
@@ -16861,7 +16876,7 @@
         <v>3628</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="16" thickBot="1">
       <c r="A72" s="42" t="s">
         <v>30</v>
       </c>
@@ -16879,7 +16894,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" ht="16" thickBot="1">
       <c r="A73" s="38" t="s">
         <v>30</v>
       </c>
@@ -16897,7 +16912,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" ht="16" thickBot="1">
       <c r="A74" s="42" t="s">
         <v>30</v>
       </c>
@@ -16915,7 +16930,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" ht="16" thickBot="1">
       <c r="A75" s="38" t="s">
         <v>30</v>
       </c>
@@ -16933,7 +16948,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" ht="16" thickBot="1">
       <c r="A76" s="42" t="s">
         <v>176</v>
       </c>
@@ -16951,7 +16966,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" ht="16" thickBot="1">
       <c r="A77" s="38" t="s">
         <v>22</v>
       </c>
@@ -16967,7 +16982,7 @@
       <c r="E77" s="41"/>
       <c r="F77" s="41"/>
     </row>
-    <row r="78" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="16" thickBot="1">
       <c r="A78" s="42" t="s">
         <v>22</v>
       </c>
@@ -16985,7 +17000,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" ht="16" thickBot="1">
       <c r="A79" s="38" t="s">
         <v>22</v>
       </c>
@@ -17003,7 +17018,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" ht="16" thickBot="1">
       <c r="A80" s="42" t="s">
         <v>620</v>
       </c>
@@ -17021,7 +17036,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" ht="25.5" thickBot="1">
       <c r="A81" s="38" t="s">
         <v>620</v>
       </c>
@@ -17039,7 +17054,7 @@
       </c>
       <c r="F81" s="41"/>
     </row>
-    <row r="82" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" ht="16" thickBot="1">
       <c r="A82" s="42" t="s">
         <v>9</v>
       </c>
@@ -17057,7 +17072,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" ht="16" thickBot="1">
       <c r="A83" s="38" t="s">
         <v>9</v>
       </c>
@@ -17075,7 +17090,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" ht="25.5" thickBot="1">
       <c r="A84" s="42" t="s">
         <v>9</v>
       </c>
@@ -17093,7 +17108,7 @@
       </c>
       <c r="F84" s="45"/>
     </row>
-    <row r="85" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" ht="25.5" thickBot="1">
       <c r="A85" s="38" t="s">
         <v>9</v>
       </c>
@@ -17111,7 +17126,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" ht="16" thickBot="1">
       <c r="A86" s="42" t="s">
         <v>9</v>
       </c>
@@ -17129,7 +17144,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" ht="25.5" thickBot="1">
       <c r="A87" s="38" t="s">
         <v>9</v>
       </c>
@@ -17147,7 +17162,7 @@
         <v>1957</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" ht="16" thickBot="1">
       <c r="A88" s="42" t="s">
         <v>173</v>
       </c>
@@ -17165,7 +17180,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="16" thickBot="1">
       <c r="A89" s="47" t="s">
         <v>34</v>
       </c>
@@ -17183,7 +17198,7 @@
       </c>
       <c r="F89" s="41"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6">
       <c r="A90" s="48" t="s">
         <v>627</v>
       </c>
@@ -17206,9 +17221,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E374"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="27.33203125" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -17217,7 +17232,7 @@
     <col min="5" max="5" width="41.83203125" style="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="34" customHeight="1">
       <c r="A1" s="57" t="s">
         <v>628</v>
       </c>
@@ -17225,7 +17240,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" s="1" customFormat="1">
       <c r="A2" s="1" t="s">
         <v>629</v>
       </c>
@@ -17242,12 +17257,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>634</v>
       </c>
@@ -17261,7 +17276,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>637</v>
       </c>
@@ -17275,7 +17290,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>639</v>
       </c>
@@ -17289,7 +17304,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>641</v>
       </c>
@@ -17303,7 +17318,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>643</v>
       </c>
@@ -17317,7 +17332,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>645</v>
       </c>
@@ -17328,7 +17343,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>646</v>
       </c>
@@ -17342,7 +17357,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>648</v>
       </c>
@@ -17356,7 +17371,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>649</v>
       </c>
@@ -17370,7 +17385,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>651</v>
       </c>
@@ -17384,7 +17399,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>653</v>
       </c>
@@ -17398,12 +17413,12 @@
         <v>636</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>655</v>
       </c>
@@ -17417,7 +17432,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" ht="46.5">
       <c r="A17" s="1" t="s">
         <v>99</v>
       </c>
@@ -17425,7 +17440,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>668</v>
       </c>
@@ -17436,7 +17451,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>669</v>
       </c>
@@ -17450,7 +17465,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>670</v>
       </c>
@@ -17464,7 +17479,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>671</v>
       </c>
@@ -17478,7 +17493,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>672</v>
       </c>
@@ -17492,7 +17507,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>673</v>
       </c>
@@ -17506,7 +17521,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>674</v>
       </c>
@@ -17520,7 +17535,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>675</v>
       </c>
@@ -17534,7 +17549,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>676</v>
       </c>
@@ -17548,7 +17563,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>677</v>
       </c>
@@ -17562,7 +17577,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>680</v>
       </c>
@@ -17573,7 +17588,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>678</v>
       </c>
@@ -17587,7 +17602,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
         <v>679</v>
       </c>
@@ -17601,7 +17616,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
         <v>705</v>
       </c>
@@ -17615,7 +17630,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
         <v>716</v>
       </c>
@@ -17626,7 +17641,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>717</v>
       </c>
@@ -17640,7 +17655,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
         <v>706</v>
       </c>
@@ -17654,7 +17669,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>715</v>
       </c>
@@ -17668,7 +17683,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>707</v>
       </c>
@@ -17682,7 +17697,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
         <v>708</v>
       </c>
@@ -17696,7 +17711,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
         <v>709</v>
       </c>
@@ -17710,7 +17725,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
         <v>710</v>
       </c>
@@ -17724,12 +17739,12 @@
         <v>658</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
         <v>712</v>
       </c>
@@ -17743,7 +17758,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
         <v>718</v>
       </c>
@@ -17754,7 +17769,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5">
       <c r="A43" s="1" t="s">
         <v>689</v>
       </c>
@@ -17762,7 +17777,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
         <v>690</v>
       </c>
@@ -17776,7 +17791,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
         <v>692</v>
       </c>
@@ -17790,7 +17805,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
         <v>694</v>
       </c>
@@ -17804,7 +17819,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5">
       <c r="A47" s="1" t="s">
         <v>696</v>
       </c>
@@ -17812,7 +17827,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
         <v>696</v>
       </c>
@@ -17826,7 +17841,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5">
       <c r="A49" s="1" t="s">
         <v>699</v>
       </c>
@@ -17834,7 +17849,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
         <v>699</v>
       </c>
@@ -17848,7 +17863,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5">
       <c r="A51" s="1" t="s">
         <v>702</v>
       </c>
@@ -17856,7 +17871,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
         <v>702</v>
       </c>
@@ -17870,7 +17885,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5">
       <c r="A53" s="1" t="s">
         <v>719</v>
       </c>
@@ -17878,7 +17893,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" ht="31">
       <c r="A54" t="s">
         <v>719</v>
       </c>
@@ -17892,12 +17907,12 @@
         <v>701</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5">
       <c r="A55" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
         <v>722</v>
       </c>
@@ -17911,7 +17926,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5">
       <c r="A57" s="1" t="s">
         <v>724</v>
       </c>
@@ -17919,7 +17934,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="58" spans="1:5" s="8" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" s="8" customFormat="1" ht="37" customHeight="1">
       <c r="A58" s="8" t="s">
         <v>725</v>
       </c>
@@ -17936,7 +17951,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5">
       <c r="A59" s="1" t="s">
         <v>729</v>
       </c>
@@ -17944,7 +17959,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5">
       <c r="A60" t="s">
         <v>729</v>
       </c>
@@ -17958,7 +17973,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5">
       <c r="A61" s="1" t="s">
         <v>732</v>
       </c>
@@ -17966,7 +17981,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5">
       <c r="A62" t="s">
         <v>733</v>
       </c>
@@ -17977,7 +17992,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5">
       <c r="A63" t="s">
         <v>735</v>
       </c>
@@ -17988,7 +18003,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5">
       <c r="A64" t="s">
         <v>737</v>
       </c>
@@ -17999,7 +18014,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5">
       <c r="A65" t="s">
         <v>738</v>
       </c>
@@ -18013,7 +18028,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5">
       <c r="A66" t="s">
         <v>741</v>
       </c>
@@ -18027,7 +18042,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5">
       <c r="A67" t="s">
         <v>743</v>
       </c>
@@ -18038,7 +18053,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5">
       <c r="A68" t="s">
         <v>744</v>
       </c>
@@ -18052,7 +18067,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="69" spans="1:5" s="8" customFormat="1" ht="52" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" s="8" customFormat="1" ht="52" customHeight="1">
       <c r="A69" s="8" t="s">
         <v>745</v>
       </c>
@@ -18069,7 +18084,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5">
       <c r="A70" t="s">
         <v>746</v>
       </c>
@@ -18083,7 +18098,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5">
       <c r="A71" t="s">
         <v>747</v>
       </c>
@@ -18094,7 +18109,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5">
       <c r="A72" t="s">
         <v>748</v>
       </c>
@@ -18105,7 +18120,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5">
       <c r="A73" t="s">
         <v>749</v>
       </c>
@@ -18119,7 +18134,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5">
       <c r="A74" t="s">
         <v>750</v>
       </c>
@@ -18136,7 +18151,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" ht="62">
       <c r="A75" t="s">
         <v>752</v>
       </c>
@@ -18153,7 +18168,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="76" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" s="8" customFormat="1">
       <c r="A76" s="8" t="s">
         <v>754</v>
       </c>
@@ -18168,7 +18183,7 @@
       </c>
       <c r="E76" s="53"/>
     </row>
-    <row r="77" spans="1:5" s="8" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" s="8" customFormat="1" ht="46.5">
       <c r="A77" s="8" t="s">
         <v>756</v>
       </c>
@@ -18185,7 +18200,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5">
       <c r="A78" t="s">
         <v>757</v>
       </c>
@@ -18196,7 +18211,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5">
       <c r="A79" t="s">
         <v>758</v>
       </c>
@@ -18207,7 +18222,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5">
       <c r="A80" t="s">
         <v>759</v>
       </c>
@@ -18218,7 +18233,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5">
       <c r="A81" t="s">
         <v>760</v>
       </c>
@@ -18235,7 +18250,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5">
       <c r="A82" t="s">
         <v>762</v>
       </c>
@@ -18246,7 +18261,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5">
       <c r="A83" t="s">
         <v>763</v>
       </c>
@@ -18260,7 +18275,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5">
       <c r="A84" t="s">
         <v>765</v>
       </c>
@@ -18271,7 +18286,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5">
       <c r="A85" t="s">
         <v>766</v>
       </c>
@@ -18285,7 +18300,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5">
       <c r="A86" t="s">
         <v>768</v>
       </c>
@@ -18296,7 +18311,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5">
       <c r="A87" t="s">
         <v>769</v>
       </c>
@@ -18310,7 +18325,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5">
       <c r="A88" t="s">
         <v>771</v>
       </c>
@@ -18321,7 +18336,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5">
       <c r="A89" t="s">
         <v>772</v>
       </c>
@@ -18332,7 +18347,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5">
       <c r="A90" t="s">
         <v>773</v>
       </c>
@@ -18343,7 +18358,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="91" spans="1:5" s="8" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" s="8" customFormat="1" ht="46.5">
       <c r="A91" s="8" t="s">
         <v>774</v>
       </c>
@@ -18360,7 +18375,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5">
       <c r="A92" s="1" t="s">
         <v>786</v>
       </c>
@@ -18368,7 +18383,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" ht="31">
       <c r="A93" t="s">
         <v>775</v>
       </c>
@@ -18382,7 +18397,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" ht="31">
       <c r="A94" t="s">
         <v>778</v>
       </c>
@@ -18396,12 +18411,12 @@
         <v>777</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5">
       <c r="A95" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" ht="31">
       <c r="A96" t="s">
         <v>779</v>
       </c>
@@ -18415,7 +18430,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4" ht="31">
       <c r="A97" t="s">
         <v>781</v>
       </c>
@@ -18429,7 +18444,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4">
       <c r="A98" t="s">
         <v>782</v>
       </c>
@@ -18443,7 +18458,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4">
       <c r="A99" t="s">
         <v>784</v>
       </c>
@@ -18457,7 +18472,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4" ht="31">
       <c r="A100" t="s">
         <v>785</v>
       </c>
@@ -18471,7 +18486,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4">
       <c r="A101" t="s">
         <v>796</v>
       </c>
@@ -18485,7 +18500,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4">
       <c r="A102" t="s">
         <v>797</v>
       </c>
@@ -18496,7 +18511,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4" ht="31">
       <c r="A103" t="s">
         <v>798</v>
       </c>
@@ -18510,7 +18525,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4">
       <c r="A104" t="s">
         <v>799</v>
       </c>
@@ -18521,7 +18536,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4" ht="31">
       <c r="A105" t="s">
         <v>800</v>
       </c>
@@ -18535,7 +18550,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4">
       <c r="A106" t="s">
         <v>801</v>
       </c>
@@ -18546,7 +18561,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4" ht="31">
       <c r="A107" t="s">
         <v>802</v>
       </c>
@@ -18560,7 +18575,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4">
       <c r="A108" t="s">
         <v>803</v>
       </c>
@@ -18571,7 +18586,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4">
       <c r="A109" t="s">
         <v>804</v>
       </c>
@@ -18582,7 +18597,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4">
       <c r="A110" t="s">
         <v>806</v>
       </c>
@@ -18596,7 +18611,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4">
       <c r="A111" t="s">
         <v>807</v>
       </c>
@@ -18607,7 +18622,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4">
       <c r="A112" t="s">
         <v>809</v>
       </c>
@@ -18618,7 +18633,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:5">
       <c r="A113" t="s">
         <v>810</v>
       </c>
@@ -18632,7 +18647,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:5">
       <c r="A114" t="s">
         <v>812</v>
       </c>
@@ -18643,7 +18658,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:5">
       <c r="A115" t="s">
         <v>813</v>
       </c>
@@ -18657,7 +18672,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:5">
       <c r="A116" t="s">
         <v>814</v>
       </c>
@@ -18671,12 +18686,12 @@
         <v>777</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:5">
       <c r="A117" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:5">
       <c r="A118" t="s">
         <v>816</v>
       </c>
@@ -18690,7 +18705,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:5" ht="31">
       <c r="A119" t="s">
         <v>818</v>
       </c>
@@ -18704,12 +18719,12 @@
         <v>777</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:5">
       <c r="A120" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:5">
       <c r="A121" t="s">
         <v>819</v>
       </c>
@@ -18723,12 +18738,12 @@
         <v>777</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:5">
       <c r="A122" s="1" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:5">
       <c r="A123" t="s">
         <v>821</v>
       </c>
@@ -18742,7 +18757,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:5">
       <c r="A124" t="s">
         <v>824</v>
       </c>
@@ -18756,7 +18771,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:5">
       <c r="A125" s="1" t="s">
         <v>825</v>
       </c>
@@ -18764,7 +18779,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:5">
       <c r="A126" t="s">
         <v>825</v>
       </c>
@@ -18778,7 +18793,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:5">
       <c r="A127" s="1" t="s">
         <v>831</v>
       </c>
@@ -18786,7 +18801,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:5" ht="46.5">
       <c r="A128" t="s">
         <v>831</v>
       </c>
@@ -18800,7 +18815,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:5">
       <c r="A129" s="1" t="s">
         <v>832</v>
       </c>
@@ -18808,7 +18823,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:5">
       <c r="A130" t="s">
         <v>833</v>
       </c>
@@ -18819,7 +18834,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:5">
       <c r="A131" t="s">
         <v>835</v>
       </c>
@@ -18833,7 +18848,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:5">
       <c r="A132" t="s">
         <v>836</v>
       </c>
@@ -18844,7 +18859,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:5">
       <c r="A133" t="s">
         <v>838</v>
       </c>
@@ -18855,7 +18870,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:5">
       <c r="A134" t="s">
         <v>839</v>
       </c>
@@ -18869,7 +18884,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:5">
       <c r="A135" t="s">
         <v>841</v>
       </c>
@@ -18880,7 +18895,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:5">
       <c r="A136" t="s">
         <v>842</v>
       </c>
@@ -18891,7 +18906,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:5" ht="31">
       <c r="A137" t="s">
         <v>843</v>
       </c>
@@ -18905,7 +18920,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:5">
       <c r="A138" t="s">
         <v>844</v>
       </c>
@@ -18919,7 +18934,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:5" ht="31">
       <c r="A139" t="s">
         <v>846</v>
       </c>
@@ -18933,7 +18948,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:5">
       <c r="A140" s="1" t="s">
         <v>847</v>
       </c>
@@ -18941,7 +18956,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:5" ht="31">
       <c r="A141" t="s">
         <v>848</v>
       </c>
@@ -18955,7 +18970,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:5">
       <c r="A142" t="s">
         <v>850</v>
       </c>
@@ -18969,7 +18984,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:5">
       <c r="A143" t="s">
         <v>852</v>
       </c>
@@ -18980,7 +18995,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:5">
       <c r="A144" t="s">
         <v>853</v>
       </c>
@@ -18994,7 +19009,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:5">
       <c r="A145" t="s">
         <v>855</v>
       </c>
@@ -19008,12 +19023,12 @@
         <v>849</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:5">
       <c r="A146" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:5">
       <c r="A147" t="s">
         <v>857</v>
       </c>
@@ -19027,7 +19042,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="52" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:5" ht="52" customHeight="1">
       <c r="A148" s="1" t="s">
         <v>1195</v>
       </c>
@@ -19035,7 +19050,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:5">
       <c r="A149" t="s">
         <v>868</v>
       </c>
@@ -19049,7 +19064,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:5" ht="31">
       <c r="A150" t="s">
         <v>869</v>
       </c>
@@ -19063,7 +19078,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:5">
       <c r="A151" t="s">
         <v>870</v>
       </c>
@@ -19077,7 +19092,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:5">
       <c r="A152" t="s">
         <v>877</v>
       </c>
@@ -19088,7 +19103,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:5">
       <c r="A153" t="s">
         <v>878</v>
       </c>
@@ -19102,7 +19117,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:5">
       <c r="A154" t="s">
         <v>879</v>
       </c>
@@ -19116,7 +19131,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:5">
       <c r="A156" t="s">
         <v>871</v>
       </c>
@@ -19127,7 +19142,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:5" ht="31">
       <c r="A157" t="s">
         <v>897</v>
       </c>
@@ -19141,7 +19156,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:5">
       <c r="A158" t="s">
         <v>898</v>
       </c>
@@ -19155,7 +19170,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:5">
       <c r="A159" t="s">
         <v>919</v>
       </c>
@@ -19169,7 +19184,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:5" ht="31">
       <c r="A160" t="s">
         <v>899</v>
       </c>
@@ -19183,7 +19198,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:4" ht="31">
       <c r="A161" t="s">
         <v>900</v>
       </c>
@@ -19197,7 +19212,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:4">
       <c r="A162" t="s">
         <v>901</v>
       </c>
@@ -19211,7 +19226,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:4">
       <c r="A163" t="s">
         <v>902</v>
       </c>
@@ -19225,7 +19240,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:4" ht="31">
       <c r="A164" t="s">
         <v>903</v>
       </c>
@@ -19239,7 +19254,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:4">
       <c r="A165" t="s">
         <v>904</v>
       </c>
@@ -19250,7 +19265,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="166" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:4" ht="31">
       <c r="A166" t="s">
         <v>905</v>
       </c>
@@ -19264,7 +19279,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:4">
       <c r="A167" t="s">
         <v>888</v>
       </c>
@@ -19278,12 +19293,12 @@
         <v>860</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:4">
       <c r="A168" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:4">
       <c r="A169" t="s">
         <v>907</v>
       </c>
@@ -19297,7 +19312,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:4">
       <c r="A170" t="s">
         <v>908</v>
       </c>
@@ -19311,7 +19326,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:4">
       <c r="A171" t="s">
         <v>909</v>
       </c>
@@ -19322,7 +19337,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:4">
       <c r="A172" t="s">
         <v>920</v>
       </c>
@@ -19333,7 +19348,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:4">
       <c r="A173" t="s">
         <v>921</v>
       </c>
@@ -19347,7 +19362,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:4">
       <c r="A174" t="s">
         <v>910</v>
       </c>
@@ -19358,7 +19373,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:4">
       <c r="A175" t="s">
         <v>911</v>
       </c>
@@ -19372,7 +19387,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:4">
       <c r="A176" t="s">
         <v>912</v>
       </c>
@@ -19386,7 +19401,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:5">
       <c r="A177" t="s">
         <v>913</v>
       </c>
@@ -19400,7 +19415,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:5">
       <c r="A178" t="s">
         <v>923</v>
       </c>
@@ -19411,7 +19426,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:5">
       <c r="A179" t="s">
         <v>914</v>
       </c>
@@ -19425,7 +19440,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:5">
       <c r="A180" t="s">
         <v>915</v>
       </c>
@@ -19436,7 +19451,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:5">
       <c r="A181" t="s">
         <v>916</v>
       </c>
@@ -19450,7 +19465,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:5">
       <c r="A182" t="s">
         <v>918</v>
       </c>
@@ -19464,7 +19479,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:5">
       <c r="A183" t="s">
         <v>959</v>
       </c>
@@ -19478,7 +19493,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:5">
       <c r="A184" t="s">
         <v>960</v>
       </c>
@@ -19489,7 +19504,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:5">
       <c r="A185" t="s">
         <v>961</v>
       </c>
@@ -19500,12 +19515,12 @@
         <v>867</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:5">
       <c r="A186" s="1" t="s">
         <v>925</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:5">
       <c r="A187" t="s">
         <v>926</v>
       </c>
@@ -19516,7 +19531,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:5" ht="26" customHeight="1">
       <c r="A188" t="s">
         <v>925</v>
       </c>
@@ -19530,7 +19545,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:5" ht="31">
       <c r="A189" s="54" t="s">
         <v>1259</v>
       </c>
@@ -19541,7 +19556,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:5">
       <c r="A190" s="8" t="s">
         <v>930</v>
       </c>
@@ -19556,7 +19571,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:5">
       <c r="A191" s="8" t="s">
         <v>932</v>
       </c>
@@ -19568,7 +19583,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:5">
       <c r="A192" s="8" t="s">
         <v>933</v>
       </c>
@@ -19580,7 +19595,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:5">
       <c r="A193" s="8" t="s">
         <v>935</v>
       </c>
@@ -19592,7 +19607,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:5">
       <c r="A194" s="8" t="s">
         <v>936</v>
       </c>
@@ -19604,7 +19619,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:5">
       <c r="A195" s="8" t="s">
         <v>938</v>
       </c>
@@ -19616,7 +19631,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:5" ht="46.5">
       <c r="A196" s="8" t="s">
         <v>939</v>
       </c>
@@ -19630,7 +19645,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:5">
       <c r="A197" s="8" t="s">
         <v>941</v>
       </c>
@@ -19642,7 +19657,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:5">
       <c r="A198" s="8" t="s">
         <v>942</v>
       </c>
@@ -19654,7 +19669,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:5">
       <c r="A199" s="8" t="s">
         <v>943</v>
       </c>
@@ -19666,7 +19681,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:5">
       <c r="A200" s="8" t="s">
         <v>944</v>
       </c>
@@ -19678,7 +19693,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:5">
       <c r="A201" s="8" t="s">
         <v>945</v>
       </c>
@@ -19693,7 +19708,7 @@
       </c>
       <c r="E201" s="53"/>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:5">
       <c r="A202" s="8" t="s">
         <v>946</v>
       </c>
@@ -19705,7 +19720,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:5">
       <c r="A203" s="8" t="s">
         <v>947</v>
       </c>
@@ -19719,7 +19734,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:5">
       <c r="A204" s="8" t="s">
         <v>949</v>
       </c>
@@ -19731,7 +19746,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:5">
       <c r="A205" s="8" t="s">
         <v>950</v>
       </c>
@@ -19743,7 +19758,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:5">
       <c r="A206" s="8" t="s">
         <v>951</v>
       </c>
@@ -19755,7 +19770,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:5">
       <c r="A207" s="8" t="s">
         <v>952</v>
       </c>
@@ -19767,7 +19782,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:5">
       <c r="A208" s="8" t="s">
         <v>953</v>
       </c>
@@ -19781,7 +19796,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:4">
       <c r="A209" s="8" t="s">
         <v>954</v>
       </c>
@@ -19795,7 +19810,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:4">
       <c r="A210" s="8" t="s">
         <v>955</v>
       </c>
@@ -19807,7 +19822,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:4">
       <c r="A211" s="8" t="s">
         <v>956</v>
       </c>
@@ -19821,7 +19836,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:4">
       <c r="A212" s="8" t="s">
         <v>958</v>
       </c>
@@ -19833,7 +19848,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:4">
       <c r="A213" s="8" t="s">
         <v>964</v>
       </c>
@@ -19845,7 +19860,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:4">
       <c r="A214" s="8" t="s">
         <v>966</v>
       </c>
@@ -19857,7 +19872,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:4">
       <c r="A215" s="8" t="s">
         <v>967</v>
       </c>
@@ -19869,7 +19884,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:4">
       <c r="A216" s="8" t="s">
         <v>968</v>
       </c>
@@ -19883,7 +19898,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="217" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:4" ht="31">
       <c r="A217" s="8" t="s">
         <v>969</v>
       </c>
@@ -19897,7 +19912,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:4">
       <c r="A218" s="8" t="s">
         <v>971</v>
       </c>
@@ -19911,7 +19926,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:4">
       <c r="A219" s="8" t="s">
         <v>973</v>
       </c>
@@ -19923,7 +19938,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:4">
       <c r="A220" s="8" t="s">
         <v>974</v>
       </c>
@@ -19935,7 +19950,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:4">
       <c r="A221" s="8" t="s">
         <v>975</v>
       </c>
@@ -19949,7 +19964,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:4">
       <c r="A222" s="8" t="s">
         <v>976</v>
       </c>
@@ -19961,7 +19976,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:4">
       <c r="A223" s="8" t="s">
         <v>977</v>
       </c>
@@ -19973,7 +19988,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:4">
       <c r="A224" s="8" t="s">
         <v>978</v>
       </c>
@@ -19987,7 +20002,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:4">
       <c r="A225" s="8" t="s">
         <v>980</v>
       </c>
@@ -19999,7 +20014,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:4">
       <c r="A226" s="8" t="s">
         <v>981</v>
       </c>
@@ -20011,7 +20026,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:4">
       <c r="A227" s="8" t="s">
         <v>982</v>
       </c>
@@ -20023,7 +20038,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="228" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:4" ht="31">
       <c r="A228" s="8" t="s">
         <v>996</v>
       </c>
@@ -20037,7 +20052,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:4">
       <c r="A229" s="8" t="s">
         <v>983</v>
       </c>
@@ -20049,7 +20064,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:4">
       <c r="A230" s="8" t="s">
         <v>984</v>
       </c>
@@ -20061,7 +20076,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:4">
       <c r="A231" s="8" t="s">
         <v>985</v>
       </c>
@@ -20073,7 +20088,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:4">
       <c r="A232" s="8" t="s">
         <v>986</v>
       </c>
@@ -20087,7 +20102,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:4">
       <c r="A233" s="8" t="s">
         <v>987</v>
       </c>
@@ -20099,7 +20114,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:4">
       <c r="A234" s="8" t="s">
         <v>988</v>
       </c>
@@ -20111,7 +20126,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:4">
       <c r="A235" s="8" t="s">
         <v>989</v>
       </c>
@@ -20123,7 +20138,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:4">
       <c r="A236" s="8" t="s">
         <v>990</v>
       </c>
@@ -20137,7 +20152,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:4">
       <c r="A237" s="8" t="s">
         <v>992</v>
       </c>
@@ -20149,7 +20164,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:4">
       <c r="A238" s="8" t="s">
         <v>993</v>
       </c>
@@ -20161,7 +20176,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:4">
       <c r="A239" s="8" t="s">
         <v>997</v>
       </c>
@@ -20173,7 +20188,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:4">
       <c r="A240" s="8" t="s">
         <v>998</v>
       </c>
@@ -20185,7 +20200,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:4">
       <c r="A241" s="8" t="s">
         <v>999</v>
       </c>
@@ -20197,7 +20212,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:4">
       <c r="A242" s="8" t="s">
         <v>1000</v>
       </c>
@@ -20209,7 +20224,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:4">
       <c r="A243" s="8" t="s">
         <v>1001</v>
       </c>
@@ -20223,7 +20238,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:4">
       <c r="A244" s="8" t="s">
         <v>1003</v>
       </c>
@@ -20235,7 +20250,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:4">
       <c r="A245" s="8" t="s">
         <v>1004</v>
       </c>
@@ -20247,7 +20262,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:4">
       <c r="A246" s="8" t="s">
         <v>1005</v>
       </c>
@@ -20259,7 +20274,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="247" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:4" ht="31">
       <c r="A247" s="8" t="s">
         <v>1006</v>
       </c>
@@ -20273,7 +20288,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="248" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:4" ht="31">
       <c r="A248" s="8" t="s">
         <v>1007</v>
       </c>
@@ -20287,7 +20302,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:4">
       <c r="A249" s="8" t="s">
         <v>1008</v>
       </c>
@@ -20301,7 +20316,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:4">
       <c r="A250" s="8" t="s">
         <v>1009</v>
       </c>
@@ -20313,7 +20328,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:4">
       <c r="A251" s="8" t="s">
         <v>1010</v>
       </c>
@@ -20325,7 +20340,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:4">
       <c r="A252" s="8" t="s">
         <v>1011</v>
       </c>
@@ -20337,7 +20352,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:4">
       <c r="A253" s="8" t="s">
         <v>1012</v>
       </c>
@@ -20349,7 +20364,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:4">
       <c r="A254" s="8" t="s">
         <v>1013</v>
       </c>
@@ -20361,7 +20376,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:4">
       <c r="A255" s="8" t="s">
         <v>1014</v>
       </c>
@@ -20373,7 +20388,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:4">
       <c r="A256" s="8" t="s">
         <v>1015</v>
       </c>
@@ -20387,7 +20402,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:5">
       <c r="A257" s="8" t="s">
         <v>1017</v>
       </c>
@@ -20401,7 +20416,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:5">
       <c r="A258" s="8" t="s">
         <v>1018</v>
       </c>
@@ -20413,7 +20428,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:5">
       <c r="A259" s="8" t="s">
         <v>1019</v>
       </c>
@@ -20425,7 +20440,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:5">
       <c r="A260" s="8" t="s">
         <v>1020</v>
       </c>
@@ -20437,7 +20452,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:5">
       <c r="A261" s="8" t="s">
         <v>1022</v>
       </c>
@@ -20451,7 +20466,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:5">
       <c r="A262" s="8" t="s">
         <v>1023</v>
       </c>
@@ -20465,7 +20480,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:5">
       <c r="A263" s="8" t="s">
         <v>1025</v>
       </c>
@@ -20479,7 +20494,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:5">
       <c r="A264" s="8" t="s">
         <v>1026</v>
       </c>
@@ -20493,7 +20508,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="265" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:5" ht="31">
       <c r="A265" s="8" t="s">
         <v>1027</v>
       </c>
@@ -20507,7 +20522,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:5">
       <c r="A266" s="8" t="s">
         <v>1029</v>
       </c>
@@ -20519,7 +20534,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="267" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:5" ht="31">
       <c r="A267" s="54" t="s">
         <v>256</v>
       </c>
@@ -20530,7 +20545,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:5">
       <c r="A268" s="8" t="s">
         <v>1030</v>
       </c>
@@ -20542,7 +20557,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:5">
       <c r="A269" s="8" t="s">
         <v>1031</v>
       </c>
@@ -20556,7 +20571,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:5">
       <c r="A270" s="8" t="s">
         <v>1034</v>
       </c>
@@ -20570,7 +20585,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:5">
       <c r="A271" s="8" t="s">
         <v>1036</v>
       </c>
@@ -20582,7 +20597,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="272" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:5" ht="31">
       <c r="A272" s="8" t="s">
         <v>1037</v>
       </c>
@@ -20596,7 +20611,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:5">
       <c r="A273" s="8" t="s">
         <v>1039</v>
       </c>
@@ -20608,7 +20623,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:5">
       <c r="A274" s="8" t="s">
         <v>1040</v>
       </c>
@@ -20622,7 +20637,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:5">
       <c r="A275" s="8"/>
       <c r="B275" s="8"/>
       <c r="C275" s="53" t="s">
@@ -20632,7 +20647,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:5" ht="46.5">
       <c r="A276" s="8" t="s">
         <v>1045</v>
       </c>
@@ -20646,7 +20661,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:5">
       <c r="A277" s="8" t="s">
         <v>1047</v>
       </c>
@@ -20658,7 +20673,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:5">
       <c r="A278" s="8" t="s">
         <v>1049</v>
       </c>
@@ -20670,7 +20685,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:5">
       <c r="A279" s="8" t="s">
         <v>1050</v>
       </c>
@@ -20682,7 +20697,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="280" spans="1:5" ht="78" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:5" ht="78" customHeight="1">
       <c r="A280" s="1" t="s">
         <v>355</v>
       </c>
@@ -20690,7 +20705,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:5">
       <c r="A281" s="8" t="s">
         <v>1062</v>
       </c>
@@ -20702,7 +20717,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:5">
       <c r="A282" t="s">
         <v>1063</v>
       </c>
@@ -20719,7 +20734,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:5">
       <c r="A283" t="s">
         <v>1064</v>
       </c>
@@ -20736,7 +20751,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:5">
       <c r="A284" t="s">
         <v>1065</v>
       </c>
@@ -20750,7 +20765,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:5">
       <c r="A285" t="s">
         <v>1066</v>
       </c>
@@ -20764,7 +20779,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:5">
       <c r="A286" s="8" t="s">
         <v>1067</v>
       </c>
@@ -20776,7 +20791,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:5">
       <c r="A287" t="s">
         <v>1068</v>
       </c>
@@ -20793,7 +20808,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:5">
       <c r="A288" s="8" t="s">
         <v>1069</v>
       </c>
@@ -20805,7 +20820,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:5">
       <c r="A289" s="8" t="s">
         <v>1070</v>
       </c>
@@ -20817,7 +20832,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:5">
       <c r="A290" t="s">
         <v>1071</v>
       </c>
@@ -20831,7 +20846,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:5">
       <c r="A291" s="8" t="s">
         <v>1072</v>
       </c>
@@ -20848,7 +20863,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:5">
       <c r="A292" s="8" t="s">
         <v>1073</v>
       </c>
@@ -20860,7 +20875,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:5">
       <c r="A293" s="8" t="s">
         <v>1074</v>
       </c>
@@ -20872,7 +20887,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:5">
       <c r="A294" t="s">
         <v>1075</v>
       </c>
@@ -20886,7 +20901,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:5">
       <c r="A295" t="s">
         <v>1076</v>
       </c>
@@ -20903,7 +20918,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:5">
       <c r="A296" t="s">
         <v>1077</v>
       </c>
@@ -20920,7 +20935,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="297" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:5" ht="62">
       <c r="A297" s="8" t="s">
         <v>1078</v>
       </c>
@@ -20937,7 +20952,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:5">
       <c r="A298" s="8" t="s">
         <v>1093</v>
       </c>
@@ -20952,7 +20967,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:5">
       <c r="A299" t="s">
         <v>1079</v>
       </c>
@@ -20963,7 +20978,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:5">
       <c r="A300" t="s">
         <v>1080</v>
       </c>
@@ -20974,7 +20989,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:5">
       <c r="A301" t="s">
         <v>1081</v>
       </c>
@@ -20985,7 +21000,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:5">
       <c r="A302" s="8" t="s">
         <v>1082</v>
       </c>
@@ -21002,7 +21017,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:5">
       <c r="A303" t="s">
         <v>1083</v>
       </c>
@@ -21016,7 +21031,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:5">
       <c r="A304" t="s">
         <v>1084</v>
       </c>
@@ -21030,7 +21045,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="305" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:5" ht="31">
       <c r="A305" t="s">
         <v>1095</v>
       </c>
@@ -21047,7 +21062,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:5">
       <c r="A306" s="8" t="s">
         <v>1085</v>
       </c>
@@ -21062,7 +21077,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:5">
       <c r="A307" s="8" t="s">
         <v>1086</v>
       </c>
@@ -21077,7 +21092,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:5">
       <c r="A308" s="8" t="s">
         <v>1087</v>
       </c>
@@ -21092,7 +21107,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:5">
       <c r="A309" s="8" t="s">
         <v>1092</v>
       </c>
@@ -21107,7 +21122,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:5">
       <c r="A310" s="8" t="s">
         <v>1089</v>
       </c>
@@ -21122,7 +21137,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="311" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:5" ht="31">
       <c r="A311" s="8" t="s">
         <v>1091</v>
       </c>
@@ -21139,7 +21154,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:5">
       <c r="A312" s="8" t="s">
         <v>1105</v>
       </c>
@@ -21154,7 +21169,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:5">
       <c r="A313" t="s">
         <v>1135</v>
       </c>
@@ -21165,7 +21180,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:5">
       <c r="A314" t="s">
         <v>1106</v>
       </c>
@@ -21182,7 +21197,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:5">
       <c r="A315" t="s">
         <v>1107</v>
       </c>
@@ -21193,7 +21208,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:5">
       <c r="A316" t="s">
         <v>1134</v>
       </c>
@@ -21210,7 +21225,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="317" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:5" ht="32" customHeight="1">
       <c r="A317" t="s">
         <v>1138</v>
       </c>
@@ -21227,7 +21242,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:5">
       <c r="A318" t="s">
         <v>1108</v>
       </c>
@@ -21238,7 +21253,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:5">
       <c r="A319" s="8" t="s">
         <v>1109</v>
       </c>
@@ -21253,7 +21268,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:5">
       <c r="A320" t="s">
         <v>1110</v>
       </c>
@@ -21270,7 +21285,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:5">
       <c r="A321" s="8" t="s">
         <v>1112</v>
       </c>
@@ -21285,7 +21300,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:5">
       <c r="A322" t="s">
         <v>1113</v>
       </c>
@@ -21296,7 +21311,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:5">
       <c r="A323" t="s">
         <v>1114</v>
       </c>
@@ -21307,7 +21322,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:5">
       <c r="A324" s="8" t="s">
         <v>1115</v>
       </c>
@@ -21322,7 +21337,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:5">
       <c r="A325" t="s">
         <v>1116</v>
       </c>
@@ -21339,7 +21354,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:5">
       <c r="A326" t="s">
         <v>1141</v>
       </c>
@@ -21350,7 +21365,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:5">
       <c r="A327" t="s">
         <v>1140</v>
       </c>
@@ -21361,7 +21376,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:5">
       <c r="A328" t="s">
         <v>1117</v>
       </c>
@@ -21378,7 +21393,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:5">
       <c r="A329" t="s">
         <v>1118</v>
       </c>
@@ -21389,7 +21404,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:5">
       <c r="A330" t="s">
         <v>1119</v>
       </c>
@@ -21400,7 +21415,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:5">
       <c r="A331" t="s">
         <v>1120</v>
       </c>
@@ -21411,7 +21426,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:5">
       <c r="A332" t="s">
         <v>1121</v>
       </c>
@@ -21425,7 +21440,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="333" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:5" ht="31">
       <c r="A333" s="8" t="s">
         <v>1122</v>
       </c>
@@ -21442,7 +21457,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:5">
       <c r="A334" s="8" t="s">
         <v>1123</v>
       </c>
@@ -21454,7 +21469,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:5">
       <c r="A335" t="s">
         <v>1124</v>
       </c>
@@ -21465,7 +21480,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:5">
       <c r="A336" t="s">
         <v>1125</v>
       </c>
@@ -21476,7 +21491,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:5">
       <c r="A337" t="s">
         <v>1126</v>
       </c>
@@ -21487,7 +21502,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:5">
       <c r="A338" t="s">
         <v>1127</v>
       </c>
@@ -21498,7 +21513,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:5">
       <c r="A339" t="s">
         <v>1128</v>
       </c>
@@ -21515,7 +21530,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:5">
       <c r="A340" s="8" t="s">
         <v>1129</v>
       </c>
@@ -21530,7 +21545,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:5">
       <c r="A341" t="s">
         <v>1130</v>
       </c>
@@ -21544,7 +21559,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:5">
       <c r="A342" t="s">
         <v>1132</v>
       </c>
@@ -21558,7 +21573,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:5">
       <c r="A343" t="s">
         <v>1104</v>
       </c>
@@ -21569,7 +21584,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="344" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:5" ht="31">
       <c r="A344" s="8" t="s">
         <v>1133</v>
       </c>
@@ -21586,7 +21601,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:5">
       <c r="A345" t="s">
         <v>1165</v>
       </c>
@@ -21597,7 +21612,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:5">
       <c r="A346" t="s">
         <v>1155</v>
       </c>
@@ -21608,7 +21623,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="347" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:5" ht="31">
       <c r="A347" t="s">
         <v>1166</v>
       </c>
@@ -21622,12 +21637,12 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:5">
       <c r="A348" s="1" t="s">
         <v>1143</v>
       </c>
     </row>
-    <row r="349" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:5" ht="31">
       <c r="A349" s="8" t="s">
         <v>1143</v>
       </c>
@@ -21644,7 +21659,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="350" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:5" ht="31">
       <c r="A350" s="1" t="s">
         <v>1169</v>
       </c>
@@ -21652,7 +21667,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="351" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:5" ht="31">
       <c r="A351" t="s">
         <v>1156</v>
       </c>
@@ -21666,7 +21681,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:5">
       <c r="A352" t="s">
         <v>1157</v>
       </c>
@@ -21680,7 +21695,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:4">
       <c r="A353" t="s">
         <v>1184</v>
       </c>
@@ -21694,7 +21709,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:4">
       <c r="A354" t="s">
         <v>1158</v>
       </c>
@@ -21708,7 +21723,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:4">
       <c r="A355" t="s">
         <v>1159</v>
       </c>
@@ -21722,7 +21737,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:4">
       <c r="A356" t="s">
         <v>1168</v>
       </c>
@@ -21736,7 +21751,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="357" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:4" ht="31">
       <c r="A357" t="s">
         <v>1161</v>
       </c>
@@ -21750,7 +21765,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:4">
       <c r="A358" t="s">
         <v>1162</v>
       </c>
@@ -21764,7 +21779,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:4">
       <c r="A359" t="s">
         <v>1163</v>
       </c>
@@ -21778,7 +21793,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:4" ht="31">
       <c r="A360" t="s">
         <v>1167</v>
       </c>
@@ -21792,7 +21807,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:4">
       <c r="A361" t="s">
         <v>1164</v>
       </c>
@@ -21806,7 +21821,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:4">
       <c r="A362" t="s">
         <v>1170</v>
       </c>
@@ -21817,7 +21832,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:4">
       <c r="A363" t="s">
         <v>1176</v>
       </c>
@@ -21831,7 +21846,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:4">
       <c r="A364" t="s">
         <v>1177</v>
       </c>
@@ -21845,7 +21860,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="365" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:4" ht="31">
       <c r="A365" t="s">
         <v>1182</v>
       </c>
@@ -21859,7 +21874,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="366" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:4" ht="31">
       <c r="A366" t="s">
         <v>1178</v>
       </c>
@@ -21873,7 +21888,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:4">
       <c r="A367" t="s">
         <v>1179</v>
       </c>
@@ -21887,7 +21902,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:4">
       <c r="A368" t="s">
         <v>1180</v>
       </c>
@@ -21901,7 +21916,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:5">
       <c r="A369" t="s">
         <v>1181</v>
       </c>
@@ -21915,7 +21930,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:5">
       <c r="A370" s="1" t="s">
         <v>1173</v>
       </c>
@@ -21923,7 +21938,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:5">
       <c r="A371" t="s">
         <v>1173</v>
       </c>
@@ -21937,19 +21952,19 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:5">
       <c r="A373" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="374" spans="1:5" ht="78" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A374" s="62" t="s">
+    <row r="374" spans="1:5" ht="78" customHeight="1">
+      <c r="A374" s="65" t="s">
         <v>1260</v>
       </c>
-      <c r="B374" s="62"/>
-      <c r="C374" s="62"/>
-      <c r="D374" s="62"/>
-      <c r="E374" s="62"/>
+      <c r="B374" s="65"/>
+      <c r="C374" s="65"/>
+      <c r="D374" s="65"/>
+      <c r="E374" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -21960,19 +21975,19 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
   <cols>
     <col min="2" max="2" width="98.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="26" t="s">
         <v>1252</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" ht="29">
       <c r="A2" s="27" t="s">
         <v>11</v>
       </c>
@@ -21980,7 +21995,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="29">
       <c r="A3" s="29" t="s">
         <v>538</v>
       </c>
@@ -21988,7 +22003,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2">
       <c r="A4" s="27" t="s">
         <v>21</v>
       </c>
@@ -21996,7 +22011,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2">
       <c r="A5" s="29" t="s">
         <v>540</v>
       </c>
@@ -22004,15 +22019,15 @@
         <v>541</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2">
       <c r="A6" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="63" t="s">
+      <c r="B6" s="61" t="s">
         <v>1286</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" ht="29">
       <c r="A7" s="29" t="s">
         <v>542</v>
       </c>
@@ -22020,7 +22035,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2">
       <c r="A8" s="27" t="s">
         <v>543</v>
       </c>
@@ -22028,7 +22043,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2">
       <c r="A9" s="29" t="s">
         <v>545</v>
       </c>
@@ -22036,23 +22051,23 @@
         <v>546</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2">
       <c r="A10" s="26" t="s">
         <v>547</v>
       </c>
-      <c r="B10" s="63" t="s">
+      <c r="B10" s="61" t="s">
         <v>1285</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2">
       <c r="A11" s="26"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2">
       <c r="A12" s="26" t="s">
         <v>1251</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" ht="25">
       <c r="A13" s="29" t="s">
         <v>553</v>
       </c>
@@ -22060,7 +22075,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2">
       <c r="A14" s="27" t="s">
         <v>554</v>
       </c>
@@ -22068,7 +22083,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2">
       <c r="A15" s="29" t="s">
         <v>557</v>
       </c>
@@ -22076,7 +22091,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2">
       <c r="A16" s="27" t="s">
         <v>558</v>
       </c>
@@ -22084,7 +22099,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2">
       <c r="A17" s="29" t="s">
         <v>559</v>
       </c>
@@ -22092,24 +22107,24 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="63"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2">
+      <c r="A18" s="61"/>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="63" t="s">
+      <c r="B19" s="61" t="s">
         <v>1254</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B20" s="63" t="s">
+    <row r="20" spans="1:2">
+      <c r="B20" s="61" t="s">
         <v>1255</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B21" s="63" t="s">
+    <row r="21" spans="1:2">
+      <c r="B21" s="61" t="s">
         <v>1288</v>
       </c>
     </row>
@@ -22119,55 +22134,55 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="114" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>1257</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" ht="31">
       <c r="A2" s="21" t="s">
         <v>1291</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="30" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" ht="29">
       <c r="A3" s="32" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="30" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" ht="29">
       <c r="A4" s="32" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" ht="29">
       <c r="A5" s="32" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" ht="29">
       <c r="A6" s="32" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" ht="29">
       <c r="A7" s="31" t="s">
         <v>1290</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" ht="29">
       <c r="A8" s="32" t="s">
         <v>552</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A1:A6">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:A6">
     <sortCondition ref="A1"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/chapter2/Brundrett and Tedersoo 2018 - mycorrhizal associations.xlsx
+++ b/data/chapter2/Brundrett and Tedersoo 2018 - mycorrhizal associations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90963425_westernsydney_edu_au/Documents/PhD/code/data/chapter2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_9EE980E2FD5D26AFDFEDEA635E1132CB8726D636" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1613E9C1-AFA1-4AD8-8784-E6DED30E6CAB}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_9EE980E2FD5D26AFDFEDEA635E1132CB8726D636" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF889681-845B-4B0E-AD38-94737A5407DF}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Article Information" sheetId="7" r:id="rId1"/>
@@ -4585,7 +4585,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -4603,41 +4603,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFC4D79B"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FFC4D79B"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFC4D79B"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FFC4D79B"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFC4D79B"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFC4D79B"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFC4D79B"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -4652,7 +4617,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4718,43 +4683,10 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="15" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4768,9 +4700,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4791,11 +4720,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4803,7 +4747,80 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="12">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFEBF1DE"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFC4D79B"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4D79B"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color rgb="FFC4D79B"/>
+        </left>
+        <top style="medium">
+          <color rgb="FFC4D79B"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC4D79B"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <border outline="0">
         <right style="thin">
@@ -4842,7 +4859,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:I439" totalsRowShown="0" headerRowDxfId="1" tableBorderDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:I439" totalsRowShown="0" headerRowDxfId="11" tableBorderDxfId="10">
   <autoFilter ref="A1:I439" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I439">
     <sortCondition ref="B1:B439"/>
@@ -4859,6 +4876,24 @@
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2922BC0C-E417-4658-AC0E-62ECDF39ADC6}" name="Table2" displayName="Table2" ref="A2:F89" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="8" tableBorderDxfId="9">
+  <autoFilter ref="A2:F89" xr:uid="{2922BC0C-E417-4658-AC0E-62ECDF39ADC6}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:F89">
+    <sortCondition ref="B2:B89"/>
+  </sortState>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{0BA76706-F6AC-4480-A1EA-EFC458A86717}" name="Order" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{5641DCB1-A433-40BD-9ED9-D33902929B8C}" name="Family" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{DAAE68C8-09E1-4B56-912D-11D87EB83220}" name="Habit" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{2BC3EF26-068C-475F-91C7-4E8D11F95517}" name="Ecology" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{C1FBDF6D-8E5A-4A09-BBA3-846E464D6CA5}" name="NM-AM" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{0B4BCA8E-55FF-4900-A159-74CFB7CBAE73}" name="NM" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -5165,12 +5200,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="36" customHeight="1">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="48" t="s">
         <v>1289</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="22" customHeight="1">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="47" t="s">
         <v>1238</v>
       </c>
     </row>
@@ -5332,7 +5367,7 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="62" t="s">
+      <c r="K1" s="50" t="s">
         <v>1246</v>
       </c>
     </row>
@@ -6304,7 +6339,7 @@
       <c r="F42" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="H42" s="55"/>
+      <c r="H42" s="43"/>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
@@ -7372,56 +7407,56 @@
       </c>
     </row>
     <row r="90" spans="1:9">
-      <c r="A90" s="58" t="s">
+      <c r="A90" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="B90" s="58" t="s">
+      <c r="B90" s="46" t="s">
         <v>148</v>
       </c>
-      <c r="C90" s="58">
+      <c r="C90" s="46">
         <v>195</v>
       </c>
-      <c r="D90" s="58">
+      <c r="D90" s="46">
         <v>2</v>
       </c>
-      <c r="E90" s="58">
+      <c r="E90" s="46">
         <v>71</v>
       </c>
-      <c r="F90" s="58" t="s">
+      <c r="F90" s="46" t="s">
         <v>149</v>
       </c>
-      <c r="G90" s="58"/>
+      <c r="G90" s="46"/>
       <c r="H90" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="I90" s="58" t="s">
+      <c r="I90" s="46" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="91" spans="1:9">
-      <c r="A91" s="58" t="s">
+      <c r="A91" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="B91" s="58" t="s">
+      <c r="B91" s="46" t="s">
         <v>148</v>
       </c>
-      <c r="C91" s="58">
+      <c r="C91" s="46">
         <v>195</v>
       </c>
-      <c r="D91" s="58">
+      <c r="D91" s="46">
         <v>2</v>
       </c>
-      <c r="E91" s="58">
+      <c r="E91" s="46">
         <v>20</v>
       </c>
-      <c r="F91" s="58" t="s">
-        <v>11</v>
-      </c>
-      <c r="G91" s="58"/>
+      <c r="F91" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="G91" s="46"/>
       <c r="H91" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="I91" s="58" t="s">
+      <c r="I91" s="46" t="s">
         <v>1283</v>
       </c>
     </row>
@@ -7459,7 +7494,7 @@
       <c r="D93" s="5">
         <v>3</v>
       </c>
-      <c r="E93" s="56"/>
+      <c r="E93" s="44"/>
       <c r="F93" s="5" t="s">
         <v>12</v>
       </c>
@@ -8263,7 +8298,7 @@
       <c r="G127" s="8" t="s">
         <v>1225</v>
       </c>
-      <c r="H127" s="63" t="s">
+      <c r="H127" s="51" t="s">
         <v>1276</v>
       </c>
       <c r="I127" s="8" t="s">
@@ -15581,1621 +15616,1624 @@
   <dimension ref="A1:G90"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.9140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.9140625" customWidth="1"/>
+    <col min="5" max="5" width="11.08203125" customWidth="1"/>
+    <col min="6" max="6" width="8.9140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="82" customHeight="1" thickBot="1">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="52" t="s">
         <v>560</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
       <c r="G1" s="8" t="s">
         <v>1261</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="16" thickBot="1">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="37" t="s">
+      <c r="B2" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="58" t="s">
         <v>561</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="D2" s="58" t="s">
         <v>562</v>
       </c>
-      <c r="E2" s="52" t="s">
+      <c r="E2" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="58" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="16" thickBot="1">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>563</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>564</v>
+      </c>
+      <c r="E3" s="36">
+        <v>2</v>
+      </c>
+      <c r="F3" s="55"/>
+    </row>
+    <row r="4" spans="1:7" ht="16" thickBot="1">
+      <c r="A4" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>590</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>591</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>592</v>
+      </c>
+      <c r="E4" s="55"/>
+      <c r="F4" s="36">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="16" thickBot="1">
+      <c r="A5" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>563</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>564</v>
+      </c>
+      <c r="E5" s="35">
+        <v>115</v>
+      </c>
+      <c r="F5" s="54"/>
+    </row>
+    <row r="6" spans="1:7" ht="16" thickBot="1">
+      <c r="A6" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="36" t="s">
+        <v>593</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>594</v>
+      </c>
+      <c r="D6" s="36" t="s">
+        <v>595</v>
+      </c>
+      <c r="E6" s="55"/>
+      <c r="F6" s="36">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="16" thickBot="1">
+      <c r="A7" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>563</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="E7" s="54"/>
+      <c r="F7" s="35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16" thickBot="1">
+      <c r="A8" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>563</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>564</v>
+      </c>
+      <c r="E8" s="36">
+        <v>56</v>
+      </c>
+      <c r="F8" s="55"/>
+    </row>
+    <row r="9" spans="1:7" ht="16" thickBot="1">
+      <c r="A9" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>571</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>563</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>572</v>
+      </c>
+      <c r="E9" s="35">
+        <v>1300</v>
+      </c>
+      <c r="F9" s="54"/>
+    </row>
+    <row r="10" spans="1:7" ht="16" thickBot="1">
+      <c r="A10" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>622</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>573</v>
+      </c>
+      <c r="E10" s="55"/>
+      <c r="F10" s="36">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="16" thickBot="1">
+      <c r="A11" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>563</v>
+      </c>
+      <c r="D11" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="E11" s="54"/>
+      <c r="F11" s="35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="16" thickBot="1">
+      <c r="A12" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>563</v>
+      </c>
+      <c r="D12" s="35" t="s">
+        <v>617</v>
+      </c>
+      <c r="E12" s="54"/>
+      <c r="F12" s="35">
+        <v>3628</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="16" thickBot="1">
+      <c r="A13" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="B13" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>563</v>
+      </c>
+      <c r="D13" s="35" t="s">
+        <v>570</v>
+      </c>
+      <c r="E13" s="56">
+        <v>3475</v>
+      </c>
+      <c r="F13" s="54"/>
+    </row>
+    <row r="14" spans="1:7" ht="16" thickBot="1">
+      <c r="A14" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" s="36" t="s">
+        <v>563</v>
+      </c>
+      <c r="D14" s="36" t="s">
+        <v>564</v>
+      </c>
+      <c r="E14" s="36">
+        <v>1</v>
+      </c>
+      <c r="F14" s="55"/>
+    </row>
+    <row r="15" spans="1:7" ht="16" thickBot="1">
+      <c r="A15" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>563</v>
+      </c>
+      <c r="D15" s="35" t="s">
+        <v>598</v>
+      </c>
+      <c r="E15" s="54"/>
+      <c r="F15" s="35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="16" thickBot="1">
+      <c r="A16" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="36" t="s">
+        <v>623</v>
+      </c>
+      <c r="C16" s="36" t="s">
+        <v>563</v>
+      </c>
+      <c r="D16" s="36" t="s">
+        <v>573</v>
+      </c>
+      <c r="E16" s="36">
+        <v>75</v>
+      </c>
+      <c r="F16" s="55"/>
+    </row>
+    <row r="17" spans="1:6" ht="16" thickBot="1">
+      <c r="A17" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>587</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>618</v>
+      </c>
+      <c r="E17" s="55"/>
+      <c r="F17" s="36">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="16" thickBot="1">
+      <c r="A18" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="35" t="s">
+        <v>563</v>
+      </c>
+      <c r="D18" s="35" t="s">
+        <v>596</v>
+      </c>
+      <c r="E18" s="54"/>
+      <c r="F18" s="35">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="16" thickBot="1">
+      <c r="A19" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="B19" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="C19" s="35" t="s">
+        <v>599</v>
+      </c>
+      <c r="D19" s="35" t="s">
+        <v>598</v>
+      </c>
+      <c r="E19" s="54"/>
+      <c r="F19" s="35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="16" thickBot="1">
+      <c r="A20" s="36" t="s">
+        <v>155</v>
+      </c>
+      <c r="B20" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="C20" s="36" t="s">
+        <v>563</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>564</v>
+      </c>
+      <c r="E20" s="55"/>
+      <c r="F20" s="36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="16" thickBot="1">
+      <c r="A21" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="C21" s="35" t="s">
+        <v>594</v>
+      </c>
+      <c r="D21" s="35" t="s">
+        <v>592</v>
+      </c>
+      <c r="E21" s="54"/>
+      <c r="F21" s="35">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="16" thickBot="1">
+      <c r="A22" s="36" t="s">
+        <v>170</v>
+      </c>
+      <c r="B22" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="C22" s="36" t="s">
+        <v>563</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>577</v>
+      </c>
+      <c r="E22" s="55"/>
+      <c r="F22" s="36">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="16" thickBot="1">
+      <c r="A23" s="36" t="s">
+        <v>173</v>
+      </c>
+      <c r="B23" s="36" t="s">
+        <v>626</v>
+      </c>
+      <c r="C23" s="36" t="s">
+        <v>240</v>
+      </c>
+      <c r="D23" s="36" t="s">
+        <v>567</v>
+      </c>
+      <c r="E23" s="55"/>
+      <c r="F23" s="36">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="16" thickBot="1">
+      <c r="A24" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="35" t="s">
+        <v>181</v>
+      </c>
+      <c r="C24" s="35" t="s">
+        <v>594</v>
+      </c>
+      <c r="D24" s="35" t="s">
+        <v>611</v>
+      </c>
+      <c r="E24" s="35" t="s">
+        <v>612</v>
+      </c>
+      <c r="F24" s="35">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="16" thickBot="1">
+      <c r="A25" s="36" t="s">
+        <v>188</v>
+      </c>
+      <c r="B25" s="36" t="s">
+        <v>189</v>
+      </c>
+      <c r="C25" s="36" t="s">
+        <v>563</v>
+      </c>
+      <c r="D25" s="36" t="s">
+        <v>570</v>
+      </c>
+      <c r="E25" s="36">
+        <v>230</v>
+      </c>
+      <c r="F25" s="55"/>
+    </row>
+    <row r="26" spans="1:6" ht="16" thickBot="1">
+      <c r="A26" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>563</v>
+      </c>
+      <c r="D26" s="35" t="s">
+        <v>573</v>
+      </c>
+      <c r="E26" s="54"/>
+      <c r="F26" s="35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="16" thickBot="1">
+      <c r="A27" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="36" t="s">
+        <v>193</v>
+      </c>
+      <c r="C27" s="36" t="s">
+        <v>563</v>
+      </c>
+      <c r="D27" s="36" t="s">
+        <v>567</v>
+      </c>
+      <c r="E27" s="55"/>
+      <c r="F27" s="36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="16" thickBot="1">
+      <c r="A28" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="B28" s="36" t="s">
+        <v>194</v>
+      </c>
+      <c r="C28" s="36" t="s">
+        <v>578</v>
+      </c>
+      <c r="D28" s="36" t="s">
+        <v>579</v>
+      </c>
+      <c r="E28" s="36">
+        <v>5500</v>
+      </c>
+      <c r="F28" s="55"/>
+    </row>
+    <row r="29" spans="1:6" ht="16" thickBot="1">
+      <c r="A29" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="B29" s="36" t="s">
+        <v>196</v>
+      </c>
+      <c r="C29" s="36" t="s">
+        <v>597</v>
+      </c>
+      <c r="D29" s="36" t="s">
+        <v>567</v>
+      </c>
+      <c r="E29" s="55"/>
+      <c r="F29" s="36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="16" thickBot="1">
+      <c r="A30" s="35" t="s">
+        <v>575</v>
+      </c>
+      <c r="B30" s="35" t="s">
+        <v>198</v>
+      </c>
+      <c r="C30" s="35" t="s">
+        <v>563</v>
+      </c>
+      <c r="D30" s="35" t="s">
+        <v>576</v>
+      </c>
+      <c r="E30" s="54"/>
+      <c r="F30" s="35">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="16" thickBot="1">
+      <c r="A31" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" s="35" t="s">
+        <v>213</v>
+      </c>
+      <c r="C31" s="35" t="s">
+        <v>563</v>
+      </c>
+      <c r="D31" s="35" t="s">
+        <v>598</v>
+      </c>
+      <c r="E31" s="54"/>
+      <c r="F31" s="35">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="16" thickBot="1">
+      <c r="A32" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" s="36" t="s">
+        <v>214</v>
+      </c>
+      <c r="C32" s="36" t="s">
+        <v>599</v>
+      </c>
+      <c r="D32" s="36" t="s">
+        <v>598</v>
+      </c>
+      <c r="E32" s="55"/>
+      <c r="F32" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="16" thickBot="1">
+      <c r="A33" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" s="36" t="s">
+        <v>226</v>
+      </c>
+      <c r="C33" s="36" t="s">
+        <v>584</v>
+      </c>
+      <c r="D33" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="E33" s="36">
+        <v>242</v>
+      </c>
+      <c r="F33" s="55"/>
+    </row>
+    <row r="34" spans="1:6" ht="16" thickBot="1">
+      <c r="A34" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="B34" s="36" t="s">
+        <v>586</v>
+      </c>
+      <c r="C34" s="36" t="s">
+        <v>587</v>
+      </c>
+      <c r="D34" s="36" t="s">
+        <v>588</v>
+      </c>
+      <c r="E34" s="55"/>
+      <c r="F34" s="36">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="16" thickBot="1">
+      <c r="A35" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" s="35" t="s">
+        <v>244</v>
+      </c>
+      <c r="C35" s="35" t="s">
+        <v>600</v>
+      </c>
+      <c r="D35" s="35" t="s">
+        <v>601</v>
+      </c>
+      <c r="E35" s="54"/>
+      <c r="F35" s="35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="16" thickBot="1">
+      <c r="A36" s="35" t="s">
+        <v>170</v>
+      </c>
+      <c r="B36" s="35" t="s">
+        <v>265</v>
+      </c>
+      <c r="C36" s="35" t="s">
+        <v>563</v>
+      </c>
+      <c r="D36" s="35" t="s">
+        <v>576</v>
+      </c>
+      <c r="E36" s="54"/>
+      <c r="F36" s="35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="16" thickBot="1">
+      <c r="A37" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="36" t="s">
+        <v>613</v>
+      </c>
+      <c r="C37" s="36" t="s">
+        <v>563</v>
+      </c>
+      <c r="D37" s="36" t="s">
+        <v>564</v>
+      </c>
+      <c r="E37" s="36">
+        <v>50</v>
+      </c>
+      <c r="F37" s="55"/>
+    </row>
+    <row r="38" spans="1:6" ht="16" thickBot="1">
+      <c r="A38" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="35" t="s">
+        <v>624</v>
+      </c>
+      <c r="C38" s="35" t="s">
+        <v>563</v>
+      </c>
+      <c r="D38" s="35" t="s">
+        <v>564</v>
+      </c>
+      <c r="E38" s="54"/>
+      <c r="F38" s="35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="16" thickBot="1">
+      <c r="A39" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="B39" s="35" t="s">
+        <v>276</v>
+      </c>
+      <c r="C39" s="35" t="s">
+        <v>563</v>
+      </c>
+      <c r="D39" s="35" t="s">
+        <v>564</v>
+      </c>
+      <c r="E39" s="54"/>
+      <c r="F39" s="35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="16" thickBot="1">
+      <c r="A40" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="B40" s="36" t="s">
+        <v>568</v>
+      </c>
+      <c r="C40" s="36" t="s">
+        <v>563</v>
+      </c>
+      <c r="D40" s="36" t="s">
+        <v>567</v>
+      </c>
+      <c r="E40" s="55"/>
+      <c r="F40" s="36">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="16" thickBot="1">
+      <c r="A41" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B41" s="36" t="s">
+        <v>278</v>
+      </c>
+      <c r="C41" s="36" t="s">
+        <v>563</v>
+      </c>
+      <c r="D41" s="36" t="s">
+        <v>574</v>
+      </c>
+      <c r="E41" s="55"/>
+      <c r="F41" s="36">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="16" thickBot="1">
+      <c r="A42" s="35" t="s">
+        <v>620</v>
+      </c>
+      <c r="B42" s="35" t="s">
+        <v>621</v>
+      </c>
+      <c r="C42" s="35" t="s">
+        <v>591</v>
+      </c>
+      <c r="D42" s="35" t="s">
+        <v>611</v>
+      </c>
+      <c r="E42" s="35">
+        <v>300</v>
+      </c>
+      <c r="F42" s="54"/>
+    </row>
+    <row r="43" spans="1:6" ht="16" thickBot="1">
+      <c r="A43" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="B43" s="36" t="s">
+        <v>293</v>
+      </c>
+      <c r="C43" s="36" t="s">
+        <v>580</v>
+      </c>
+      <c r="D43" s="36" t="s">
+        <v>581</v>
+      </c>
+      <c r="E43" s="55"/>
+      <c r="F43" s="36">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="16" thickBot="1">
+      <c r="A44" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="B44" s="35" t="s">
+        <v>294</v>
+      </c>
+      <c r="C44" s="35" t="s">
+        <v>563</v>
+      </c>
+      <c r="D44" s="35" t="s">
+        <v>564</v>
+      </c>
+      <c r="E44" s="35">
+        <v>34</v>
+      </c>
+      <c r="F44" s="54"/>
+    </row>
+    <row r="45" spans="1:6" ht="16" thickBot="1">
+      <c r="A45" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="B45" s="35" t="s">
+        <v>565</v>
+      </c>
+      <c r="C45" s="35" t="s">
+        <v>566</v>
+      </c>
+      <c r="D45" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="E45" s="54"/>
+      <c r="F45" s="35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="16" thickBot="1">
+      <c r="A46" s="36" t="s">
+        <v>620</v>
+      </c>
+      <c r="B46" s="36" t="s">
+        <v>307</v>
+      </c>
+      <c r="C46" s="36" t="s">
+        <v>563</v>
+      </c>
+      <c r="D46" s="36" t="s">
+        <v>567</v>
+      </c>
+      <c r="E46" s="55"/>
+      <c r="F46" s="36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="16" thickBot="1">
+      <c r="A47" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" s="36" t="s">
+        <v>308</v>
+      </c>
+      <c r="C47" s="36" t="s">
+        <v>563</v>
+      </c>
+      <c r="D47" s="36" t="s">
+        <v>598</v>
+      </c>
+      <c r="E47" s="55"/>
+      <c r="F47" s="36">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="16" thickBot="1">
+      <c r="A48" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B48" s="36" t="s">
+        <v>312</v>
+      </c>
+      <c r="C48" s="36" t="s">
+        <v>563</v>
+      </c>
+      <c r="D48" s="36" t="s">
+        <v>564</v>
+      </c>
+      <c r="E48" s="55"/>
+      <c r="F48" s="36">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="16" thickBot="1">
+      <c r="A49" s="36" t="s">
+        <v>176</v>
+      </c>
+      <c r="B49" s="36" t="s">
+        <v>316</v>
+      </c>
+      <c r="C49" s="36" t="s">
+        <v>594</v>
+      </c>
+      <c r="D49" s="36" t="s">
+        <v>589</v>
+      </c>
+      <c r="E49" s="55"/>
+      <c r="F49" s="36">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="16" thickBot="1">
+      <c r="A50" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="B50" s="35" t="s">
+        <v>320</v>
+      </c>
+      <c r="C50" s="35" t="s">
+        <v>609</v>
+      </c>
+      <c r="D50" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="E50" s="54"/>
+      <c r="F50" s="35">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="16" thickBot="1">
+      <c r="A51" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B51" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="C51" s="35" t="s">
+        <v>563</v>
+      </c>
+      <c r="D51" s="35" t="s">
+        <v>564</v>
+      </c>
+      <c r="E51" s="35">
+        <v>60</v>
+      </c>
+      <c r="F51" s="54"/>
+    </row>
+    <row r="52" spans="1:6" ht="16" thickBot="1">
+      <c r="A52" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="B52" s="36" t="s">
+        <v>341</v>
+      </c>
+      <c r="C52" s="36" t="s">
+        <v>609</v>
+      </c>
+      <c r="D52" s="36" t="s">
+        <v>567</v>
+      </c>
+      <c r="E52" s="55"/>
+      <c r="F52" s="36">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="16" thickBot="1">
+      <c r="A53" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="B53" s="36" t="s">
+        <v>342</v>
+      </c>
+      <c r="C53" s="36" t="s">
+        <v>597</v>
+      </c>
+      <c r="D53" s="36" t="s">
+        <v>567</v>
+      </c>
+      <c r="E53" s="55"/>
+      <c r="F53" s="36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="16" thickBot="1">
+      <c r="A54" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B54" s="36" t="s">
+        <v>343</v>
+      </c>
+      <c r="C54" s="36" t="s">
+        <v>563</v>
+      </c>
+      <c r="D54" s="36" t="s">
+        <v>602</v>
+      </c>
+      <c r="E54" s="55"/>
+      <c r="F54" s="36">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="16" thickBot="1">
+      <c r="A55" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="B55" s="35" t="s">
+        <v>352</v>
+      </c>
+      <c r="C55" s="35" t="s">
+        <v>584</v>
+      </c>
+      <c r="D55" s="35" t="s">
+        <v>585</v>
+      </c>
+      <c r="E55" s="54"/>
+      <c r="F55" s="35">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="16" thickBot="1">
+      <c r="A56" s="36" t="s">
+        <v>357</v>
+      </c>
+      <c r="B56" s="36" t="s">
+        <v>358</v>
+      </c>
+      <c r="C56" s="36" t="s">
+        <v>563</v>
+      </c>
+      <c r="D56" s="36" t="s">
+        <v>564</v>
+      </c>
+      <c r="E56" s="55"/>
+      <c r="F56" s="36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="16" thickBot="1">
+      <c r="A57" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B57" s="35" t="s">
+        <v>359</v>
+      </c>
+      <c r="C57" s="35" t="s">
+        <v>240</v>
+      </c>
+      <c r="D57" s="35" t="s">
+        <v>598</v>
+      </c>
+      <c r="E57" s="54"/>
+      <c r="F57" s="35">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="16" thickBot="1">
+      <c r="A58" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B58" s="36" t="s">
+        <v>363</v>
+      </c>
+      <c r="C58" s="36" t="s">
+        <v>584</v>
+      </c>
+      <c r="D58" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="E58" s="55"/>
+      <c r="F58" s="36">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="16" thickBot="1">
+      <c r="A59" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B59" s="35" t="s">
         <v>364</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C59" s="35" t="s">
         <v>563</v>
       </c>
-      <c r="D3" s="39" t="s">
+      <c r="D59" s="35" t="s">
         <v>564</v>
       </c>
-      <c r="E3" s="40">
+      <c r="E59" s="35">
         <v>70</v>
       </c>
-      <c r="F3" s="41"/>
-    </row>
-    <row r="4" spans="1:7" ht="16" thickBot="1">
-      <c r="A4" s="42" t="s">
-        <v>155</v>
-      </c>
-      <c r="B4" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="C4" s="44" t="s">
+      <c r="F59" s="54"/>
+    </row>
+    <row r="60" spans="1:6" ht="16" thickBot="1">
+      <c r="A60" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="B60" s="36" t="s">
+        <v>608</v>
+      </c>
+      <c r="C60" s="36" t="s">
+        <v>584</v>
+      </c>
+      <c r="D60" s="36" t="s">
+        <v>567</v>
+      </c>
+      <c r="E60" s="55"/>
+      <c r="F60" s="36">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="16" thickBot="1">
+      <c r="A61" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="B61" s="36" t="s">
+        <v>371</v>
+      </c>
+      <c r="C61" s="36" t="s">
+        <v>584</v>
+      </c>
+      <c r="D61" s="36" t="s">
+        <v>567</v>
+      </c>
+      <c r="E61" s="55"/>
+      <c r="F61" s="36">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="16" thickBot="1">
+      <c r="A62" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B62" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="C62" s="35" t="s">
         <v>563</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="D62" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="E62" s="54"/>
+      <c r="F62" s="35">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="16" thickBot="1">
+      <c r="A63" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="B63" s="35" t="s">
+        <v>380</v>
+      </c>
+      <c r="C63" s="35" t="s">
+        <v>563</v>
+      </c>
+      <c r="D63" s="35" t="s">
+        <v>589</v>
+      </c>
+      <c r="E63" s="35">
+        <v>775</v>
+      </c>
+      <c r="F63" s="54"/>
+    </row>
+    <row r="64" spans="1:6" ht="16" thickBot="1">
+      <c r="A64" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B64" s="35" t="s">
+        <v>410</v>
+      </c>
+      <c r="C64" s="35" t="s">
+        <v>569</v>
+      </c>
+      <c r="D64" s="35" t="s">
+        <v>589</v>
+      </c>
+      <c r="E64" s="54"/>
+      <c r="F64" s="35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="16" thickBot="1">
+      <c r="A65" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="B65" s="35" t="s">
+        <v>414</v>
+      </c>
+      <c r="C65" s="35" t="s">
+        <v>569</v>
+      </c>
+      <c r="D65" s="35" t="s">
+        <v>570</v>
+      </c>
+      <c r="E65" s="35">
+        <v>3700</v>
+      </c>
+      <c r="F65" s="54"/>
+    </row>
+    <row r="66" spans="1:6" ht="16" thickBot="1">
+      <c r="A66" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B66" s="36" t="s">
+        <v>419</v>
+      </c>
+      <c r="C66" s="36" t="s">
+        <v>591</v>
+      </c>
+      <c r="D66" s="36" t="s">
+        <v>603</v>
+      </c>
+      <c r="E66" s="36">
+        <v>725</v>
+      </c>
+      <c r="F66" s="55"/>
+    </row>
+    <row r="67" spans="1:6" ht="16" thickBot="1">
+      <c r="A67" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B67" s="35" t="s">
+        <v>421</v>
+      </c>
+      <c r="C67" s="35" t="s">
+        <v>563</v>
+      </c>
+      <c r="D67" s="35" t="s">
         <v>564</v>
       </c>
-      <c r="E4" s="45"/>
-      <c r="F4" s="44">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="16" thickBot="1">
-      <c r="A5" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="B5" s="39" t="s">
-        <v>565</v>
-      </c>
-      <c r="C5" s="40" t="s">
-        <v>566</v>
-      </c>
-      <c r="D5" s="40" t="s">
+      <c r="E67" s="35">
+        <v>300</v>
+      </c>
+      <c r="F67" s="54"/>
+    </row>
+    <row r="68" spans="1:6" ht="16" thickBot="1">
+      <c r="A68" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B68" s="35" t="s">
+        <v>424</v>
+      </c>
+      <c r="C68" s="35" t="s">
+        <v>604</v>
+      </c>
+      <c r="D68" s="35" t="s">
+        <v>589</v>
+      </c>
+      <c r="E68" s="54"/>
+      <c r="F68" s="35">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="16" thickBot="1">
+      <c r="A69" s="36" t="s">
+        <v>170</v>
+      </c>
+      <c r="B69" s="36" t="s">
+        <v>425</v>
+      </c>
+      <c r="C69" s="36" t="s">
+        <v>563</v>
+      </c>
+      <c r="D69" s="36" t="s">
+        <v>564</v>
+      </c>
+      <c r="E69" s="36">
+        <v>34</v>
+      </c>
+      <c r="F69" s="55"/>
+    </row>
+    <row r="70" spans="1:6" ht="16" thickBot="1">
+      <c r="A70" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B70" s="36" t="s">
+        <v>605</v>
+      </c>
+      <c r="C70" s="36" t="s">
+        <v>569</v>
+      </c>
+      <c r="D70" s="36" t="s">
+        <v>606</v>
+      </c>
+      <c r="E70" s="36">
+        <v>115</v>
+      </c>
+      <c r="F70" s="55"/>
+    </row>
+    <row r="71" spans="1:6" ht="16" thickBot="1">
+      <c r="A71" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B71" s="36" t="s">
+        <v>427</v>
+      </c>
+      <c r="C71" s="36" t="s">
+        <v>563</v>
+      </c>
+      <c r="D71" s="36" t="s">
+        <v>573</v>
+      </c>
+      <c r="E71" s="55"/>
+      <c r="F71" s="36">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="16" thickBot="1">
+      <c r="A72" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="B72" s="35" t="s">
+        <v>428</v>
+      </c>
+      <c r="C72" s="35" t="s">
+        <v>563</v>
+      </c>
+      <c r="D72" s="35" t="s">
+        <v>564</v>
+      </c>
+      <c r="E72" s="35">
+        <v>110</v>
+      </c>
+      <c r="F72" s="54"/>
+    </row>
+    <row r="73" spans="1:6" ht="16" thickBot="1">
+      <c r="A73" s="35" t="s">
+        <v>357</v>
+      </c>
+      <c r="B73" s="35" t="s">
+        <v>430</v>
+      </c>
+      <c r="C73" s="35" t="s">
+        <v>584</v>
+      </c>
+      <c r="D73" s="35" t="s">
+        <v>585</v>
+      </c>
+      <c r="E73" s="54"/>
+      <c r="F73" s="35">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="16" thickBot="1">
+      <c r="A74" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="B74" s="36" t="s">
+        <v>615</v>
+      </c>
+      <c r="C74" s="36" t="s">
+        <v>584</v>
+      </c>
+      <c r="D74" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="E74" s="55"/>
+      <c r="F74" s="36">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="16" thickBot="1">
+      <c r="A75" s="35" t="s">
+        <v>616</v>
+      </c>
+      <c r="B75" s="35" t="s">
+        <v>433</v>
+      </c>
+      <c r="C75" s="35" t="s">
+        <v>597</v>
+      </c>
+      <c r="D75" s="35" t="s">
         <v>567</v>
       </c>
-      <c r="E5" s="41"/>
-      <c r="F5" s="40">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="25.5" thickBot="1">
-      <c r="A6" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" s="43" t="s">
-        <v>568</v>
-      </c>
-      <c r="C6" s="44" t="s">
+      <c r="E75" s="54"/>
+      <c r="F75" s="35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="16" thickBot="1">
+      <c r="A76" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="B76" s="35" t="s">
+        <v>436</v>
+      </c>
+      <c r="C76" s="35" t="s">
+        <v>594</v>
+      </c>
+      <c r="D76" s="35" t="s">
+        <v>619</v>
+      </c>
+      <c r="E76" s="54"/>
+      <c r="F76" s="35">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="16" thickBot="1">
+      <c r="A77" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="B77" s="35" t="s">
+        <v>582</v>
+      </c>
+      <c r="C77" s="35" t="s">
         <v>563</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="D77" s="35" t="s">
+        <v>583</v>
+      </c>
+      <c r="E77" s="54"/>
+      <c r="F77" s="35">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="16" thickBot="1">
+      <c r="A78" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="B78" s="36" t="s">
+        <v>441</v>
+      </c>
+      <c r="C78" s="36" t="s">
+        <v>584</v>
+      </c>
+      <c r="D78" s="36" t="s">
+        <v>573</v>
+      </c>
+      <c r="E78" s="36">
+        <v>147</v>
+      </c>
+      <c r="F78" s="55"/>
+    </row>
+    <row r="79" spans="1:6" ht="16" thickBot="1">
+      <c r="A79" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B79" s="35" t="s">
+        <v>444</v>
+      </c>
+      <c r="C79" s="35" t="s">
+        <v>600</v>
+      </c>
+      <c r="D79" s="35" t="s">
+        <v>598</v>
+      </c>
+      <c r="E79" s="54"/>
+      <c r="F79" s="54"/>
+    </row>
+    <row r="80" spans="1:6" ht="16" thickBot="1">
+      <c r="A80" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B80" s="36" t="s">
+        <v>448</v>
+      </c>
+      <c r="C80" s="36" t="s">
+        <v>563</v>
+      </c>
+      <c r="D80" s="36" t="s">
+        <v>574</v>
+      </c>
+      <c r="E80" s="55"/>
+      <c r="F80" s="36">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="16" thickBot="1">
+      <c r="A81" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" s="35" t="s">
+        <v>610</v>
+      </c>
+      <c r="C81" s="35" t="s">
+        <v>584</v>
+      </c>
+      <c r="D81" s="35" t="s">
         <v>567</v>
       </c>
-      <c r="E6" s="45"/>
-      <c r="F6" s="44">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="16" thickBot="1">
-      <c r="A7" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" s="39" t="s">
-        <v>414</v>
-      </c>
-      <c r="C7" s="40" t="s">
-        <v>569</v>
-      </c>
-      <c r="D7" s="39" t="s">
-        <v>570</v>
-      </c>
-      <c r="E7" s="40">
-        <v>3700</v>
-      </c>
-      <c r="F7" s="41"/>
-    </row>
-    <row r="8" spans="1:7" ht="16" thickBot="1">
-      <c r="A8" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="43" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="44" t="s">
+      <c r="E81" s="54"/>
+      <c r="F81" s="35">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="16" thickBot="1">
+      <c r="A82" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B82" s="35" t="s">
+        <v>459</v>
+      </c>
+      <c r="C82" s="35" t="s">
         <v>563</v>
       </c>
-      <c r="D8" s="43" t="s">
+      <c r="D82" s="35" t="s">
+        <v>598</v>
+      </c>
+      <c r="E82" s="54"/>
+      <c r="F82" s="35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="16" thickBot="1">
+      <c r="A83" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="B83" s="35" t="s">
+        <v>461</v>
+      </c>
+      <c r="C83" s="35" t="s">
+        <v>563</v>
+      </c>
+      <c r="D83" s="35" t="s">
+        <v>614</v>
+      </c>
+      <c r="E83" s="35">
+        <v>640</v>
+      </c>
+      <c r="F83" s="54"/>
+    </row>
+    <row r="84" spans="1:6" ht="16" thickBot="1">
+      <c r="A84" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B84" s="35" t="s">
+        <v>490</v>
+      </c>
+      <c r="C84" s="35" t="s">
+        <v>584</v>
+      </c>
+      <c r="D84" s="35" t="s">
+        <v>607</v>
+      </c>
+      <c r="E84" s="35">
+        <v>78</v>
+      </c>
+      <c r="F84" s="54"/>
+    </row>
+    <row r="85" spans="1:6" ht="16" thickBot="1">
+      <c r="A85" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="B85" s="36" t="s">
+        <v>512</v>
+      </c>
+      <c r="C85" s="36" t="s">
+        <v>563</v>
+      </c>
+      <c r="D85" s="36" t="s">
         <v>564</v>
       </c>
-      <c r="E8" s="44">
-        <v>2</v>
-      </c>
-      <c r="F8" s="45"/>
-    </row>
-    <row r="9" spans="1:7" ht="16" thickBot="1">
-      <c r="A9" s="38" t="s">
+      <c r="E85" s="55"/>
+      <c r="F85" s="36">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="16" thickBot="1">
+      <c r="A86" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="B86" s="36" t="s">
+        <v>514</v>
+      </c>
+      <c r="C86" s="36" t="s">
+        <v>591</v>
+      </c>
+      <c r="D86" s="36" t="s">
+        <v>589</v>
+      </c>
+      <c r="E86" s="36">
+        <v>2625</v>
+      </c>
+      <c r="F86" s="55"/>
+    </row>
+    <row r="87" spans="1:6" ht="16" thickBot="1">
+      <c r="A87" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="B87" s="35" t="s">
+        <v>526</v>
+      </c>
+      <c r="C87" s="35" t="s">
+        <v>563</v>
+      </c>
+      <c r="D87" s="35" t="s">
+        <v>564</v>
+      </c>
+      <c r="E87" s="54"/>
+      <c r="F87" s="35">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="16" thickBot="1">
+      <c r="A88" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="40" t="s">
+      <c r="B88" s="35" t="s">
+        <v>528</v>
+      </c>
+      <c r="C88" s="35" t="s">
         <v>563</v>
       </c>
-      <c r="D9" s="39" t="s">
-        <v>564</v>
-      </c>
-      <c r="E9" s="40">
-        <v>115</v>
-      </c>
-      <c r="F9" s="41"/>
-    </row>
-    <row r="10" spans="1:7" ht="16" thickBot="1">
-      <c r="A10" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="44" t="s">
-        <v>563</v>
-      </c>
-      <c r="D10" s="43" t="s">
-        <v>564</v>
-      </c>
-      <c r="E10" s="44">
-        <v>56</v>
-      </c>
-      <c r="F10" s="45"/>
-    </row>
-    <row r="11" spans="1:7" ht="16" thickBot="1">
-      <c r="A11" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="39" t="s">
-        <v>571</v>
-      </c>
-      <c r="C11" s="40" t="s">
-        <v>563</v>
-      </c>
-      <c r="D11" s="39" t="s">
-        <v>572</v>
-      </c>
-      <c r="E11" s="40">
-        <v>1300</v>
-      </c>
-      <c r="F11" s="41"/>
-    </row>
-    <row r="12" spans="1:7" ht="16" thickBot="1">
-      <c r="A12" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="C12" s="44" t="s">
-        <v>563</v>
-      </c>
-      <c r="D12" s="43" t="s">
-        <v>564</v>
-      </c>
-      <c r="E12" s="44">
-        <v>1</v>
-      </c>
-      <c r="F12" s="45"/>
-    </row>
-    <row r="13" spans="1:7" ht="16" thickBot="1">
-      <c r="A13" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>190</v>
-      </c>
-      <c r="C13" s="40" t="s">
-        <v>563</v>
-      </c>
-      <c r="D13" s="39" t="s">
+      <c r="D88" s="35" t="s">
         <v>573</v>
       </c>
-      <c r="E13" s="41"/>
-      <c r="F13" s="40">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="16" thickBot="1">
-      <c r="A14" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="43" t="s">
-        <v>278</v>
-      </c>
-      <c r="C14" s="44" t="s">
-        <v>563</v>
-      </c>
-      <c r="D14" s="43" t="s">
-        <v>574</v>
-      </c>
-      <c r="E14" s="45"/>
-      <c r="F14" s="44">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="16" thickBot="1">
-      <c r="A15" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="39" t="s">
-        <v>294</v>
-      </c>
-      <c r="C15" s="40" t="s">
-        <v>563</v>
-      </c>
-      <c r="D15" s="39" t="s">
-        <v>564</v>
-      </c>
-      <c r="E15" s="40">
-        <v>34</v>
-      </c>
-      <c r="F15" s="41"/>
-    </row>
-    <row r="16" spans="1:7" ht="16" thickBot="1">
-      <c r="A16" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="43" t="s">
-        <v>427</v>
-      </c>
-      <c r="C16" s="44" t="s">
-        <v>563</v>
-      </c>
-      <c r="D16" s="43" t="s">
-        <v>573</v>
-      </c>
-      <c r="E16" s="45"/>
-      <c r="F16" s="44">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="16" thickBot="1">
-      <c r="A17" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="39" t="s">
-        <v>428</v>
-      </c>
-      <c r="C17" s="40" t="s">
-        <v>563</v>
-      </c>
-      <c r="D17" s="39" t="s">
-        <v>564</v>
-      </c>
-      <c r="E17" s="40">
-        <v>110</v>
-      </c>
-      <c r="F17" s="41"/>
-    </row>
-    <row r="18" spans="1:6" ht="16" thickBot="1">
-      <c r="A18" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="43" t="s">
-        <v>448</v>
-      </c>
-      <c r="C18" s="44" t="s">
-        <v>563</v>
-      </c>
-      <c r="D18" s="43" t="s">
-        <v>574</v>
-      </c>
-      <c r="E18" s="45"/>
-      <c r="F18" s="44">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="16" thickBot="1">
-      <c r="A19" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" s="39" t="s">
-        <v>528</v>
-      </c>
-      <c r="C19" s="40" t="s">
-        <v>563</v>
-      </c>
-      <c r="D19" s="39" t="s">
-        <v>573</v>
-      </c>
-      <c r="E19" s="41"/>
-      <c r="F19" s="40">
+      <c r="E88" s="54"/>
+      <c r="F88" s="35">
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="16" thickBot="1">
-      <c r="A20" s="42" t="s">
-        <v>188</v>
-      </c>
-      <c r="B20" s="43" t="s">
-        <v>189</v>
-      </c>
-      <c r="C20" s="44" t="s">
-        <v>563</v>
-      </c>
-      <c r="D20" s="43" t="s">
-        <v>570</v>
-      </c>
-      <c r="E20" s="44">
-        <v>230</v>
-      </c>
-      <c r="F20" s="45"/>
-    </row>
-    <row r="21" spans="1:6" ht="16" thickBot="1">
-      <c r="A21" s="38" t="s">
-        <v>575</v>
-      </c>
-      <c r="B21" s="39" t="s">
-        <v>198</v>
-      </c>
-      <c r="C21" s="40" t="s">
-        <v>563</v>
-      </c>
-      <c r="D21" s="39" t="s">
-        <v>576</v>
-      </c>
-      <c r="E21" s="41"/>
-      <c r="F21" s="40">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="16" thickBot="1">
-      <c r="A22" s="42" t="s">
-        <v>170</v>
-      </c>
-      <c r="B22" s="44" t="s">
-        <v>171</v>
-      </c>
-      <c r="C22" s="43" t="s">
-        <v>563</v>
-      </c>
-      <c r="D22" s="43" t="s">
-        <v>577</v>
-      </c>
-      <c r="E22" s="45"/>
-      <c r="F22" s="44">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="16" thickBot="1">
-      <c r="A23" s="38" t="s">
-        <v>170</v>
-      </c>
-      <c r="B23" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="C23" s="40" t="s">
-        <v>563</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>576</v>
-      </c>
-      <c r="E23" s="41"/>
-      <c r="F23" s="40">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="16" thickBot="1">
-      <c r="A24" s="42" t="s">
-        <v>170</v>
-      </c>
-      <c r="B24" s="43" t="s">
-        <v>425</v>
-      </c>
-      <c r="C24" s="44" t="s">
-        <v>563</v>
-      </c>
-      <c r="D24" s="43" t="s">
-        <v>564</v>
-      </c>
-      <c r="E24" s="44">
-        <v>34</v>
-      </c>
-      <c r="F24" s="45"/>
-    </row>
-    <row r="25" spans="1:6" ht="16" thickBot="1">
-      <c r="A25" s="38" t="s">
-        <v>111</v>
-      </c>
-      <c r="B25" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="C25" s="40" t="s">
-        <v>563</v>
-      </c>
-      <c r="D25" s="39" t="s">
-        <v>570</v>
-      </c>
-      <c r="E25" s="46">
-        <v>3475</v>
-      </c>
-      <c r="F25" s="41"/>
-    </row>
-    <row r="26" spans="1:6" ht="16" thickBot="1">
-      <c r="A26" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="B26" s="43" t="s">
-        <v>194</v>
-      </c>
-      <c r="C26" s="44" t="s">
-        <v>578</v>
-      </c>
-      <c r="D26" s="43" t="s">
-        <v>579</v>
-      </c>
-      <c r="E26" s="44">
-        <v>5500</v>
-      </c>
-      <c r="F26" s="45"/>
-    </row>
-    <row r="27" spans="1:6" ht="16" thickBot="1">
-      <c r="A27" s="38" t="s">
-        <v>111</v>
-      </c>
-      <c r="B27" s="39" t="s">
-        <v>276</v>
-      </c>
-      <c r="C27" s="40" t="s">
-        <v>563</v>
-      </c>
-      <c r="D27" s="39" t="s">
-        <v>564</v>
-      </c>
-      <c r="E27" s="41"/>
-      <c r="F27" s="40">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="16" thickBot="1">
-      <c r="A28" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="B28" s="43" t="s">
-        <v>293</v>
-      </c>
-      <c r="C28" s="44" t="s">
-        <v>580</v>
-      </c>
-      <c r="D28" s="43" t="s">
-        <v>581</v>
-      </c>
-      <c r="E28" s="45"/>
-      <c r="F28" s="44">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="25.5" thickBot="1">
-      <c r="A29" s="38" t="s">
-        <v>111</v>
-      </c>
-      <c r="B29" s="39" t="s">
-        <v>582</v>
-      </c>
-      <c r="C29" s="40" t="s">
-        <v>563</v>
-      </c>
-      <c r="D29" s="39" t="s">
-        <v>583</v>
-      </c>
-      <c r="E29" s="41"/>
-      <c r="F29" s="40">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="16" thickBot="1">
-      <c r="A30" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="B30" s="43" t="s">
-        <v>512</v>
-      </c>
-      <c r="C30" s="44" t="s">
-        <v>563</v>
-      </c>
-      <c r="D30" s="43" t="s">
-        <v>564</v>
-      </c>
-      <c r="E30" s="45"/>
-      <c r="F30" s="44">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="16" thickBot="1">
-      <c r="A31" s="38" t="s">
-        <v>111</v>
-      </c>
-      <c r="B31" s="39" t="s">
-        <v>526</v>
-      </c>
-      <c r="C31" s="40" t="s">
-        <v>563</v>
-      </c>
-      <c r="D31" s="39" t="s">
-        <v>564</v>
-      </c>
-      <c r="E31" s="41"/>
-      <c r="F31" s="40">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="16" thickBot="1">
-      <c r="A32" s="42" t="s">
-        <v>357</v>
-      </c>
-      <c r="B32" s="43" t="s">
-        <v>358</v>
-      </c>
-      <c r="C32" s="44" t="s">
-        <v>563</v>
-      </c>
-      <c r="D32" s="43" t="s">
-        <v>564</v>
-      </c>
-      <c r="E32" s="45"/>
-      <c r="F32" s="44">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="16" thickBot="1">
-      <c r="A33" s="38" t="s">
-        <v>357</v>
-      </c>
-      <c r="B33" s="39" t="s">
-        <v>430</v>
-      </c>
-      <c r="C33" s="40" t="s">
-        <v>584</v>
-      </c>
-      <c r="D33" s="40" t="s">
-        <v>585</v>
-      </c>
-      <c r="E33" s="41"/>
-      <c r="F33" s="40">
-        <v>1660</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="25.5" thickBot="1">
-      <c r="A34" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="B34" s="43" t="s">
-        <v>586</v>
-      </c>
-      <c r="C34" s="44" t="s">
-        <v>587</v>
-      </c>
-      <c r="D34" s="44" t="s">
-        <v>588</v>
-      </c>
-      <c r="E34" s="45"/>
-      <c r="F34" s="44">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="16" thickBot="1">
-      <c r="A35" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="B35" s="39" t="s">
-        <v>380</v>
-      </c>
-      <c r="C35" s="40" t="s">
-        <v>563</v>
-      </c>
-      <c r="D35" s="40" t="s">
-        <v>589</v>
-      </c>
-      <c r="E35" s="40">
-        <v>775</v>
-      </c>
-      <c r="F35" s="41"/>
-    </row>
-    <row r="36" spans="1:6" ht="25.5" thickBot="1">
-      <c r="A36" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="B36" s="43" t="s">
-        <v>590</v>
-      </c>
-      <c r="C36" s="43" t="s">
+    <row r="89" spans="1:6">
+      <c r="A89" s="34" t="s">
+        <v>298</v>
+      </c>
+      <c r="B89" s="34" t="s">
+        <v>529</v>
+      </c>
+      <c r="C89" s="34" t="s">
         <v>591</v>
       </c>
-      <c r="D36" s="43" t="s">
+      <c r="D89" s="34" t="s">
         <v>592</v>
       </c>
-      <c r="E36" s="45"/>
-      <c r="F36" s="44">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="16" thickBot="1">
-      <c r="A37" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="B37" s="40" t="s">
-        <v>63</v>
-      </c>
-      <c r="C37" s="39" t="s">
-        <v>563</v>
-      </c>
-      <c r="D37" s="40" t="s">
-        <v>567</v>
-      </c>
-      <c r="E37" s="41"/>
-      <c r="F37" s="40">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="25.5" thickBot="1">
-      <c r="A38" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="B38" s="43" t="s">
-        <v>593</v>
-      </c>
-      <c r="C38" s="44" t="s">
-        <v>594</v>
-      </c>
-      <c r="D38" s="43" t="s">
-        <v>595</v>
-      </c>
-      <c r="E38" s="45"/>
-      <c r="F38" s="44">
-        <v>2040</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="16" thickBot="1">
-      <c r="A39" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="B39" s="39" t="s">
-        <v>147</v>
-      </c>
-      <c r="C39" s="40" t="s">
-        <v>563</v>
-      </c>
-      <c r="D39" s="40" t="s">
-        <v>596</v>
-      </c>
-      <c r="E39" s="41"/>
-      <c r="F39" s="40">
-        <v>2625</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="16" thickBot="1">
-      <c r="A40" s="42" t="s">
-        <v>104</v>
-      </c>
-      <c r="B40" s="44" t="s">
-        <v>196</v>
-      </c>
-      <c r="C40" s="44" t="s">
-        <v>597</v>
-      </c>
-      <c r="D40" s="44" t="s">
-        <v>567</v>
-      </c>
-      <c r="E40" s="45"/>
-      <c r="F40" s="44">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="16" thickBot="1">
-      <c r="A41" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="B41" s="39" t="s">
-        <v>213</v>
-      </c>
-      <c r="C41" s="40" t="s">
-        <v>563</v>
-      </c>
-      <c r="D41" s="40" t="s">
-        <v>598</v>
-      </c>
-      <c r="E41" s="41"/>
-      <c r="F41" s="40">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="16" thickBot="1">
-      <c r="A42" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="B42" s="43" t="s">
-        <v>214</v>
-      </c>
-      <c r="C42" s="44" t="s">
-        <v>599</v>
-      </c>
-      <c r="D42" s="44" t="s">
-        <v>598</v>
-      </c>
-      <c r="E42" s="45"/>
-      <c r="F42" s="44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="16" thickBot="1">
-      <c r="A43" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="B43" s="39" t="s">
-        <v>244</v>
-      </c>
-      <c r="C43" s="40" t="s">
-        <v>600</v>
-      </c>
-      <c r="D43" s="40" t="s">
-        <v>601</v>
-      </c>
-      <c r="E43" s="41"/>
-      <c r="F43" s="40">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="16" thickBot="1">
-      <c r="A44" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="B44" s="43" t="s">
-        <v>343</v>
-      </c>
-      <c r="C44" s="44" t="s">
-        <v>563</v>
-      </c>
-      <c r="D44" s="44" t="s">
-        <v>602</v>
-      </c>
-      <c r="E44" s="45"/>
-      <c r="F44" s="44">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="16" thickBot="1">
-      <c r="A45" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="B45" s="39" t="s">
-        <v>359</v>
-      </c>
-      <c r="C45" s="40" t="s">
-        <v>240</v>
-      </c>
-      <c r="D45" s="40" t="s">
-        <v>598</v>
-      </c>
-      <c r="E45" s="41"/>
-      <c r="F45" s="40">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="16" thickBot="1">
-      <c r="A46" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="B46" s="43" t="s">
-        <v>363</v>
-      </c>
-      <c r="C46" s="44" t="s">
-        <v>584</v>
-      </c>
-      <c r="D46" s="44" t="s">
-        <v>227</v>
-      </c>
-      <c r="E46" s="45"/>
-      <c r="F46" s="44">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="16" thickBot="1">
-      <c r="A47" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="B47" s="39" t="s">
-        <v>410</v>
-      </c>
-      <c r="C47" s="40" t="s">
-        <v>569</v>
-      </c>
-      <c r="D47" s="40" t="s">
-        <v>589</v>
-      </c>
-      <c r="E47" s="41"/>
-      <c r="F47" s="40">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="16" thickBot="1">
-      <c r="A48" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="B48" s="43" t="s">
-        <v>419</v>
-      </c>
-      <c r="C48" s="44" t="s">
-        <v>591</v>
-      </c>
-      <c r="D48" s="44" t="s">
-        <v>603</v>
-      </c>
-      <c r="E48" s="44">
-        <v>725</v>
-      </c>
-      <c r="F48" s="45"/>
-    </row>
-    <row r="49" spans="1:6" ht="16" thickBot="1">
-      <c r="A49" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="B49" s="39" t="s">
-        <v>424</v>
-      </c>
-      <c r="C49" s="40" t="s">
-        <v>604</v>
-      </c>
-      <c r="D49" s="40" t="s">
-        <v>589</v>
-      </c>
-      <c r="E49" s="41"/>
-      <c r="F49" s="40">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="16" thickBot="1">
-      <c r="A50" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="B50" s="43" t="s">
-        <v>605</v>
-      </c>
-      <c r="C50" s="44" t="s">
-        <v>569</v>
-      </c>
-      <c r="D50" s="44" t="s">
-        <v>606</v>
-      </c>
-      <c r="E50" s="44">
-        <v>115</v>
-      </c>
-      <c r="F50" s="45"/>
-    </row>
-    <row r="51" spans="1:6" ht="16" thickBot="1">
-      <c r="A51" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="B51" s="39" t="s">
-        <v>490</v>
-      </c>
-      <c r="C51" s="40" t="s">
-        <v>584</v>
-      </c>
-      <c r="D51" s="40" t="s">
-        <v>607</v>
-      </c>
-      <c r="E51" s="40">
-        <v>78</v>
-      </c>
-      <c r="F51" s="41"/>
-    </row>
-    <row r="52" spans="1:6" ht="16" thickBot="1">
-      <c r="A52" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="B52" s="43" t="s">
-        <v>608</v>
-      </c>
-      <c r="C52" s="44" t="s">
-        <v>584</v>
-      </c>
-      <c r="D52" s="44" t="s">
-        <v>567</v>
-      </c>
-      <c r="E52" s="45"/>
-      <c r="F52" s="44">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="16" thickBot="1">
-      <c r="A53" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="B53" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="C53" s="40" t="s">
-        <v>563</v>
-      </c>
-      <c r="D53" s="40" t="s">
-        <v>567</v>
-      </c>
-      <c r="E53" s="41"/>
-      <c r="F53" s="40">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="16" thickBot="1">
-      <c r="A54" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="B54" s="43" t="s">
-        <v>371</v>
-      </c>
-      <c r="C54" s="44" t="s">
-        <v>584</v>
-      </c>
-      <c r="D54" s="44" t="s">
-        <v>567</v>
-      </c>
-      <c r="E54" s="45"/>
-      <c r="F54" s="44">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="16" thickBot="1">
-      <c r="A55" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="B55" s="39" t="s">
-        <v>320</v>
-      </c>
-      <c r="C55" s="40" t="s">
-        <v>609</v>
-      </c>
-      <c r="D55" s="40" t="s">
-        <v>567</v>
-      </c>
-      <c r="E55" s="41"/>
-      <c r="F55" s="40">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="16" thickBot="1">
-      <c r="A56" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="B56" s="43" t="s">
-        <v>341</v>
-      </c>
-      <c r="C56" s="44" t="s">
-        <v>609</v>
-      </c>
-      <c r="D56" s="44" t="s">
-        <v>567</v>
-      </c>
-      <c r="E56" s="45"/>
-      <c r="F56" s="44">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="16" thickBot="1">
-      <c r="A57" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="B57" s="39" t="s">
-        <v>610</v>
-      </c>
-      <c r="C57" s="40" t="s">
-        <v>584</v>
-      </c>
-      <c r="D57" s="40" t="s">
-        <v>567</v>
-      </c>
-      <c r="E57" s="41"/>
-      <c r="F57" s="40">
-        <v>1097</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="16" thickBot="1">
-      <c r="A58" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="B58" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="C58" s="44" t="s">
-        <v>563</v>
-      </c>
-      <c r="D58" s="44" t="s">
-        <v>567</v>
-      </c>
-      <c r="E58" s="45"/>
-      <c r="F58" s="44">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="16" thickBot="1">
-      <c r="A59" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="39" t="s">
-        <v>181</v>
-      </c>
-      <c r="C59" s="40" t="s">
-        <v>594</v>
-      </c>
-      <c r="D59" s="39" t="s">
-        <v>611</v>
-      </c>
-      <c r="E59" s="40" t="s">
-        <v>612</v>
-      </c>
-      <c r="F59" s="40">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="16" thickBot="1">
-      <c r="A60" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="B60" s="43" t="s">
-        <v>613</v>
-      </c>
-      <c r="C60" s="44" t="s">
-        <v>563</v>
-      </c>
-      <c r="D60" s="44" t="s">
-        <v>564</v>
-      </c>
-      <c r="E60" s="44">
-        <v>50</v>
-      </c>
-      <c r="F60" s="45"/>
-    </row>
-    <row r="61" spans="1:6" ht="16" thickBot="1">
-      <c r="A61" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="39" t="s">
-        <v>461</v>
-      </c>
-      <c r="C61" s="40" t="s">
-        <v>563</v>
-      </c>
-      <c r="D61" s="40" t="s">
-        <v>614</v>
-      </c>
-      <c r="E61" s="40">
-        <v>640</v>
-      </c>
-      <c r="F61" s="41"/>
-    </row>
-    <row r="62" spans="1:6" ht="16" thickBot="1">
-      <c r="A62" s="42" t="s">
-        <v>298</v>
-      </c>
-      <c r="B62" s="43" t="s">
-        <v>529</v>
-      </c>
-      <c r="C62" s="43" t="s">
-        <v>591</v>
-      </c>
-      <c r="D62" s="44" t="s">
-        <v>592</v>
-      </c>
-      <c r="E62" s="44">
+      <c r="E89" s="34">
         <v>285</v>
       </c>
-      <c r="F62" s="45"/>
-    </row>
-    <row r="63" spans="1:6" ht="16" thickBot="1">
-      <c r="A63" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="B63" s="39" t="s">
-        <v>352</v>
-      </c>
-      <c r="C63" s="40" t="s">
-        <v>584</v>
-      </c>
-      <c r="D63" s="40" t="s">
-        <v>585</v>
-      </c>
-      <c r="E63" s="41"/>
-      <c r="F63" s="40">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="16" thickBot="1">
-      <c r="A64" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="B64" s="43" t="s">
-        <v>226</v>
-      </c>
-      <c r="C64" s="44" t="s">
-        <v>584</v>
-      </c>
-      <c r="D64" s="44" t="s">
-        <v>227</v>
-      </c>
-      <c r="E64" s="44">
-        <v>242</v>
-      </c>
-      <c r="F64" s="45"/>
-    </row>
-    <row r="65" spans="1:6" ht="16" thickBot="1">
-      <c r="A65" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="B65" s="39" t="s">
-        <v>421</v>
-      </c>
-      <c r="C65" s="40" t="s">
-        <v>563</v>
-      </c>
-      <c r="D65" s="40" t="s">
-        <v>564</v>
-      </c>
-      <c r="E65" s="40">
-        <v>300</v>
-      </c>
-      <c r="F65" s="41"/>
-    </row>
-    <row r="66" spans="1:6" ht="16" thickBot="1">
-      <c r="A66" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="B66" s="43" t="s">
-        <v>615</v>
-      </c>
-      <c r="C66" s="44" t="s">
-        <v>584</v>
-      </c>
-      <c r="D66" s="44" t="s">
-        <v>227</v>
-      </c>
-      <c r="E66" s="45"/>
-      <c r="F66" s="44">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="16" thickBot="1">
-      <c r="A67" s="38" t="s">
-        <v>616</v>
-      </c>
-      <c r="B67" s="40" t="s">
-        <v>433</v>
-      </c>
-      <c r="C67" s="40" t="s">
-        <v>597</v>
-      </c>
-      <c r="D67" s="40" t="s">
-        <v>567</v>
-      </c>
-      <c r="E67" s="41"/>
-      <c r="F67" s="40">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="16" thickBot="1">
-      <c r="A68" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="B68" s="43" t="s">
-        <v>441</v>
-      </c>
-      <c r="C68" s="44" t="s">
-        <v>584</v>
-      </c>
-      <c r="D68" s="44" t="s">
-        <v>573</v>
-      </c>
-      <c r="E68" s="44">
-        <v>147</v>
-      </c>
-      <c r="F68" s="45"/>
-    </row>
-    <row r="69" spans="1:6" ht="16" thickBot="1">
-      <c r="A69" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="B69" s="39" t="s">
-        <v>154</v>
-      </c>
-      <c r="C69" s="40" t="s">
-        <v>599</v>
-      </c>
-      <c r="D69" s="40" t="s">
-        <v>598</v>
-      </c>
-      <c r="E69" s="41"/>
-      <c r="F69" s="40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="16" thickBot="1">
-      <c r="A70" s="42" t="s">
-        <v>91</v>
-      </c>
-      <c r="B70" s="43" t="s">
-        <v>514</v>
-      </c>
-      <c r="C70" s="44" t="s">
-        <v>591</v>
-      </c>
-      <c r="D70" s="44" t="s">
-        <v>589</v>
-      </c>
-      <c r="E70" s="44">
-        <v>2625</v>
-      </c>
-      <c r="F70" s="45"/>
-    </row>
-    <row r="71" spans="1:6" ht="16" thickBot="1">
-      <c r="A71" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="B71" s="39" t="s">
-        <v>110</v>
-      </c>
-      <c r="C71" s="39" t="s">
-        <v>563</v>
-      </c>
-      <c r="D71" s="40" t="s">
-        <v>617</v>
-      </c>
-      <c r="E71" s="41"/>
-      <c r="F71" s="40">
-        <v>3628</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="16" thickBot="1">
-      <c r="A72" s="42" t="s">
-        <v>30</v>
-      </c>
-      <c r="B72" s="43" t="s">
-        <v>141</v>
-      </c>
-      <c r="C72" s="44" t="s">
-        <v>587</v>
-      </c>
-      <c r="D72" s="44" t="s">
-        <v>618</v>
-      </c>
-      <c r="E72" s="45"/>
-      <c r="F72" s="44">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="16" thickBot="1">
-      <c r="A73" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="B73" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="C73" s="40" t="s">
-        <v>594</v>
-      </c>
-      <c r="D73" s="40" t="s">
-        <v>592</v>
-      </c>
-      <c r="E73" s="41"/>
-      <c r="F73" s="40">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="16" thickBot="1">
-      <c r="A74" s="42" t="s">
-        <v>30</v>
-      </c>
-      <c r="B74" s="43" t="s">
-        <v>312</v>
-      </c>
-      <c r="C74" s="44" t="s">
-        <v>563</v>
-      </c>
-      <c r="D74" s="44" t="s">
-        <v>564</v>
-      </c>
-      <c r="E74" s="45"/>
-      <c r="F74" s="44">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="16" thickBot="1">
-      <c r="A75" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="B75" s="39" t="s">
-        <v>436</v>
-      </c>
-      <c r="C75" s="40" t="s">
-        <v>594</v>
-      </c>
-      <c r="D75" s="40" t="s">
-        <v>619</v>
-      </c>
-      <c r="E75" s="41"/>
-      <c r="F75" s="40">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="16" thickBot="1">
-      <c r="A76" s="42" t="s">
-        <v>176</v>
-      </c>
-      <c r="B76" s="43" t="s">
-        <v>316</v>
-      </c>
-      <c r="C76" s="44" t="s">
-        <v>594</v>
-      </c>
-      <c r="D76" s="44" t="s">
-        <v>589</v>
-      </c>
-      <c r="E76" s="45"/>
-      <c r="F76" s="44">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="16" thickBot="1">
-      <c r="A77" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="B77" s="40" t="s">
-        <v>444</v>
-      </c>
-      <c r="C77" s="39" t="s">
-        <v>600</v>
-      </c>
-      <c r="D77" s="40" t="s">
-        <v>598</v>
-      </c>
-      <c r="E77" s="41"/>
-      <c r="F77" s="41"/>
-    </row>
-    <row r="78" spans="1:6" ht="16" thickBot="1">
-      <c r="A78" s="42" t="s">
-        <v>22</v>
-      </c>
-      <c r="B78" s="44" t="s">
-        <v>342</v>
-      </c>
-      <c r="C78" s="44" t="s">
-        <v>597</v>
-      </c>
-      <c r="D78" s="44" t="s">
-        <v>567</v>
-      </c>
-      <c r="E78" s="45"/>
-      <c r="F78" s="44">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="16" thickBot="1">
-      <c r="A79" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="B79" s="40" t="s">
-        <v>459</v>
-      </c>
-      <c r="C79" s="40" t="s">
-        <v>563</v>
-      </c>
-      <c r="D79" s="40" t="s">
-        <v>598</v>
-      </c>
-      <c r="E79" s="41"/>
-      <c r="F79" s="40">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="16" thickBot="1">
-      <c r="A80" s="42" t="s">
-        <v>620</v>
-      </c>
-      <c r="B80" s="43" t="s">
-        <v>307</v>
-      </c>
-      <c r="C80" s="44" t="s">
-        <v>563</v>
-      </c>
-      <c r="D80" s="44" t="s">
-        <v>567</v>
-      </c>
-      <c r="E80" s="45"/>
-      <c r="F80" s="44">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="25.5" thickBot="1">
-      <c r="A81" s="38" t="s">
-        <v>620</v>
-      </c>
-      <c r="B81" s="39" t="s">
-        <v>621</v>
-      </c>
-      <c r="C81" s="39" t="s">
-        <v>591</v>
-      </c>
-      <c r="D81" s="40" t="s">
-        <v>611</v>
-      </c>
-      <c r="E81" s="40">
-        <v>300</v>
-      </c>
-      <c r="F81" s="41"/>
-    </row>
-    <row r="82" spans="1:6" ht="16" thickBot="1">
-      <c r="A82" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="B82" s="43" t="s">
-        <v>622</v>
-      </c>
-      <c r="C82" s="44" t="s">
-        <v>101</v>
-      </c>
-      <c r="D82" s="44" t="s">
-        <v>573</v>
-      </c>
-      <c r="E82" s="45"/>
-      <c r="F82" s="44">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="16" thickBot="1">
-      <c r="A83" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="B83" s="39" t="s">
-        <v>125</v>
-      </c>
-      <c r="C83" s="40" t="s">
-        <v>563</v>
-      </c>
-      <c r="D83" s="40" t="s">
-        <v>598</v>
-      </c>
-      <c r="E83" s="41"/>
-      <c r="F83" s="40">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="25.5" thickBot="1">
-      <c r="A84" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="B84" s="43" t="s">
-        <v>623</v>
-      </c>
-      <c r="C84" s="44" t="s">
-        <v>563</v>
-      </c>
-      <c r="D84" s="44" t="s">
-        <v>573</v>
-      </c>
-      <c r="E84" s="44">
-        <v>75</v>
-      </c>
-      <c r="F84" s="45"/>
-    </row>
-    <row r="85" spans="1:6" ht="25.5" thickBot="1">
-      <c r="A85" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="B85" s="39" t="s">
-        <v>624</v>
-      </c>
-      <c r="C85" s="40" t="s">
-        <v>563</v>
-      </c>
-      <c r="D85" s="40" t="s">
-        <v>564</v>
-      </c>
-      <c r="E85" s="41"/>
-      <c r="F85" s="40">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="16" thickBot="1">
-      <c r="A86" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="B86" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="C86" s="44" t="s">
-        <v>563</v>
-      </c>
-      <c r="D86" s="44" t="s">
-        <v>598</v>
-      </c>
-      <c r="E86" s="45"/>
-      <c r="F86" s="44">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="25.5" thickBot="1">
-      <c r="A87" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="B87" s="39" t="s">
-        <v>625</v>
-      </c>
-      <c r="C87" s="40" t="s">
-        <v>563</v>
-      </c>
-      <c r="D87" s="40" t="s">
-        <v>567</v>
-      </c>
-      <c r="E87" s="41"/>
-      <c r="F87" s="40">
-        <v>1957</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="16" thickBot="1">
-      <c r="A88" s="42" t="s">
-        <v>173</v>
-      </c>
-      <c r="B88" s="43" t="s">
-        <v>626</v>
-      </c>
-      <c r="C88" s="43" t="s">
-        <v>240</v>
-      </c>
-      <c r="D88" s="44" t="s">
-        <v>567</v>
-      </c>
-      <c r="E88" s="45"/>
-      <c r="F88" s="44">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="16" thickBot="1">
-      <c r="A89" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="B89" s="40" t="s">
-        <v>337</v>
-      </c>
-      <c r="C89" s="39" t="s">
-        <v>563</v>
-      </c>
-      <c r="D89" s="40" t="s">
-        <v>564</v>
-      </c>
-      <c r="E89" s="40">
-        <v>60</v>
-      </c>
-      <c r="F89" s="41"/>
+      <c r="F89" s="57"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="A90" s="48" t="s">
+      <c r="A90" s="37" t="s">
         <v>627</v>
       </c>
-      <c r="B90" s="49"/>
-      <c r="C90" s="50"/>
-      <c r="D90" s="49"/>
-      <c r="E90" s="51">
+      <c r="B90" s="38"/>
+      <c r="C90" s="39"/>
+      <c r="D90" s="38"/>
+      <c r="E90" s="40">
         <v>21044</v>
       </c>
-      <c r="F90" s="51">
+      <c r="F90" s="40">
         <v>24814</v>
       </c>
     </row>
@@ -17204,6 +17242,9 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -17220,10 +17261,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="34" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="45" t="s">
         <v>628</v>
       </c>
-      <c r="E1" s="53" t="s">
+      <c r="E1" s="41" t="s">
         <v>1256</v>
       </c>
     </row>
@@ -17928,13 +17969,13 @@
       <c r="B58" s="8" t="s">
         <v>726</v>
       </c>
-      <c r="C58" s="53" t="s">
+      <c r="C58" s="41" t="s">
         <v>727</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>728</v>
       </c>
-      <c r="E58" s="53" t="s">
+      <c r="E58" s="41" t="s">
         <v>1214</v>
       </c>
     </row>
@@ -18061,13 +18102,13 @@
       <c r="B69" s="8">
         <v>78</v>
       </c>
-      <c r="C69" s="53" t="s">
+      <c r="C69" s="41" t="s">
         <v>755</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>736</v>
       </c>
-      <c r="E69" s="53" t="s">
+      <c r="E69" s="41" t="s">
         <v>794</v>
       </c>
     </row>
@@ -18162,13 +18203,13 @@
       <c r="B76" s="8">
         <v>12</v>
       </c>
-      <c r="C76" s="53" t="s">
+      <c r="C76" s="41" t="s">
         <v>739</v>
       </c>
       <c r="D76" s="8" t="s">
         <v>736</v>
       </c>
-      <c r="E76" s="53"/>
+      <c r="E76" s="41"/>
     </row>
     <row r="77" spans="1:5" s="8" customFormat="1" ht="46.5">
       <c r="A77" s="8" t="s">
@@ -18177,13 +18218,13 @@
       <c r="B77" s="8">
         <v>37</v>
       </c>
-      <c r="C77" s="53" t="s">
+      <c r="C77" s="41" t="s">
         <v>791</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>736</v>
       </c>
-      <c r="E77" s="53" t="s">
+      <c r="E77" s="41" t="s">
         <v>792</v>
       </c>
     </row>
@@ -18352,13 +18393,13 @@
       <c r="B91" s="8">
         <v>1</v>
       </c>
-      <c r="C91" s="53" t="s">
+      <c r="C91" s="41" t="s">
         <v>795</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>736</v>
       </c>
-      <c r="E91" s="53" t="s">
+      <c r="E91" s="41" t="s">
         <v>1258</v>
       </c>
     </row>
@@ -19533,13 +19574,13 @@
       </c>
     </row>
     <row r="189" spans="1:5" ht="31">
-      <c r="A189" s="54" t="s">
+      <c r="A189" s="42" t="s">
         <v>1259</v>
       </c>
       <c r="B189" s="8"/>
-      <c r="C189" s="53"/>
+      <c r="C189" s="41"/>
       <c r="D189" s="8"/>
-      <c r="E189" s="53" t="s">
+      <c r="E189" s="41" t="s">
         <v>963</v>
       </c>
     </row>
@@ -19550,11 +19591,11 @@
       <c r="B190" s="8">
         <v>1</v>
       </c>
-      <c r="C190" s="53"/>
+      <c r="C190" s="41"/>
       <c r="D190" s="8" t="s">
         <v>931</v>
       </c>
-      <c r="E190" s="53" t="s">
+      <c r="E190" s="41" t="s">
         <v>1218</v>
       </c>
     </row>
@@ -19565,7 +19606,7 @@
       <c r="B191" s="8">
         <v>4</v>
       </c>
-      <c r="C191" s="53"/>
+      <c r="C191" s="41"/>
       <c r="D191" s="8" t="s">
         <v>931</v>
       </c>
@@ -19577,7 +19618,7 @@
       <c r="B192" s="8">
         <v>4</v>
       </c>
-      <c r="C192" s="53"/>
+      <c r="C192" s="41"/>
       <c r="D192" s="8" t="s">
         <v>934</v>
       </c>
@@ -19589,7 +19630,7 @@
       <c r="B193" s="8">
         <v>2</v>
       </c>
-      <c r="C193" s="53"/>
+      <c r="C193" s="41"/>
       <c r="D193" s="8" t="s">
         <v>931</v>
       </c>
@@ -19601,7 +19642,7 @@
       <c r="B194" s="8">
         <v>8</v>
       </c>
-      <c r="C194" s="53"/>
+      <c r="C194" s="41"/>
       <c r="D194" s="8" t="s">
         <v>937</v>
       </c>
@@ -19613,7 +19654,7 @@
       <c r="B195" s="8">
         <v>3</v>
       </c>
-      <c r="C195" s="53"/>
+      <c r="C195" s="41"/>
       <c r="D195" s="8" t="s">
         <v>931</v>
       </c>
@@ -19625,7 +19666,7 @@
       <c r="B196" s="8">
         <v>19</v>
       </c>
-      <c r="C196" s="53" t="s">
+      <c r="C196" s="41" t="s">
         <v>940</v>
       </c>
       <c r="D196" s="8" t="s">
@@ -19639,7 +19680,7 @@
       <c r="B197" s="8">
         <v>1</v>
       </c>
-      <c r="C197" s="53"/>
+      <c r="C197" s="41"/>
       <c r="D197" s="8" t="s">
         <v>931</v>
       </c>
@@ -19651,7 +19692,7 @@
       <c r="B198" s="8">
         <v>6</v>
       </c>
-      <c r="C198" s="53"/>
+      <c r="C198" s="41"/>
       <c r="D198" s="8" t="s">
         <v>934</v>
       </c>
@@ -19663,7 +19704,7 @@
       <c r="B199" s="8">
         <v>1</v>
       </c>
-      <c r="C199" s="53"/>
+      <c r="C199" s="41"/>
       <c r="D199" s="8" t="s">
         <v>962</v>
       </c>
@@ -19675,7 +19716,7 @@
       <c r="B200" s="8">
         <v>4</v>
       </c>
-      <c r="C200" s="53"/>
+      <c r="C200" s="41"/>
       <c r="D200" s="8" t="s">
         <v>937</v>
       </c>
@@ -19687,13 +19728,13 @@
       <c r="B201" s="8">
         <v>11</v>
       </c>
-      <c r="C201" s="53" t="s">
+      <c r="C201" s="41" t="s">
         <v>1219</v>
       </c>
       <c r="D201" s="8" t="s">
         <v>931</v>
       </c>
-      <c r="E201" s="53"/>
+      <c r="E201" s="41"/>
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="8" t="s">
@@ -19702,7 +19743,7 @@
       <c r="B202" s="8">
         <v>1</v>
       </c>
-      <c r="C202" s="53"/>
+      <c r="C202" s="41"/>
       <c r="D202" s="8" t="s">
         <v>931</v>
       </c>
@@ -19714,7 +19755,7 @@
       <c r="B203" s="8">
         <v>3</v>
       </c>
-      <c r="C203" s="53" t="s">
+      <c r="C203" s="41" t="s">
         <v>948</v>
       </c>
       <c r="D203" s="8" t="s">
@@ -19728,7 +19769,7 @@
       <c r="B204" s="8">
         <v>9</v>
       </c>
-      <c r="C204" s="53"/>
+      <c r="C204" s="41"/>
       <c r="D204" s="8" t="s">
         <v>931</v>
       </c>
@@ -19740,7 +19781,7 @@
       <c r="B205" s="8">
         <v>2</v>
       </c>
-      <c r="C205" s="53"/>
+      <c r="C205" s="41"/>
       <c r="D205" s="8" t="s">
         <v>931</v>
       </c>
@@ -19752,7 +19793,7 @@
       <c r="B206" s="8">
         <v>37</v>
       </c>
-      <c r="C206" s="53"/>
+      <c r="C206" s="41"/>
       <c r="D206" s="8" t="s">
         <v>931</v>
       </c>
@@ -19764,7 +19805,7 @@
       <c r="B207" s="8">
         <v>1</v>
       </c>
-      <c r="C207" s="53"/>
+      <c r="C207" s="41"/>
       <c r="D207" s="8" t="s">
         <v>931</v>
       </c>
@@ -19776,7 +19817,7 @@
       <c r="B208" s="8">
         <v>1</v>
       </c>
-      <c r="C208" s="53" t="s">
+      <c r="C208" s="41" t="s">
         <v>948</v>
       </c>
       <c r="D208" s="8" t="s">
@@ -19790,7 +19831,7 @@
       <c r="B209" s="8">
         <v>1</v>
       </c>
-      <c r="C209" s="53" t="s">
+      <c r="C209" s="41" t="s">
         <v>948</v>
       </c>
       <c r="D209" s="8" t="s">
@@ -19804,7 +19845,7 @@
       <c r="B210" s="8">
         <v>9</v>
       </c>
-      <c r="C210" s="53"/>
+      <c r="C210" s="41"/>
       <c r="D210" s="8" t="s">
         <v>931</v>
       </c>
@@ -19816,7 +19857,7 @@
       <c r="B211" s="8">
         <v>2</v>
       </c>
-      <c r="C211" s="53" t="s">
+      <c r="C211" s="41" t="s">
         <v>957</v>
       </c>
       <c r="D211" s="8" t="s">
@@ -19830,7 +19871,7 @@
       <c r="B212" s="8">
         <v>7</v>
       </c>
-      <c r="C212" s="53"/>
+      <c r="C212" s="41"/>
       <c r="D212" s="8" t="s">
         <v>931</v>
       </c>
@@ -19842,7 +19883,7 @@
       <c r="B213" s="8">
         <v>10</v>
       </c>
-      <c r="C213" s="53"/>
+      <c r="C213" s="41"/>
       <c r="D213" s="8" t="s">
         <v>965</v>
       </c>
@@ -19854,7 +19895,7 @@
       <c r="B214" s="8">
         <v>1</v>
       </c>
-      <c r="C214" s="53"/>
+      <c r="C214" s="41"/>
       <c r="D214" s="8" t="s">
         <v>934</v>
       </c>
@@ -19866,7 +19907,7 @@
       <c r="B215" s="8">
         <v>2</v>
       </c>
-      <c r="C215" s="53"/>
+      <c r="C215" s="41"/>
       <c r="D215" s="8" t="s">
         <v>931</v>
       </c>
@@ -19878,7 +19919,7 @@
       <c r="B216" s="8">
         <v>4</v>
       </c>
-      <c r="C216" s="53" t="s">
+      <c r="C216" s="41" t="s">
         <v>948</v>
       </c>
       <c r="D216" s="8" t="s">
@@ -19892,7 +19933,7 @@
       <c r="B217" s="8">
         <v>5</v>
       </c>
-      <c r="C217" s="53" t="s">
+      <c r="C217" s="41" t="s">
         <v>970</v>
       </c>
       <c r="D217" s="8" t="s">
@@ -19906,7 +19947,7 @@
       <c r="B218" s="8">
         <v>17</v>
       </c>
-      <c r="C218" s="53" t="s">
+      <c r="C218" s="41" t="s">
         <v>972</v>
       </c>
       <c r="D218" s="8" t="s">
@@ -19920,7 +19961,7 @@
       <c r="B219" s="8">
         <v>1</v>
       </c>
-      <c r="C219" s="53"/>
+      <c r="C219" s="41"/>
       <c r="D219" s="8" t="s">
         <v>937</v>
       </c>
@@ -19932,7 +19973,7 @@
       <c r="B220" s="8">
         <v>1</v>
       </c>
-      <c r="C220" s="53"/>
+      <c r="C220" s="41"/>
       <c r="D220" s="8" t="s">
         <v>931</v>
       </c>
@@ -19944,7 +19985,7 @@
       <c r="B221" s="8">
         <v>1</v>
       </c>
-      <c r="C221" s="53" t="s">
+      <c r="C221" s="41" t="s">
         <v>948</v>
       </c>
       <c r="D221" s="8" t="s">
@@ -19958,7 +19999,7 @@
       <c r="B222" s="8">
         <v>1</v>
       </c>
-      <c r="C222" s="53"/>
+      <c r="C222" s="41"/>
       <c r="D222" s="8" t="s">
         <v>931</v>
       </c>
@@ -19970,7 +20011,7 @@
       <c r="B223" s="8">
         <v>1</v>
       </c>
-      <c r="C223" s="53"/>
+      <c r="C223" s="41"/>
       <c r="D223" s="8" t="s">
         <v>931</v>
       </c>
@@ -19982,7 +20023,7 @@
       <c r="B224" s="8">
         <v>17</v>
       </c>
-      <c r="C224" s="53" t="s">
+      <c r="C224" s="41" t="s">
         <v>979</v>
       </c>
       <c r="D224" s="8" t="s">
@@ -19996,7 +20037,7 @@
       <c r="B225" s="8">
         <v>3</v>
       </c>
-      <c r="C225" s="53"/>
+      <c r="C225" s="41"/>
       <c r="D225" s="8" t="s">
         <v>934</v>
       </c>
@@ -20008,7 +20049,7 @@
       <c r="B226" s="8">
         <v>1</v>
       </c>
-      <c r="C226" s="53"/>
+      <c r="C226" s="41"/>
       <c r="D226" s="8" t="s">
         <v>740</v>
       </c>
@@ -20020,7 +20061,7 @@
       <c r="B227" s="8">
         <v>2</v>
       </c>
-      <c r="C227" s="53"/>
+      <c r="C227" s="41"/>
       <c r="D227" s="8" t="s">
         <v>740</v>
       </c>
@@ -20032,7 +20073,7 @@
       <c r="B228" s="8" t="s">
         <v>995</v>
       </c>
-      <c r="C228" s="53" t="s">
+      <c r="C228" s="41" t="s">
         <v>994</v>
       </c>
       <c r="D228" s="8" t="s">
@@ -20046,7 +20087,7 @@
       <c r="B229" s="8">
         <v>1</v>
       </c>
-      <c r="C229" s="53"/>
+      <c r="C229" s="41"/>
       <c r="D229" s="8" t="s">
         <v>931</v>
       </c>
@@ -20058,7 +20099,7 @@
       <c r="B230" s="8">
         <v>9</v>
       </c>
-      <c r="C230" s="53"/>
+      <c r="C230" s="41"/>
       <c r="D230" s="8" t="s">
         <v>931</v>
       </c>
@@ -20070,7 +20111,7 @@
       <c r="B231" s="8">
         <v>1</v>
       </c>
-      <c r="C231" s="53"/>
+      <c r="C231" s="41"/>
       <c r="D231" s="8" t="s">
         <v>934</v>
       </c>
@@ -20082,7 +20123,7 @@
       <c r="B232" s="8">
         <v>1</v>
       </c>
-      <c r="C232" s="53" t="s">
+      <c r="C232" s="41" t="s">
         <v>948</v>
       </c>
       <c r="D232" s="8" t="s">
@@ -20096,7 +20137,7 @@
       <c r="B233" s="8">
         <v>2</v>
       </c>
-      <c r="C233" s="53"/>
+      <c r="C233" s="41"/>
       <c r="D233" s="8" t="s">
         <v>931</v>
       </c>
@@ -20108,7 +20149,7 @@
       <c r="B234" s="8">
         <v>11</v>
       </c>
-      <c r="C234" s="53"/>
+      <c r="C234" s="41"/>
       <c r="D234" s="8" t="s">
         <v>740</v>
       </c>
@@ -20120,7 +20161,7 @@
       <c r="B235" s="8">
         <v>1</v>
       </c>
-      <c r="C235" s="53"/>
+      <c r="C235" s="41"/>
       <c r="D235" s="8" t="s">
         <v>931</v>
       </c>
@@ -20132,7 +20173,7 @@
       <c r="B236" s="8">
         <v>10</v>
       </c>
-      <c r="C236" s="53" t="s">
+      <c r="C236" s="41" t="s">
         <v>991</v>
       </c>
       <c r="D236" s="8" t="s">
@@ -20146,7 +20187,7 @@
       <c r="B237" s="8">
         <v>7</v>
       </c>
-      <c r="C237" s="53"/>
+      <c r="C237" s="41"/>
       <c r="D237" s="8" t="s">
         <v>934</v>
       </c>
@@ -20158,7 +20199,7 @@
       <c r="B238" s="8">
         <v>4</v>
       </c>
-      <c r="C238" s="53"/>
+      <c r="C238" s="41"/>
       <c r="D238" s="8" t="s">
         <v>937</v>
       </c>
@@ -20170,7 +20211,7 @@
       <c r="B239" s="8">
         <v>1</v>
       </c>
-      <c r="C239" s="53"/>
+      <c r="C239" s="41"/>
       <c r="D239" s="8" t="s">
         <v>931</v>
       </c>
@@ -20182,7 +20223,7 @@
       <c r="B240" s="8">
         <v>16</v>
       </c>
-      <c r="C240" s="53"/>
+      <c r="C240" s="41"/>
       <c r="D240" s="8" t="s">
         <v>934</v>
       </c>
@@ -20194,7 +20235,7 @@
       <c r="B241" s="8">
         <v>15</v>
       </c>
-      <c r="C241" s="53"/>
+      <c r="C241" s="41"/>
       <c r="D241" s="8" t="s">
         <v>931</v>
       </c>
@@ -20206,7 +20247,7 @@
       <c r="B242" s="8">
         <v>2</v>
       </c>
-      <c r="C242" s="53"/>
+      <c r="C242" s="41"/>
       <c r="D242" s="8" t="s">
         <v>931</v>
       </c>
@@ -20218,7 +20259,7 @@
       <c r="B243" s="8">
         <v>53</v>
       </c>
-      <c r="C243" s="53" t="s">
+      <c r="C243" s="41" t="s">
         <v>1002</v>
       </c>
       <c r="D243" s="8" t="s">
@@ -20232,7 +20273,7 @@
       <c r="B244" s="8">
         <v>1</v>
       </c>
-      <c r="C244" s="53"/>
+      <c r="C244" s="41"/>
       <c r="D244" s="8" t="s">
         <v>740</v>
       </c>
@@ -20244,7 +20285,7 @@
       <c r="B245" s="8">
         <v>2</v>
       </c>
-      <c r="C245" s="53"/>
+      <c r="C245" s="41"/>
       <c r="D245" s="8" t="s">
         <v>934</v>
       </c>
@@ -20256,7 +20297,7 @@
       <c r="B246" s="8">
         <v>1</v>
       </c>
-      <c r="C246" s="53"/>
+      <c r="C246" s="41"/>
       <c r="D246" s="8" t="s">
         <v>931</v>
       </c>
@@ -20268,7 +20309,7 @@
       <c r="B247" s="8">
         <v>20</v>
       </c>
-      <c r="C247" s="53" t="s">
+      <c r="C247" s="41" t="s">
         <v>1021</v>
       </c>
       <c r="D247" s="8" t="s">
@@ -20282,7 +20323,7 @@
       <c r="B248" s="8">
         <v>6</v>
       </c>
-      <c r="C248" s="53" t="s">
+      <c r="C248" s="41" t="s">
         <v>1220</v>
       </c>
       <c r="D248" s="8" t="s">
@@ -20296,7 +20337,7 @@
       <c r="B249" s="8">
         <v>2</v>
       </c>
-      <c r="C249" s="53" t="s">
+      <c r="C249" s="41" t="s">
         <v>957</v>
       </c>
       <c r="D249" s="8" t="s">
@@ -20310,7 +20351,7 @@
       <c r="B250" s="8">
         <v>1</v>
       </c>
-      <c r="C250" s="53"/>
+      <c r="C250" s="41"/>
       <c r="D250" s="8" t="s">
         <v>934</v>
       </c>
@@ -20322,7 +20363,7 @@
       <c r="B251" s="8">
         <v>1</v>
       </c>
-      <c r="C251" s="53"/>
+      <c r="C251" s="41"/>
       <c r="D251" s="8" t="s">
         <v>931</v>
       </c>
@@ -20334,7 +20375,7 @@
       <c r="B252" s="8">
         <v>6</v>
       </c>
-      <c r="C252" s="53"/>
+      <c r="C252" s="41"/>
       <c r="D252" s="8" t="s">
         <v>934</v>
       </c>
@@ -20346,7 +20387,7 @@
       <c r="B253" s="8">
         <v>1</v>
       </c>
-      <c r="C253" s="53"/>
+      <c r="C253" s="41"/>
       <c r="D253" s="8" t="s">
         <v>934</v>
       </c>
@@ -20358,7 +20399,7 @@
       <c r="B254" s="8">
         <v>1</v>
       </c>
-      <c r="C254" s="53"/>
+      <c r="C254" s="41"/>
       <c r="D254" s="8" t="s">
         <v>931</v>
       </c>
@@ -20370,7 +20411,7 @@
       <c r="B255" s="8">
         <v>26</v>
       </c>
-      <c r="C255" s="53"/>
+      <c r="C255" s="41"/>
       <c r="D255" s="8" t="s">
         <v>937</v>
       </c>
@@ -20382,7 +20423,7 @@
       <c r="B256" s="8">
         <v>46</v>
       </c>
-      <c r="C256" s="53" t="s">
+      <c r="C256" s="41" t="s">
         <v>1016</v>
       </c>
       <c r="D256" s="8" t="s">
@@ -20396,7 +20437,7 @@
       <c r="B257" s="8">
         <v>10</v>
       </c>
-      <c r="C257" s="53" t="s">
+      <c r="C257" s="41" t="s">
         <v>991</v>
       </c>
       <c r="D257" s="8" t="s">
@@ -20410,7 +20451,7 @@
       <c r="B258" s="8">
         <v>6</v>
       </c>
-      <c r="C258" s="53"/>
+      <c r="C258" s="41"/>
       <c r="D258" s="8" t="s">
         <v>740</v>
       </c>
@@ -20422,7 +20463,7 @@
       <c r="B259" s="8">
         <v>1</v>
       </c>
-      <c r="C259" s="53"/>
+      <c r="C259" s="41"/>
       <c r="D259" s="8" t="s">
         <v>740</v>
       </c>
@@ -20434,7 +20475,7 @@
       <c r="B260" s="8">
         <v>4</v>
       </c>
-      <c r="C260" s="53"/>
+      <c r="C260" s="41"/>
       <c r="D260" s="8" t="s">
         <v>934</v>
       </c>
@@ -20446,7 +20487,7 @@
       <c r="B261" s="8">
         <v>2</v>
       </c>
-      <c r="C261" s="53" t="s">
+      <c r="C261" s="41" t="s">
         <v>948</v>
       </c>
       <c r="D261" s="8" t="s">
@@ -20460,7 +20501,7 @@
       <c r="B262" s="8">
         <v>1</v>
       </c>
-      <c r="C262" s="53" t="s">
+      <c r="C262" s="41" t="s">
         <v>1024</v>
       </c>
       <c r="D262" s="8" t="s">
@@ -20474,7 +20515,7 @@
       <c r="B263" s="8">
         <v>3</v>
       </c>
-      <c r="C263" s="53" t="s">
+      <c r="C263" s="41" t="s">
         <v>948</v>
       </c>
       <c r="D263" s="8" t="s">
@@ -20488,7 +20529,7 @@
       <c r="B264" s="8">
         <v>1</v>
       </c>
-      <c r="C264" s="53" t="s">
+      <c r="C264" s="41" t="s">
         <v>948</v>
       </c>
       <c r="D264" s="8" t="s">
@@ -20502,7 +20543,7 @@
       <c r="B265" s="8">
         <v>5</v>
       </c>
-      <c r="C265" s="53" t="s">
+      <c r="C265" s="41" t="s">
         <v>1028</v>
       </c>
       <c r="D265" s="8" t="s">
@@ -20516,19 +20557,19 @@
       <c r="B266" s="8">
         <v>8</v>
       </c>
-      <c r="C266" s="53"/>
+      <c r="C266" s="41"/>
       <c r="D266" s="8" t="s">
         <v>931</v>
       </c>
     </row>
     <row r="267" spans="1:5" ht="31">
-      <c r="A267" s="54" t="s">
+      <c r="A267" s="42" t="s">
         <v>256</v>
       </c>
       <c r="B267" s="8"/>
-      <c r="C267" s="53"/>
+      <c r="C267" s="41"/>
       <c r="D267" s="8"/>
-      <c r="E267" s="53" t="s">
+      <c r="E267" s="41" t="s">
         <v>963</v>
       </c>
     </row>
@@ -20539,7 +20580,7 @@
       <c r="B268" s="8">
         <v>4</v>
       </c>
-      <c r="C268" s="53"/>
+      <c r="C268" s="41"/>
       <c r="D268" s="8" t="s">
         <v>1033</v>
       </c>
@@ -20551,7 +20592,7 @@
       <c r="B269" s="8">
         <v>1</v>
       </c>
-      <c r="C269" s="53" t="s">
+      <c r="C269" s="41" t="s">
         <v>1032</v>
       </c>
       <c r="D269" s="8" t="s">
@@ -20565,7 +20606,7 @@
       <c r="B270" s="8">
         <v>1</v>
       </c>
-      <c r="C270" s="53" t="s">
+      <c r="C270" s="41" t="s">
         <v>1035</v>
       </c>
       <c r="D270" s="8" t="s">
@@ -20579,7 +20620,7 @@
       <c r="B271" s="8">
         <v>6</v>
       </c>
-      <c r="C271" s="53"/>
+      <c r="C271" s="41"/>
       <c r="D271" s="8" t="s">
         <v>1033</v>
       </c>
@@ -20591,7 +20632,7 @@
       <c r="B272" s="8">
         <v>69</v>
       </c>
-      <c r="C272" s="53" t="s">
+      <c r="C272" s="41" t="s">
         <v>1038</v>
       </c>
       <c r="D272" s="8" t="s">
@@ -20605,7 +20646,7 @@
       <c r="B273" s="8">
         <v>1</v>
       </c>
-      <c r="C273" s="53"/>
+      <c r="C273" s="41"/>
       <c r="D273" s="8" t="s">
         <v>1033</v>
       </c>
@@ -20617,7 +20658,7 @@
       <c r="B274" s="8" t="s">
         <v>1041</v>
       </c>
-      <c r="C274" s="53" t="s">
+      <c r="C274" s="41" t="s">
         <v>1042</v>
       </c>
       <c r="D274" s="8" t="s">
@@ -20627,7 +20668,7 @@
     <row r="275" spans="1:5">
       <c r="A275" s="8"/>
       <c r="B275" s="8"/>
-      <c r="C275" s="53" t="s">
+      <c r="C275" s="41" t="s">
         <v>1002</v>
       </c>
       <c r="D275" s="8" t="s">
@@ -20641,7 +20682,7 @@
       <c r="B276" s="8" t="s">
         <v>1046</v>
       </c>
-      <c r="C276" s="53" t="s">
+      <c r="C276" s="41" t="s">
         <v>1090</v>
       </c>
       <c r="D276" s="8" t="s">
@@ -20655,7 +20696,7 @@
       <c r="B277" s="8" t="s">
         <v>1048</v>
       </c>
-      <c r="C277" s="53"/>
+      <c r="C277" s="41"/>
       <c r="D277" s="8" t="s">
         <v>1033</v>
       </c>
@@ -20667,7 +20708,7 @@
       <c r="B278" s="8">
         <v>29</v>
       </c>
-      <c r="C278" s="53"/>
+      <c r="C278" s="41"/>
       <c r="D278" s="8" t="s">
         <v>1033</v>
       </c>
@@ -20679,7 +20720,7 @@
       <c r="B279" s="8">
         <v>1</v>
       </c>
-      <c r="C279" s="53"/>
+      <c r="C279" s="41"/>
       <c r="D279" s="8" t="s">
         <v>1033</v>
       </c>
@@ -20688,7 +20729,7 @@
       <c r="A280" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="E280" s="53" t="s">
+      <c r="E280" s="41" t="s">
         <v>1197</v>
       </c>
     </row>
@@ -20699,7 +20740,7 @@
       <c r="B281" s="8">
         <v>1</v>
       </c>
-      <c r="C281" s="53"/>
+      <c r="C281" s="41"/>
       <c r="D281" s="8" t="s">
         <v>1051</v>
       </c>
@@ -20717,7 +20758,7 @@
       <c r="D282" t="s">
         <v>1051</v>
       </c>
-      <c r="E282" s="53" t="s">
+      <c r="E282" s="41" t="s">
         <v>556</v>
       </c>
     </row>
@@ -20773,7 +20814,7 @@
       <c r="B286" s="8">
         <v>9</v>
       </c>
-      <c r="C286" s="53"/>
+      <c r="C286" s="41"/>
       <c r="D286" s="8" t="s">
         <v>1055</v>
       </c>
@@ -20802,7 +20843,7 @@
       <c r="B288" s="8">
         <v>4</v>
       </c>
-      <c r="C288" s="53"/>
+      <c r="C288" s="41"/>
       <c r="D288" s="8" t="s">
         <v>740</v>
       </c>
@@ -20814,7 +20855,7 @@
       <c r="B289" s="8">
         <v>2</v>
       </c>
-      <c r="C289" s="53"/>
+      <c r="C289" s="41"/>
       <c r="D289" s="8" t="s">
         <v>1055</v>
       </c>
@@ -20840,7 +20881,7 @@
       <c r="B291" s="8">
         <v>47</v>
       </c>
-      <c r="C291" s="53" t="s">
+      <c r="C291" s="41" t="s">
         <v>1057</v>
       </c>
       <c r="D291" s="8" t="s">
@@ -20857,7 +20898,7 @@
       <c r="B292" s="8">
         <v>1</v>
       </c>
-      <c r="C292" s="53"/>
+      <c r="C292" s="41"/>
       <c r="D292" s="8" t="s">
         <v>740</v>
       </c>
@@ -20869,7 +20910,7 @@
       <c r="B293" s="8">
         <v>1</v>
       </c>
-      <c r="C293" s="53"/>
+      <c r="C293" s="41"/>
       <c r="D293" s="8" t="s">
         <v>1058</v>
       </c>
@@ -20929,13 +20970,13 @@
       <c r="B297" s="8">
         <v>80</v>
       </c>
-      <c r="C297" s="53" t="s">
+      <c r="C297" s="41" t="s">
         <v>1094</v>
       </c>
       <c r="D297" s="8" t="s">
         <v>1051</v>
       </c>
-      <c r="E297" s="53" t="s">
+      <c r="E297" s="41" t="s">
         <v>1189</v>
       </c>
     </row>
@@ -20946,7 +20987,7 @@
       <c r="B298" s="8">
         <v>13</v>
       </c>
-      <c r="C298" s="53"/>
+      <c r="C298" s="41"/>
       <c r="D298" s="8" t="s">
         <v>1051</v>
       </c>
@@ -20994,7 +21035,7 @@
       <c r="B302" s="8">
         <v>52</v>
       </c>
-      <c r="C302" s="53" t="s">
+      <c r="C302" s="41" t="s">
         <v>739</v>
       </c>
       <c r="D302" s="8" t="s">
@@ -21056,11 +21097,11 @@
       <c r="B306" s="8">
         <v>8</v>
       </c>
-      <c r="C306" s="53"/>
+      <c r="C306" s="41"/>
       <c r="D306" s="8" t="s">
         <v>1051</v>
       </c>
-      <c r="E306" s="53" t="s">
+      <c r="E306" s="41" t="s">
         <v>1189</v>
       </c>
     </row>
@@ -21071,11 +21112,11 @@
       <c r="B307" s="8">
         <v>1</v>
       </c>
-      <c r="C307" s="53"/>
+      <c r="C307" s="41"/>
       <c r="D307" s="8" t="s">
         <v>1051</v>
       </c>
-      <c r="E307" s="53" t="s">
+      <c r="E307" s="41" t="s">
         <v>1189</v>
       </c>
     </row>
@@ -21086,11 +21127,11 @@
       <c r="B308" s="8">
         <v>11</v>
       </c>
-      <c r="C308" s="53"/>
+      <c r="C308" s="41"/>
       <c r="D308" s="8" t="s">
         <v>1051</v>
       </c>
-      <c r="E308" s="53" t="s">
+      <c r="E308" s="41" t="s">
         <v>1189</v>
       </c>
     </row>
@@ -21101,11 +21142,11 @@
       <c r="B309" s="8">
         <v>1</v>
       </c>
-      <c r="C309" s="53"/>
+      <c r="C309" s="41"/>
       <c r="D309" s="8" t="s">
         <v>1088</v>
       </c>
-      <c r="E309" s="53" t="s">
+      <c r="E309" s="41" t="s">
         <v>1189</v>
       </c>
     </row>
@@ -21116,11 +21157,11 @@
       <c r="B310" s="8">
         <v>23</v>
       </c>
-      <c r="C310" s="53"/>
+      <c r="C310" s="41"/>
       <c r="D310" s="8" t="s">
         <v>1051</v>
       </c>
-      <c r="E310" s="53" t="s">
+      <c r="E310" s="41" t="s">
         <v>1189</v>
       </c>
     </row>
@@ -21131,13 +21172,13 @@
       <c r="B311" s="8">
         <v>24</v>
       </c>
-      <c r="C311" s="53" t="s">
+      <c r="C311" s="41" t="s">
         <v>1061</v>
       </c>
       <c r="D311" s="8" t="s">
         <v>1051</v>
       </c>
-      <c r="E311" s="53" t="s">
+      <c r="E311" s="41" t="s">
         <v>1189</v>
       </c>
     </row>
@@ -21148,11 +21189,11 @@
       <c r="B312" s="8">
         <v>6</v>
       </c>
-      <c r="C312" s="53"/>
+      <c r="C312" s="41"/>
       <c r="D312" s="8" t="s">
         <v>1051</v>
       </c>
-      <c r="E312" s="53" t="s">
+      <c r="E312" s="41" t="s">
         <v>1189</v>
       </c>
     </row>
@@ -21247,7 +21288,7 @@
       <c r="B319" s="8">
         <v>6</v>
       </c>
-      <c r="C319" s="53"/>
+      <c r="C319" s="41"/>
       <c r="D319" s="8" t="s">
         <v>1055</v>
       </c>
@@ -21279,7 +21320,7 @@
       <c r="B321" s="8">
         <v>50</v>
       </c>
-      <c r="C321" s="53"/>
+      <c r="C321" s="41"/>
       <c r="D321" s="8" t="s">
         <v>1051</v>
       </c>
@@ -21316,7 +21357,7 @@
       <c r="B324" s="8">
         <v>6</v>
       </c>
-      <c r="C324" s="53"/>
+      <c r="C324" s="41"/>
       <c r="D324" s="8" t="s">
         <v>1051</v>
       </c>
@@ -21434,7 +21475,7 @@
       <c r="B333" s="8">
         <v>13</v>
       </c>
-      <c r="C333" s="53" t="s">
+      <c r="C333" s="41" t="s">
         <v>1101</v>
       </c>
       <c r="D333" s="8" t="s">
@@ -21451,7 +21492,7 @@
       <c r="B334" s="8">
         <v>4</v>
       </c>
-      <c r="C334" s="53"/>
+      <c r="C334" s="41"/>
       <c r="D334" s="8" t="s">
         <v>740</v>
       </c>
@@ -21524,7 +21565,7 @@
       <c r="B340" s="8">
         <v>7</v>
       </c>
-      <c r="C340" s="53"/>
+      <c r="C340" s="41"/>
       <c r="D340" s="8" t="s">
         <v>1055</v>
       </c>
@@ -21578,7 +21619,7 @@
       <c r="B344" s="8">
         <v>111</v>
       </c>
-      <c r="C344" s="53" t="s">
+      <c r="C344" s="41" t="s">
         <v>1061</v>
       </c>
       <c r="D344" s="8" t="s">
@@ -21636,13 +21677,13 @@
       <c r="B349" s="8">
         <v>27</v>
       </c>
-      <c r="C349" s="53" t="s">
+      <c r="C349" s="41" t="s">
         <v>1221</v>
       </c>
       <c r="D349" s="8" t="s">
         <v>1144</v>
       </c>
-      <c r="E349" s="53" t="s">
+      <c r="E349" s="41" t="s">
         <v>1222</v>
       </c>
     </row>
@@ -21945,13 +21986,13 @@
       </c>
     </row>
     <row r="374" spans="1:5" ht="78" customHeight="1">
-      <c r="A374" s="65" t="s">
+      <c r="A374" s="53" t="s">
         <v>1260</v>
       </c>
-      <c r="B374" s="65"/>
-      <c r="C374" s="65"/>
-      <c r="D374" s="65"/>
-      <c r="E374" s="65"/>
+      <c r="B374" s="53"/>
+      <c r="C374" s="53"/>
+      <c r="D374" s="53"/>
+      <c r="E374" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -22010,7 +22051,7 @@
       <c r="A6" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="61" t="s">
+      <c r="B6" s="49" t="s">
         <v>1286</v>
       </c>
     </row>
@@ -22042,7 +22083,7 @@
       <c r="A10" s="26" t="s">
         <v>547</v>
       </c>
-      <c r="B10" s="61" t="s">
+      <c r="B10" s="49" t="s">
         <v>1285</v>
       </c>
     </row>
@@ -22095,23 +22136,23 @@
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="61"/>
+      <c r="A18" s="49"/>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="61" t="s">
+      <c r="B19" s="49" t="s">
         <v>1254</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="49" t="s">
         <v>1255</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="B21" s="61" t="s">
+      <c r="B21" s="49" t="s">
         <v>1288</v>
       </c>
     </row>

--- a/data/chapter2/Brundrett and Tedersoo 2018 - mycorrhizal associations.xlsx
+++ b/data/chapter2/Brundrett and Tedersoo 2018 - mycorrhizal associations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90963425_westernsydney_edu_au/Documents/PhD/code/data/chapter2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_9EE980E2FD5D26AFDFEDEA635E1132CB8726D636" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF889681-845B-4B0E-AD38-94737A5407DF}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="11_9EE980E2FD5D26AFDFEDEA635E1132CB8726D636" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56EA462F-12E2-488D-A9D7-FFA93E862D54}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Article Information" sheetId="7" r:id="rId1"/>
@@ -4720,12 +4720,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -4741,6 +4735,12 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -4748,12 +4748,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="12">
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -4803,13 +4797,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFC4D79B"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="medium">
           <color rgb="FFC4D79B"/>
         </left>
@@ -4820,6 +4807,19 @@
           <color rgb="FFC4D79B"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFC4D79B"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -4858,6 +4858,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:I439" totalsRowShown="0" headerRowDxfId="11" tableBorderDxfId="10">
   <autoFilter ref="A1:I439" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
@@ -4880,18 +4884,18 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2922BC0C-E417-4658-AC0E-62ECDF39ADC6}" name="Table2" displayName="Table2" ref="A2:F89" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="8" tableBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2922BC0C-E417-4658-AC0E-62ECDF39ADC6}" name="Table2" displayName="Table2" ref="A2:F89" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6">
   <autoFilter ref="A2:F89" xr:uid="{2922BC0C-E417-4658-AC0E-62ECDF39ADC6}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:F89">
     <sortCondition ref="B2:B89"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{0BA76706-F6AC-4480-A1EA-EFC458A86717}" name="Order" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{5641DCB1-A433-40BD-9ED9-D33902929B8C}" name="Family" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{DAAE68C8-09E1-4B56-912D-11D87EB83220}" name="Habit" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{2BC3EF26-068C-475F-91C7-4E8D11F95517}" name="Ecology" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{C1FBDF6D-8E5A-4A09-BBA3-846E464D6CA5}" name="NM-AM" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{0B4BCA8E-55FF-4900-A159-74CFB7CBAE73}" name="NM" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{0BA76706-F6AC-4480-A1EA-EFC458A86717}" name="Order" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{5641DCB1-A433-40BD-9ED9-D33902929B8C}" name="Family" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{DAAE68C8-09E1-4B56-912D-11D87EB83220}" name="Habit" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{2BC3EF26-068C-475F-91C7-4E8D11F95517}" name="Ecology" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{C1FBDF6D-8E5A-4A09-BBA3-846E464D6CA5}" name="NM-AM" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{0B4BCA8E-55FF-4900-A159-74CFB7CBAE73}" name="NM" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5329,7 +5333,7 @@
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
-    <col min="2" max="2" width="24.5" customWidth="1"/>
+    <col min="2" max="2" width="32.4140625" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" customWidth="1"/>
     <col min="5" max="5" width="13.33203125" customWidth="1"/>
@@ -15625,35 +15629,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="82" customHeight="1" thickBot="1">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="57" t="s">
         <v>560</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
       <c r="G1" s="8" t="s">
         <v>1261</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="16" thickBot="1">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="58" t="s">
+      <c r="B2" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="56" t="s">
         <v>561</v>
       </c>
-      <c r="D2" s="58" t="s">
+      <c r="D2" s="56" t="s">
         <v>562</v>
       </c>
-      <c r="E2" s="58" t="s">
+      <c r="E2" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="58" t="s">
+      <c r="F2" s="56" t="s">
         <v>12</v>
       </c>
     </row>
@@ -15673,7 +15677,7 @@
       <c r="E3" s="36">
         <v>2</v>
       </c>
-      <c r="F3" s="55"/>
+      <c r="F3" s="53"/>
     </row>
     <row r="4" spans="1:7" ht="16" thickBot="1">
       <c r="A4" s="36" t="s">
@@ -15688,7 +15692,7 @@
       <c r="D4" s="36" t="s">
         <v>592</v>
       </c>
-      <c r="E4" s="55"/>
+      <c r="E4" s="53"/>
       <c r="F4" s="36">
         <v>1900</v>
       </c>
@@ -15709,7 +15713,7 @@
       <c r="E5" s="35">
         <v>115</v>
       </c>
-      <c r="F5" s="54"/>
+      <c r="F5" s="52"/>
     </row>
     <row r="6" spans="1:7" ht="16" thickBot="1">
       <c r="A6" s="36" t="s">
@@ -15724,7 +15728,7 @@
       <c r="D6" s="36" t="s">
         <v>595</v>
       </c>
-      <c r="E6" s="55"/>
+      <c r="E6" s="53"/>
       <c r="F6" s="36">
         <v>2040</v>
       </c>
@@ -15742,7 +15746,7 @@
       <c r="D7" s="35" t="s">
         <v>567</v>
       </c>
-      <c r="E7" s="54"/>
+      <c r="E7" s="52"/>
       <c r="F7" s="35">
         <v>10</v>
       </c>
@@ -15763,7 +15767,7 @@
       <c r="E8" s="36">
         <v>56</v>
       </c>
-      <c r="F8" s="55"/>
+      <c r="F8" s="53"/>
     </row>
     <row r="9" spans="1:7" ht="16" thickBot="1">
       <c r="A9" s="35" t="s">
@@ -15781,7 +15785,7 @@
       <c r="E9" s="35">
         <v>1300</v>
       </c>
-      <c r="F9" s="54"/>
+      <c r="F9" s="52"/>
     </row>
     <row r="10" spans="1:7" ht="16" thickBot="1">
       <c r="A10" s="36" t="s">
@@ -15796,7 +15800,7 @@
       <c r="D10" s="36" t="s">
         <v>573</v>
       </c>
-      <c r="E10" s="55"/>
+      <c r="E10" s="53"/>
       <c r="F10" s="36">
         <v>8</v>
       </c>
@@ -15814,7 +15818,7 @@
       <c r="D11" s="35" t="s">
         <v>567</v>
       </c>
-      <c r="E11" s="54"/>
+      <c r="E11" s="52"/>
       <c r="F11" s="35">
         <v>39</v>
       </c>
@@ -15832,7 +15836,7 @@
       <c r="D12" s="35" t="s">
         <v>617</v>
       </c>
-      <c r="E12" s="54"/>
+      <c r="E12" s="52"/>
       <c r="F12" s="35">
         <v>3628</v>
       </c>
@@ -15850,10 +15854,10 @@
       <c r="D13" s="35" t="s">
         <v>570</v>
       </c>
-      <c r="E13" s="56">
+      <c r="E13" s="54">
         <v>3475</v>
       </c>
-      <c r="F13" s="54"/>
+      <c r="F13" s="52"/>
     </row>
     <row r="14" spans="1:7" ht="16" thickBot="1">
       <c r="A14" s="36" t="s">
@@ -15871,7 +15875,7 @@
       <c r="E14" s="36">
         <v>1</v>
       </c>
-      <c r="F14" s="55"/>
+      <c r="F14" s="53"/>
     </row>
     <row r="15" spans="1:7" ht="16" thickBot="1">
       <c r="A15" s="35" t="s">
@@ -15886,7 +15890,7 @@
       <c r="D15" s="35" t="s">
         <v>598</v>
       </c>
-      <c r="E15" s="54"/>
+      <c r="E15" s="52"/>
       <c r="F15" s="35">
         <v>8</v>
       </c>
@@ -15907,7 +15911,7 @@
       <c r="E16" s="36">
         <v>75</v>
       </c>
-      <c r="F16" s="55"/>
+      <c r="F16" s="53"/>
     </row>
     <row r="17" spans="1:6" ht="16" thickBot="1">
       <c r="A17" s="36" t="s">
@@ -15922,7 +15926,7 @@
       <c r="D17" s="36" t="s">
         <v>618</v>
       </c>
-      <c r="E17" s="55"/>
+      <c r="E17" s="53"/>
       <c r="F17" s="36">
         <v>450</v>
       </c>
@@ -15940,7 +15944,7 @@
       <c r="D18" s="35" t="s">
         <v>596</v>
       </c>
-      <c r="E18" s="54"/>
+      <c r="E18" s="52"/>
       <c r="F18" s="35">
         <v>2625</v>
       </c>
@@ -15958,7 +15962,7 @@
       <c r="D19" s="35" t="s">
         <v>598</v>
       </c>
-      <c r="E19" s="54"/>
+      <c r="E19" s="52"/>
       <c r="F19" s="35">
         <v>1</v>
       </c>
@@ -15976,7 +15980,7 @@
       <c r="D20" s="36" t="s">
         <v>564</v>
       </c>
-      <c r="E20" s="55"/>
+      <c r="E20" s="53"/>
       <c r="F20" s="36">
         <v>4</v>
       </c>
@@ -15994,7 +15998,7 @@
       <c r="D21" s="35" t="s">
         <v>592</v>
       </c>
-      <c r="E21" s="54"/>
+      <c r="E21" s="52"/>
       <c r="F21" s="35">
         <v>346</v>
       </c>
@@ -16012,7 +16016,7 @@
       <c r="D22" s="36" t="s">
         <v>577</v>
       </c>
-      <c r="E22" s="55"/>
+      <c r="E22" s="53"/>
       <c r="F22" s="36">
         <v>731</v>
       </c>
@@ -16030,7 +16034,7 @@
       <c r="D23" s="36" t="s">
         <v>567</v>
       </c>
-      <c r="E23" s="55"/>
+      <c r="E23" s="53"/>
       <c r="F23" s="36">
         <v>172</v>
       </c>
@@ -16071,7 +16075,7 @@
       <c r="E25" s="36">
         <v>230</v>
       </c>
-      <c r="F25" s="55"/>
+      <c r="F25" s="53"/>
     </row>
     <row r="26" spans="1:6" ht="16" thickBot="1">
       <c r="A26" s="35" t="s">
@@ -16086,7 +16090,7 @@
       <c r="D26" s="35" t="s">
         <v>573</v>
       </c>
-      <c r="E26" s="54"/>
+      <c r="E26" s="52"/>
       <c r="F26" s="35">
         <v>17</v>
       </c>
@@ -16104,7 +16108,7 @@
       <c r="D27" s="36" t="s">
         <v>567</v>
       </c>
-      <c r="E27" s="55"/>
+      <c r="E27" s="53"/>
       <c r="F27" s="36">
         <v>2</v>
       </c>
@@ -16125,7 +16129,7 @@
       <c r="E28" s="36">
         <v>5500</v>
       </c>
-      <c r="F28" s="55"/>
+      <c r="F28" s="53"/>
     </row>
     <row r="29" spans="1:6" ht="16" thickBot="1">
       <c r="A29" s="36" t="s">
@@ -16140,7 +16144,7 @@
       <c r="D29" s="36" t="s">
         <v>567</v>
       </c>
-      <c r="E29" s="55"/>
+      <c r="E29" s="53"/>
       <c r="F29" s="36">
         <v>10</v>
       </c>
@@ -16158,7 +16162,7 @@
       <c r="D30" s="35" t="s">
         <v>576</v>
       </c>
-      <c r="E30" s="54"/>
+      <c r="E30" s="52"/>
       <c r="F30" s="35">
         <v>16</v>
       </c>
@@ -16176,7 +16180,7 @@
       <c r="D31" s="35" t="s">
         <v>598</v>
       </c>
-      <c r="E31" s="54"/>
+      <c r="E31" s="52"/>
       <c r="F31" s="35">
         <v>180</v>
       </c>
@@ -16194,7 +16198,7 @@
       <c r="D32" s="36" t="s">
         <v>598</v>
       </c>
-      <c r="E32" s="55"/>
+      <c r="E32" s="53"/>
       <c r="F32" s="36">
         <v>1</v>
       </c>
@@ -16215,7 +16219,7 @@
       <c r="E33" s="36">
         <v>242</v>
       </c>
-      <c r="F33" s="55"/>
+      <c r="F33" s="53"/>
     </row>
     <row r="34" spans="1:6" ht="16" thickBot="1">
       <c r="A34" s="36" t="s">
@@ -16230,7 +16234,7 @@
       <c r="D34" s="36" t="s">
         <v>588</v>
       </c>
-      <c r="E34" s="55"/>
+      <c r="E34" s="53"/>
       <c r="F34" s="36">
         <v>700</v>
       </c>
@@ -16248,7 +16252,7 @@
       <c r="D35" s="35" t="s">
         <v>601</v>
       </c>
-      <c r="E35" s="54"/>
+      <c r="E35" s="52"/>
       <c r="F35" s="35">
         <v>90</v>
       </c>
@@ -16266,7 +16270,7 @@
       <c r="D36" s="35" t="s">
         <v>576</v>
       </c>
-      <c r="E36" s="54"/>
+      <c r="E36" s="52"/>
       <c r="F36" s="35">
         <v>102</v>
       </c>
@@ -16287,7 +16291,7 @@
       <c r="E37" s="36">
         <v>50</v>
       </c>
-      <c r="F37" s="55"/>
+      <c r="F37" s="53"/>
     </row>
     <row r="38" spans="1:6" ht="16" thickBot="1">
       <c r="A38" s="35" t="s">
@@ -16302,7 +16306,7 @@
       <c r="D38" s="35" t="s">
         <v>564</v>
       </c>
-      <c r="E38" s="54"/>
+      <c r="E38" s="52"/>
       <c r="F38" s="35">
         <v>3</v>
       </c>
@@ -16320,7 +16324,7 @@
       <c r="D39" s="35" t="s">
         <v>564</v>
       </c>
-      <c r="E39" s="54"/>
+      <c r="E39" s="52"/>
       <c r="F39" s="35">
         <v>12</v>
       </c>
@@ -16338,7 +16342,7 @@
       <c r="D40" s="36" t="s">
         <v>567</v>
       </c>
-      <c r="E40" s="55"/>
+      <c r="E40" s="53"/>
       <c r="F40" s="36">
         <v>7</v>
       </c>
@@ -16356,7 +16360,7 @@
       <c r="D41" s="36" t="s">
         <v>574</v>
       </c>
-      <c r="E41" s="55"/>
+      <c r="E41" s="53"/>
       <c r="F41" s="36">
         <v>135</v>
       </c>
@@ -16377,7 +16381,7 @@
       <c r="E42" s="35">
         <v>300</v>
       </c>
-      <c r="F42" s="54"/>
+      <c r="F42" s="52"/>
     </row>
     <row r="43" spans="1:6" ht="16" thickBot="1">
       <c r="A43" s="36" t="s">
@@ -16392,7 +16396,7 @@
       <c r="D43" s="36" t="s">
         <v>581</v>
       </c>
-      <c r="E43" s="55"/>
+      <c r="E43" s="53"/>
       <c r="F43" s="36">
         <v>464</v>
       </c>
@@ -16413,7 +16417,7 @@
       <c r="E44" s="35">
         <v>34</v>
       </c>
-      <c r="F44" s="54"/>
+      <c r="F44" s="52"/>
     </row>
     <row r="45" spans="1:6" ht="16" thickBot="1">
       <c r="A45" s="35" t="s">
@@ -16428,7 +16432,7 @@
       <c r="D45" s="35" t="s">
         <v>567</v>
       </c>
-      <c r="E45" s="54"/>
+      <c r="E45" s="52"/>
       <c r="F45" s="35">
         <v>19</v>
       </c>
@@ -16446,7 +16450,7 @@
       <c r="D46" s="36" t="s">
         <v>567</v>
       </c>
-      <c r="E46" s="55"/>
+      <c r="E46" s="53"/>
       <c r="F46" s="36">
         <v>4</v>
       </c>
@@ -16464,7 +16468,7 @@
       <c r="D47" s="36" t="s">
         <v>598</v>
       </c>
-      <c r="E47" s="55"/>
+      <c r="E47" s="53"/>
       <c r="F47" s="36">
         <v>316</v>
       </c>
@@ -16482,7 +16486,7 @@
       <c r="D48" s="36" t="s">
         <v>564</v>
       </c>
-      <c r="E48" s="55"/>
+      <c r="E48" s="53"/>
       <c r="F48" s="36">
         <v>8</v>
       </c>
@@ -16500,7 +16504,7 @@
       <c r="D49" s="36" t="s">
         <v>589</v>
       </c>
-      <c r="E49" s="55"/>
+      <c r="E49" s="53"/>
       <c r="F49" s="36">
         <v>308</v>
       </c>
@@ -16518,7 +16522,7 @@
       <c r="D50" s="35" t="s">
         <v>567</v>
       </c>
-      <c r="E50" s="54"/>
+      <c r="E50" s="52"/>
       <c r="F50" s="35">
         <v>1039</v>
       </c>
@@ -16539,7 +16543,7 @@
       <c r="E51" s="35">
         <v>60</v>
       </c>
-      <c r="F51" s="54"/>
+      <c r="F51" s="52"/>
     </row>
     <row r="52" spans="1:6" ht="16" thickBot="1">
       <c r="A52" s="36" t="s">
@@ -16554,7 +16558,7 @@
       <c r="D52" s="36" t="s">
         <v>567</v>
       </c>
-      <c r="E52" s="55"/>
+      <c r="E52" s="53"/>
       <c r="F52" s="36">
         <v>8</v>
       </c>
@@ -16572,7 +16576,7 @@
       <c r="D53" s="36" t="s">
         <v>567</v>
       </c>
-      <c r="E53" s="55"/>
+      <c r="E53" s="53"/>
       <c r="F53" s="36">
         <v>2</v>
       </c>
@@ -16590,7 +16594,7 @@
       <c r="D54" s="36" t="s">
         <v>602</v>
       </c>
-      <c r="E54" s="55"/>
+      <c r="E54" s="53"/>
       <c r="F54" s="36">
         <v>80</v>
       </c>
@@ -16608,7 +16612,7 @@
       <c r="D55" s="35" t="s">
         <v>585</v>
       </c>
-      <c r="E55" s="54"/>
+      <c r="E55" s="52"/>
       <c r="F55" s="35">
         <v>57</v>
       </c>
@@ -16626,7 +16630,7 @@
       <c r="D56" s="36" t="s">
         <v>564</v>
       </c>
-      <c r="E56" s="55"/>
+      <c r="E56" s="53"/>
       <c r="F56" s="36">
         <v>3</v>
       </c>
@@ -16644,7 +16648,7 @@
       <c r="D57" s="35" t="s">
         <v>598</v>
       </c>
-      <c r="E57" s="54"/>
+      <c r="E57" s="52"/>
       <c r="F57" s="35">
         <v>150</v>
       </c>
@@ -16662,7 +16666,7 @@
       <c r="D58" s="36" t="s">
         <v>227</v>
       </c>
-      <c r="E58" s="55"/>
+      <c r="E58" s="53"/>
       <c r="F58" s="36">
         <v>400</v>
       </c>
@@ -16683,7 +16687,7 @@
       <c r="E59" s="35">
         <v>70</v>
       </c>
-      <c r="F59" s="54"/>
+      <c r="F59" s="52"/>
     </row>
     <row r="60" spans="1:6" ht="16" thickBot="1">
       <c r="A60" s="36" t="s">
@@ -16698,7 +16702,7 @@
       <c r="D60" s="36" t="s">
         <v>567</v>
       </c>
-      <c r="E60" s="55"/>
+      <c r="E60" s="53"/>
       <c r="F60" s="36">
         <v>59</v>
       </c>
@@ -16716,7 +16720,7 @@
       <c r="D61" s="36" t="s">
         <v>567</v>
       </c>
-      <c r="E61" s="55"/>
+      <c r="E61" s="53"/>
       <c r="F61" s="36">
         <v>36</v>
       </c>
@@ -16734,7 +16738,7 @@
       <c r="D62" s="35" t="s">
         <v>567</v>
       </c>
-      <c r="E62" s="54"/>
+      <c r="E62" s="52"/>
       <c r="F62" s="35">
         <v>1957</v>
       </c>
@@ -16755,7 +16759,7 @@
       <c r="E63" s="35">
         <v>775</v>
       </c>
-      <c r="F63" s="54"/>
+      <c r="F63" s="52"/>
     </row>
     <row r="64" spans="1:6" ht="16" thickBot="1">
       <c r="A64" s="35" t="s">
@@ -16770,7 +16774,7 @@
       <c r="D64" s="35" t="s">
         <v>589</v>
       </c>
-      <c r="E64" s="54"/>
+      <c r="E64" s="52"/>
       <c r="F64" s="35">
         <v>33</v>
       </c>
@@ -16791,7 +16795,7 @@
       <c r="E65" s="35">
         <v>3700</v>
       </c>
-      <c r="F65" s="54"/>
+      <c r="F65" s="52"/>
     </row>
     <row r="66" spans="1:6" ht="16" thickBot="1">
       <c r="A66" s="36" t="s">
@@ -16809,7 +16813,7 @@
       <c r="E66" s="36">
         <v>725</v>
       </c>
-      <c r="F66" s="55"/>
+      <c r="F66" s="53"/>
     </row>
     <row r="67" spans="1:6" ht="16" thickBot="1">
       <c r="A67" s="35" t="s">
@@ -16827,7 +16831,7 @@
       <c r="E67" s="35">
         <v>300</v>
       </c>
-      <c r="F67" s="54"/>
+      <c r="F67" s="52"/>
     </row>
     <row r="68" spans="1:6" ht="16" thickBot="1">
       <c r="A68" s="35" t="s">
@@ -16842,7 +16846,7 @@
       <c r="D68" s="35" t="s">
         <v>589</v>
       </c>
-      <c r="E68" s="54"/>
+      <c r="E68" s="52"/>
       <c r="F68" s="35">
         <v>1200</v>
       </c>
@@ -16863,7 +16867,7 @@
       <c r="E69" s="36">
         <v>34</v>
       </c>
-      <c r="F69" s="55"/>
+      <c r="F69" s="53"/>
     </row>
     <row r="70" spans="1:6" ht="16" thickBot="1">
       <c r="A70" s="36" t="s">
@@ -16881,7 +16885,7 @@
       <c r="E70" s="36">
         <v>115</v>
       </c>
-      <c r="F70" s="55"/>
+      <c r="F70" s="53"/>
     </row>
     <row r="71" spans="1:6" ht="16" thickBot="1">
       <c r="A71" s="36" t="s">
@@ -16896,7 +16900,7 @@
       <c r="D71" s="36" t="s">
         <v>573</v>
       </c>
-      <c r="E71" s="55"/>
+      <c r="E71" s="53"/>
       <c r="F71" s="36">
         <v>9</v>
       </c>
@@ -16917,7 +16921,7 @@
       <c r="E72" s="35">
         <v>110</v>
       </c>
-      <c r="F72" s="54"/>
+      <c r="F72" s="52"/>
     </row>
     <row r="73" spans="1:6" ht="16" thickBot="1">
       <c r="A73" s="35" t="s">
@@ -16932,7 +16936,7 @@
       <c r="D73" s="35" t="s">
         <v>585</v>
       </c>
-      <c r="E73" s="54"/>
+      <c r="E73" s="52"/>
       <c r="F73" s="35">
         <v>1660</v>
       </c>
@@ -16950,7 +16954,7 @@
       <c r="D74" s="36" t="s">
         <v>227</v>
       </c>
-      <c r="E74" s="55"/>
+      <c r="E74" s="53"/>
       <c r="F74" s="36">
         <v>50</v>
       </c>
@@ -16968,7 +16972,7 @@
       <c r="D75" s="35" t="s">
         <v>567</v>
       </c>
-      <c r="E75" s="54"/>
+      <c r="E75" s="52"/>
       <c r="F75" s="35">
         <v>25</v>
       </c>
@@ -16986,7 +16990,7 @@
       <c r="D76" s="35" t="s">
         <v>619</v>
       </c>
-      <c r="E76" s="54"/>
+      <c r="E76" s="52"/>
       <c r="F76" s="35">
         <v>107</v>
       </c>
@@ -17004,7 +17008,7 @@
       <c r="D77" s="35" t="s">
         <v>583</v>
       </c>
-      <c r="E77" s="54"/>
+      <c r="E77" s="52"/>
       <c r="F77" s="35">
         <v>572</v>
       </c>
@@ -17025,7 +17029,7 @@
       <c r="E78" s="36">
         <v>147</v>
       </c>
-      <c r="F78" s="55"/>
+      <c r="F78" s="53"/>
     </row>
     <row r="79" spans="1:6" ht="16" thickBot="1">
       <c r="A79" s="35" t="s">
@@ -17040,8 +17044,8 @@
       <c r="D79" s="35" t="s">
         <v>598</v>
       </c>
-      <c r="E79" s="54"/>
-      <c r="F79" s="54"/>
+      <c r="E79" s="52"/>
+      <c r="F79" s="52"/>
     </row>
     <row r="80" spans="1:6" ht="16" thickBot="1">
       <c r="A80" s="36" t="s">
@@ -17056,7 +17060,7 @@
       <c r="D80" s="36" t="s">
         <v>574</v>
       </c>
-      <c r="E80" s="55"/>
+      <c r="E80" s="53"/>
       <c r="F80" s="36">
         <v>8</v>
       </c>
@@ -17074,7 +17078,7 @@
       <c r="D81" s="35" t="s">
         <v>567</v>
       </c>
-      <c r="E81" s="54"/>
+      <c r="E81" s="52"/>
       <c r="F81" s="35">
         <v>1097</v>
       </c>
@@ -17092,7 +17096,7 @@
       <c r="D82" s="35" t="s">
         <v>598</v>
       </c>
-      <c r="E82" s="54"/>
+      <c r="E82" s="52"/>
       <c r="F82" s="35">
         <v>34</v>
       </c>
@@ -17113,7 +17117,7 @@
       <c r="E83" s="35">
         <v>640</v>
       </c>
-      <c r="F83" s="54"/>
+      <c r="F83" s="52"/>
     </row>
     <row r="84" spans="1:6" ht="16" thickBot="1">
       <c r="A84" s="35" t="s">
@@ -17131,7 +17135,7 @@
       <c r="E84" s="35">
         <v>78</v>
       </c>
-      <c r="F84" s="54"/>
+      <c r="F84" s="52"/>
     </row>
     <row r="85" spans="1:6" ht="16" thickBot="1">
       <c r="A85" s="36" t="s">
@@ -17146,7 +17150,7 @@
       <c r="D85" s="36" t="s">
         <v>564</v>
       </c>
-      <c r="E85" s="55"/>
+      <c r="E85" s="53"/>
       <c r="F85" s="36">
         <v>51</v>
       </c>
@@ -17167,7 +17171,7 @@
       <c r="E86" s="36">
         <v>2625</v>
       </c>
-      <c r="F86" s="55"/>
+      <c r="F86" s="53"/>
     </row>
     <row r="87" spans="1:6" ht="16" thickBot="1">
       <c r="A87" s="35" t="s">
@@ -17182,7 +17186,7 @@
       <c r="D87" s="35" t="s">
         <v>564</v>
       </c>
-      <c r="E87" s="54"/>
+      <c r="E87" s="52"/>
       <c r="F87" s="35">
         <v>399</v>
       </c>
@@ -17200,7 +17204,7 @@
       <c r="D88" s="35" t="s">
         <v>573</v>
       </c>
-      <c r="E88" s="54"/>
+      <c r="E88" s="52"/>
       <c r="F88" s="35">
         <v>22</v>
       </c>
@@ -17221,7 +17225,7 @@
       <c r="E89" s="34">
         <v>285</v>
       </c>
-      <c r="F89" s="57"/>
+      <c r="F89" s="55"/>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="37" t="s">
@@ -21986,13 +21990,13 @@
       </c>
     </row>
     <row r="374" spans="1:5" ht="78" customHeight="1">
-      <c r="A374" s="53" t="s">
+      <c r="A374" s="58" t="s">
         <v>1260</v>
       </c>
-      <c r="B374" s="53"/>
-      <c r="C374" s="53"/>
-      <c r="D374" s="53"/>
-      <c r="E374" s="53"/>
+      <c r="B374" s="58"/>
+      <c r="C374" s="58"/>
+      <c r="D374" s="58"/>
+      <c r="E374" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/chapter2/Brundrett and Tedersoo 2018 - mycorrhizal associations.xlsx
+++ b/data/chapter2/Brundrett and Tedersoo 2018 - mycorrhizal associations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90963425_westernsydney_edu_au/Documents/PhD/code/data/chapter2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_9EE980E2FD5D26AFDFEDEA635E1132CB8726D636" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56EA462F-12E2-488D-A9D7-FFA93E862D54}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="11_9EE980E2FD5D26AFDFEDEA635E1132CB8726D636" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9142FCD1-841D-46F7-BE01-F1D7C18E1826}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Article Information" sheetId="7" r:id="rId1"/>

--- a/data/chapter2/Brundrett and Tedersoo 2018 - mycorrhizal associations.xlsx
+++ b/data/chapter2/Brundrett and Tedersoo 2018 - mycorrhizal associations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90963425_westernsydney_edu_au/Documents/PhD/code/data/chapter2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="11_9EE980E2FD5D26AFDFEDEA635E1132CB8726D636" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9142FCD1-841D-46F7-BE01-F1D7C18E1826}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="11_9EE980E2FD5D26AFDFEDEA635E1132CB8726D636" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{400E431F-0B84-4B76-8C78-E306B40FBEF0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Article Information" sheetId="7" r:id="rId1"/>

--- a/data/chapter2/Brundrett and Tedersoo 2018 - mycorrhizal associations.xlsx
+++ b/data/chapter2/Brundrett and Tedersoo 2018 - mycorrhizal associations.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="24" documentId="11_9EE980E2FD5D26AFDFEDEA635E1132CB8726D636" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{400E431F-0B84-4B76-8C78-E306B40FBEF0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Article Information" sheetId="7" r:id="rId1"/>

--- a/data/chapter2/Brundrett and Tedersoo 2018 - mycorrhizal associations.xlsx
+++ b/data/chapter2/Brundrett and Tedersoo 2018 - mycorrhizal associations.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="24" documentId="11_9EE980E2FD5D26AFDFEDEA635E1132CB8726D636" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{400E431F-0B84-4B76-8C78-E306B40FBEF0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Article Information" sheetId="7" r:id="rId1"/>

--- a/data/chapter2/Brundrett and Tedersoo 2018 - mycorrhizal associations.xlsx
+++ b/data/chapter2/Brundrett and Tedersoo 2018 - mycorrhizal associations.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="24" documentId="11_9EE980E2FD5D26AFDFEDEA635E1132CB8726D636" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{400E431F-0B84-4B76-8C78-E306B40FBEF0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Article Information" sheetId="7" r:id="rId1"/>
